--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\Becario Procesos\EOAT Project\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\BECARIO PROCESOS\EOAT PROJECT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C67F98C-612F-4E93-AAB4-A4E5E423296B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC522F30-779C-4B2D-942D-FAC4D34D0AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="700">
   <si>
     <t>I-1937</t>
   </si>
@@ -326,9 +326,6 @@
     <t>I-1472</t>
   </si>
   <si>
-    <t>I-1216</t>
-  </si>
-  <si>
     <t>I-1938</t>
   </si>
   <si>
@@ -686,9 +683,6 @@
     <t>I-1472.jpeg</t>
   </si>
   <si>
-    <t>I-1216.jpeg</t>
-  </si>
-  <si>
     <t>I-1938.jpeg</t>
   </si>
   <si>
@@ -2025,6 +2019,126 @@
   </si>
   <si>
     <t>4 ventosas, se agregaron pinzas de corte</t>
+  </si>
+  <si>
+    <t>1 ventosa</t>
+  </si>
+  <si>
+    <t>1 pinza</t>
+  </si>
+  <si>
+    <t>1 pinza, 2 ventosas</t>
+  </si>
+  <si>
+    <t>1 pinza, 1 ventosa</t>
+  </si>
+  <si>
+    <t>2 ventosas, 2 pinzas, 2 dedos</t>
+  </si>
+  <si>
+    <t>6 ventosas, 1 pinza</t>
+  </si>
+  <si>
+    <t>4 ventosas, 3 pinzas</t>
+  </si>
+  <si>
+    <t>3 pinzas</t>
+  </si>
+  <si>
+    <t>3 ventosas, 1 pinza</t>
+  </si>
+  <si>
+    <t>6 ventosas</t>
+  </si>
+  <si>
+    <t>1 ventosa, 1 pinza</t>
+  </si>
+  <si>
+    <t>2 dedos, 4 pinzas</t>
+  </si>
+  <si>
+    <t>2 ventosas, 1 dedo, 3 pinzas</t>
+  </si>
+  <si>
+    <t>1 ventosa, 4 pinzas</t>
+  </si>
+  <si>
+    <t>2 ventosas, 2 dedos, 1 pinza</t>
+  </si>
+  <si>
+    <t>2 ventosas, 4 pinzas</t>
+  </si>
+  <si>
+    <t>2 dedos, 7 pinzas</t>
+  </si>
+  <si>
+    <t>2 dedos, 6 pinzas</t>
+  </si>
+  <si>
+    <t>4 ventosas, 2 dedos, 2 pinzas</t>
+  </si>
+  <si>
+    <t>6 pinzas</t>
+  </si>
+  <si>
+    <t>1 ventosa, 2 pinzas</t>
+  </si>
+  <si>
+    <t>4 dedos, 2 pinzas</t>
+  </si>
+  <si>
+    <t>3 ventosas, 2 dedos</t>
+  </si>
+  <si>
+    <t>4 dedos</t>
+  </si>
+  <si>
+    <t>4 ventosas, 2 dedos, 6 pinzas</t>
+  </si>
+  <si>
+    <t>2 ventosas, 2 dedos, 5 pinzas</t>
+  </si>
+  <si>
+    <t>2 ventosas, 4 dedos, 1 pinza</t>
+  </si>
+  <si>
+    <t>9 ventosas, 6 pinzas, 6 dedos</t>
+  </si>
+  <si>
+    <t>6 ventosas, 2 dedos, 1 pinza</t>
+  </si>
+  <si>
+    <t>2 ventosas, 3 dedos</t>
+  </si>
+  <si>
+    <t>2 ventosas, 2 dedos</t>
+  </si>
+  <si>
+    <t>2 pinzas de corte, 3 pinzas</t>
+  </si>
+  <si>
+    <t>8 ventosas, 7 dedos, 4 pinzas</t>
+  </si>
+  <si>
+    <t>8 ventosas, 4 dedos</t>
+  </si>
+  <si>
+    <t>18 pinzas</t>
+  </si>
+  <si>
+    <t>15 ventosas, 4 pinzas</t>
+  </si>
+  <si>
+    <t>15 ventosas, 2 pinzas</t>
+  </si>
+  <si>
+    <t>8 dedos, 4 pinzas</t>
+  </si>
+  <si>
+    <t>8 ventosas, 2 pinzas</t>
+  </si>
+  <si>
+    <t>3 dedos, 2 pinzas</t>
   </si>
 </sst>
 </file>
@@ -2415,22 +2529,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C1" t="s">
         <v>250</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>251</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>252</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>253</v>
-      </c>
-      <c r="E1" t="s">
-        <v>254</v>
-      </c>
-      <c r="F1" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2438,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>256</v>
+        <v>699</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -2450,7 +2564,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2458,7 +2572,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>256</v>
+        <v>694</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -2470,7 +2584,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2478,7 +2592,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -2490,7 +2604,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2498,7 +2612,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>256</v>
+        <v>693</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -2510,7 +2624,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2518,7 +2632,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>256</v>
+        <v>652</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -2530,7 +2644,7 @@
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2538,7 +2652,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -2550,7 +2664,7 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2558,7 +2672,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -2570,7 +2684,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2578,7 +2692,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>256</v>
+        <v>692</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -2590,7 +2704,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2598,7 +2712,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>256</v>
+        <v>690</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -2610,7 +2724,7 @@
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2618,7 +2732,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>256</v>
+        <v>689</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -2630,7 +2744,7 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2638,7 +2752,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>256</v>
+        <v>688</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -2650,7 +2764,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2658,7 +2772,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -2670,7 +2784,7 @@
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2678,7 +2792,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>256</v>
+        <v>688</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -2690,7 +2804,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2698,7 +2812,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>256</v>
+        <v>687</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -2710,7 +2824,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2718,7 +2832,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -2730,7 +2844,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2738,7 +2852,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>256</v>
+        <v>685</v>
       </c>
       <c r="C17">
         <v>3</v>
@@ -2750,7 +2864,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2758,7 +2872,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>256</v>
+        <v>652</v>
       </c>
       <c r="C18">
         <v>3</v>
@@ -2770,7 +2884,7 @@
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2778,7 +2892,7 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>256</v>
+        <v>667</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -2790,7 +2904,7 @@
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2798,7 +2912,7 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>256</v>
+        <v>682</v>
       </c>
       <c r="C20">
         <v>3</v>
@@ -2810,7 +2924,7 @@
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2818,7 +2932,7 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>256</v>
+        <v>684</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -2830,7 +2944,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2838,7 +2952,7 @@
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>256</v>
+        <v>683</v>
       </c>
       <c r="C22">
         <v>3</v>
@@ -2850,7 +2964,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2858,7 +2972,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -2870,7 +2984,7 @@
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2878,7 +2992,7 @@
         <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -2890,7 +3004,7 @@
         <v>2</v>
       </c>
       <c r="F24" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2898,7 +3012,7 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -2910,7 +3024,7 @@
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2918,7 +3032,7 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -2930,15 +3044,15 @@
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B27" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -2950,15 +3064,15 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B28" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -2970,7 +3084,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2978,7 +3092,7 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -2990,7 +3104,7 @@
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2998,7 +3112,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>256</v>
+        <v>673</v>
       </c>
       <c r="C30">
         <v>3</v>
@@ -3010,7 +3124,7 @@
         <v>3</v>
       </c>
       <c r="F30" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -3018,7 +3132,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C31">
         <v>3</v>
@@ -3030,7 +3144,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -3038,7 +3152,7 @@
         <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C32">
         <v>3</v>
@@ -3050,7 +3164,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -3058,7 +3172,7 @@
         <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C33">
         <v>3</v>
@@ -3070,7 +3184,7 @@
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -3078,7 +3192,7 @@
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C34">
         <v>3</v>
@@ -3090,7 +3204,7 @@
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -3098,7 +3212,7 @@
         <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>256</v>
+        <v>672</v>
       </c>
       <c r="C35">
         <v>3</v>
@@ -3110,7 +3224,7 @@
         <v>3</v>
       </c>
       <c r="F35" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3118,7 +3232,7 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>256</v>
+        <v>671</v>
       </c>
       <c r="C36">
         <v>3</v>
@@ -3130,7 +3244,7 @@
         <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3138,7 +3252,7 @@
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C37">
         <v>3</v>
@@ -3150,7 +3264,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3158,7 +3272,7 @@
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C38">
         <v>3</v>
@@ -3170,7 +3284,7 @@
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3178,7 +3292,7 @@
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C39">
         <v>3</v>
@@ -3190,7 +3304,7 @@
         <v>2</v>
       </c>
       <c r="F39" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3198,7 +3312,7 @@
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C40">
         <v>3</v>
@@ -3210,7 +3324,7 @@
         <v>3</v>
       </c>
       <c r="F40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -3218,7 +3332,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C41">
         <v>3</v>
@@ -3230,7 +3344,7 @@
         <v>3</v>
       </c>
       <c r="F41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -3238,7 +3352,7 @@
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C42">
         <v>3</v>
@@ -3250,7 +3364,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -3258,7 +3372,7 @@
         <v>47</v>
       </c>
       <c r="B43" t="s">
-        <v>256</v>
+        <v>649</v>
       </c>
       <c r="C43">
         <v>3</v>
@@ -3270,7 +3384,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -3278,7 +3392,7 @@
         <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C44">
         <v>3</v>
@@ -3290,7 +3404,7 @@
         <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -3298,7 +3412,7 @@
         <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>256</v>
+        <v>666</v>
       </c>
       <c r="C45">
         <v>3</v>
@@ -3310,7 +3424,7 @@
         <v>3</v>
       </c>
       <c r="F45" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -3318,7 +3432,7 @@
         <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>256</v>
+        <v>645</v>
       </c>
       <c r="C46">
         <v>3</v>
@@ -3330,7 +3444,7 @@
         <v>3</v>
       </c>
       <c r="F46" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3338,7 +3452,7 @@
         <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C47">
         <v>3</v>
@@ -3350,7 +3464,7 @@
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3358,7 +3472,7 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C48">
         <v>3</v>
@@ -3370,7 +3484,7 @@
         <v>2</v>
       </c>
       <c r="F48" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3378,7 +3492,7 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C49">
         <v>3</v>
@@ -3390,7 +3504,7 @@
         <v>3</v>
       </c>
       <c r="F49" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -3398,7 +3512,7 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C50">
         <v>3</v>
@@ -3410,7 +3524,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -3418,7 +3532,7 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C51">
         <v>3</v>
@@ -3427,10 +3541,10 @@
         <v>56</v>
       </c>
       <c r="E51" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F51" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3438,7 +3552,7 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -3447,10 +3561,10 @@
         <v>56</v>
       </c>
       <c r="E52" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F52" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -3458,7 +3572,7 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C53">
         <v>3</v>
@@ -3470,7 +3584,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3478,7 +3592,7 @@
         <v>62</v>
       </c>
       <c r="B54" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C54">
         <v>3</v>
@@ -3490,7 +3604,7 @@
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3498,7 +3612,7 @@
         <v>63</v>
       </c>
       <c r="B55" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C55">
         <v>3</v>
@@ -3510,7 +3624,7 @@
         <v>2</v>
       </c>
       <c r="F55" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3620,7 +3734,7 @@
         <v>58</v>
       </c>
       <c r="B62" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C62">
         <v>3</v>
@@ -3632,7 +3746,7 @@
         <v>3</v>
       </c>
       <c r="F62" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3640,7 +3754,7 @@
         <v>91</v>
       </c>
       <c r="B63" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C63">
         <v>3</v>
@@ -3652,7 +3766,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3660,7 +3774,7 @@
         <v>93</v>
       </c>
       <c r="B64" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C64">
         <v>3</v>
@@ -3672,7 +3786,7 @@
         <v>2</v>
       </c>
       <c r="F64" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -3680,7 +3794,7 @@
         <v>94</v>
       </c>
       <c r="B65" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C65">
         <v>3</v>
@@ -3692,15 +3806,15 @@
         <v>2</v>
       </c>
       <c r="F65" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B66" t="s">
-        <v>256</v>
+        <v>89</v>
       </c>
       <c r="C66">
         <v>3</v>
@@ -3711,228 +3825,225 @@
       <c r="E66">
         <v>3</v>
       </c>
-      <c r="F66" t="s">
-        <v>215</v>
-      </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>95</v>
+      </c>
+      <c r="B67" t="s">
+        <v>254</v>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+      <c r="D67" t="s">
         <v>96</v>
       </c>
-      <c r="B67" t="s">
-        <v>256</v>
-      </c>
-      <c r="C67">
-        <v>3</v>
-      </c>
-      <c r="D67" t="s">
-        <v>97</v>
-      </c>
       <c r="E67">
         <v>1</v>
       </c>
       <c r="F67" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B68" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C68">
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E68">
         <v>1</v>
       </c>
       <c r="F68" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B69" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C69">
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E69">
         <v>2</v>
       </c>
       <c r="F69" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B70" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C70">
         <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E70">
         <v>2</v>
       </c>
       <c r="F70" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B71" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C71">
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E71">
         <v>3</v>
       </c>
       <c r="F71" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>101</v>
+      </c>
+      <c r="B72" t="s">
+        <v>254</v>
+      </c>
+      <c r="C72">
+        <v>3</v>
+      </c>
+      <c r="D72" t="s">
         <v>102</v>
       </c>
-      <c r="B72" t="s">
-        <v>256</v>
-      </c>
-      <c r="C72">
-        <v>3</v>
-      </c>
-      <c r="D72" t="s">
-        <v>103</v>
-      </c>
       <c r="E72">
         <v>1</v>
       </c>
       <c r="F72" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B73" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C73">
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E73">
         <v>1</v>
       </c>
       <c r="F73" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B74" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C74">
         <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E74">
         <v>2</v>
       </c>
       <c r="F74" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B75" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C75">
         <v>3</v>
       </c>
       <c r="D75" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E75">
         <v>2</v>
       </c>
       <c r="F75" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B76" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C76">
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E76">
         <v>3</v>
       </c>
       <c r="F76" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B77" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C77">
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E77">
         <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3940,7 +4051,7 @@
         <v>66</v>
       </c>
       <c r="B78" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C78">
         <v>2</v>
@@ -3952,7 +4063,7 @@
         <v>1</v>
       </c>
       <c r="F78" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3960,7 +4071,7 @@
         <v>68</v>
       </c>
       <c r="B79" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C79">
         <v>2</v>
@@ -3972,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3997,7 +4108,7 @@
         <v>69</v>
       </c>
       <c r="B81" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C81">
         <v>2</v>
@@ -4009,7 +4120,7 @@
         <v>3</v>
       </c>
       <c r="F81" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -4017,7 +4128,7 @@
         <v>70</v>
       </c>
       <c r="B82" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C82">
         <v>2</v>
@@ -4029,15 +4140,15 @@
         <v>3</v>
       </c>
       <c r="F82" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B83" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C83">
         <v>2</v>
@@ -4049,7 +4160,7 @@
         <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -4057,7 +4168,7 @@
         <v>71</v>
       </c>
       <c r="B84" t="s">
-        <v>256</v>
+        <v>645</v>
       </c>
       <c r="C84">
         <v>2</v>
@@ -4069,7 +4180,7 @@
         <v>1</v>
       </c>
       <c r="F84" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -4077,7 +4188,7 @@
         <v>73</v>
       </c>
       <c r="B85" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C85">
         <v>2</v>
@@ -4089,7 +4200,7 @@
         <v>2</v>
       </c>
       <c r="F85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -4097,7 +4208,7 @@
         <v>74</v>
       </c>
       <c r="B86" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C86">
         <v>2</v>
@@ -4109,7 +4220,7 @@
         <v>3</v>
       </c>
       <c r="F86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -4117,7 +4228,7 @@
         <v>75</v>
       </c>
       <c r="B87" t="s">
-        <v>256</v>
+        <v>646</v>
       </c>
       <c r="C87">
         <v>2</v>
@@ -4129,7 +4240,7 @@
         <v>1</v>
       </c>
       <c r="F87" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -4137,7 +4248,7 @@
         <v>77</v>
       </c>
       <c r="B88" t="s">
-        <v>256</v>
+        <v>646</v>
       </c>
       <c r="C88">
         <v>2</v>
@@ -4149,7 +4260,7 @@
         <v>1</v>
       </c>
       <c r="F88" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -4157,7 +4268,7 @@
         <v>78</v>
       </c>
       <c r="B89" t="s">
-        <v>256</v>
+        <v>654</v>
       </c>
       <c r="C89">
         <v>2</v>
@@ -4169,7 +4280,7 @@
         <v>2</v>
       </c>
       <c r="F89" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -4177,7 +4288,7 @@
         <v>79</v>
       </c>
       <c r="B90" t="s">
-        <v>256</v>
+        <v>652</v>
       </c>
       <c r="C90">
         <v>2</v>
@@ -4189,7 +4300,7 @@
         <v>2</v>
       </c>
       <c r="F90" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -4197,7 +4308,7 @@
         <v>80</v>
       </c>
       <c r="B91" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C91">
         <v>2</v>
@@ -4209,7 +4320,7 @@
         <v>3</v>
       </c>
       <c r="F91" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -4217,7 +4328,7 @@
         <v>81</v>
       </c>
       <c r="B92" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C92">
         <v>2</v>
@@ -4229,7 +4340,7 @@
         <v>3</v>
       </c>
       <c r="F92" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -4237,7 +4348,7 @@
         <v>82</v>
       </c>
       <c r="B93" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C93">
         <v>2</v>
@@ -4249,7 +4360,7 @@
         <v>1</v>
       </c>
       <c r="F93" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -4257,7 +4368,7 @@
         <v>84</v>
       </c>
       <c r="B94" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C94">
         <v>2</v>
@@ -4269,7 +4380,7 @@
         <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -4277,7 +4388,7 @@
         <v>85</v>
       </c>
       <c r="B95" t="s">
-        <v>256</v>
+        <v>675</v>
       </c>
       <c r="C95">
         <v>2</v>
@@ -4289,7 +4400,7 @@
         <v>2</v>
       </c>
       <c r="F95" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -4297,7 +4408,7 @@
         <v>86</v>
       </c>
       <c r="B96" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C96">
         <v>2</v>
@@ -4309,7 +4420,7 @@
         <v>2</v>
       </c>
       <c r="F96" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -4317,7 +4428,7 @@
         <v>87</v>
       </c>
       <c r="B97" t="s">
-        <v>256</v>
+        <v>652</v>
       </c>
       <c r="C97">
         <v>2</v>
@@ -4329,7 +4440,7 @@
         <v>3</v>
       </c>
       <c r="F97" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -4337,7 +4448,7 @@
         <v>88</v>
       </c>
       <c r="B98" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C98">
         <v>2</v>
@@ -4349,447 +4460,447 @@
         <v>3</v>
       </c>
       <c r="F98" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>108</v>
+      </c>
+      <c r="B99" t="s">
+        <v>254</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+      <c r="D99" t="s">
         <v>109</v>
       </c>
-      <c r="B99" t="s">
-        <v>256</v>
-      </c>
-      <c r="C99">
-        <v>2</v>
-      </c>
-      <c r="D99" t="s">
-        <v>110</v>
-      </c>
       <c r="E99">
         <v>1</v>
       </c>
       <c r="F99" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B100" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C100">
         <v>2</v>
       </c>
       <c r="D100" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E100">
         <v>2</v>
       </c>
       <c r="F100" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B101" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C101">
         <v>2</v>
       </c>
       <c r="D101" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E101">
         <v>3</v>
       </c>
       <c r="F101" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B102" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C102">
         <v>2</v>
       </c>
       <c r="D102" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E102">
         <v>3</v>
       </c>
       <c r="F102" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>113</v>
+      </c>
+      <c r="B103" t="s">
+        <v>254</v>
+      </c>
+      <c r="C103">
+        <v>2</v>
+      </c>
+      <c r="D103" t="s">
         <v>114</v>
       </c>
-      <c r="B103" t="s">
-        <v>256</v>
-      </c>
-      <c r="C103">
-        <v>2</v>
-      </c>
-      <c r="D103" t="s">
-        <v>115</v>
-      </c>
       <c r="E103">
         <v>1</v>
       </c>
       <c r="F103" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B104" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C104">
         <v>2</v>
       </c>
       <c r="D104" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E104">
         <v>2</v>
       </c>
       <c r="F104" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B105" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C105">
         <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E105">
         <v>2</v>
       </c>
       <c r="F105" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B106" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C106">
         <v>2</v>
       </c>
       <c r="D106" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E106">
         <v>3</v>
       </c>
       <c r="F106" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B107" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C107">
         <v>2</v>
       </c>
       <c r="D107" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E107">
         <v>3</v>
       </c>
       <c r="F107" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>119</v>
+      </c>
+      <c r="B108" t="s">
+        <v>254</v>
+      </c>
+      <c r="C108">
+        <v>2</v>
+      </c>
+      <c r="D108" t="s">
         <v>120</v>
       </c>
-      <c r="B108" t="s">
-        <v>256</v>
-      </c>
-      <c r="C108">
-        <v>2</v>
-      </c>
-      <c r="D108" t="s">
-        <v>121</v>
-      </c>
       <c r="E108">
         <v>1</v>
       </c>
       <c r="F108" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B109" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C109">
         <v>2</v>
       </c>
       <c r="D109" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E109">
         <v>2</v>
       </c>
       <c r="F109" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B110" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C110">
         <v>2</v>
       </c>
       <c r="D110" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E110">
         <v>3</v>
       </c>
       <c r="F110" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B111" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C111">
         <v>2</v>
       </c>
       <c r="D111" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E111">
         <v>3</v>
       </c>
       <c r="F111" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>124</v>
+      </c>
+      <c r="B112" t="s">
+        <v>646</v>
+      </c>
+      <c r="C112">
+        <v>2</v>
+      </c>
+      <c r="D112" t="s">
         <v>125</v>
       </c>
-      <c r="B112" t="s">
-        <v>256</v>
-      </c>
-      <c r="C112">
-        <v>2</v>
-      </c>
-      <c r="D112" t="s">
-        <v>126</v>
-      </c>
       <c r="E112">
         <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B113" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C113">
         <v>2</v>
       </c>
       <c r="D113" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E113">
         <v>2</v>
       </c>
       <c r="F113" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B114" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C114">
         <v>2</v>
       </c>
       <c r="D114" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E114">
         <v>3</v>
       </c>
       <c r="F114" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>129</v>
+      </c>
+      <c r="B115" t="s">
+        <v>254</v>
+      </c>
+      <c r="C115">
+        <v>2</v>
+      </c>
+      <c r="D115" t="s">
         <v>130</v>
       </c>
-      <c r="B115" t="s">
-        <v>256</v>
-      </c>
-      <c r="C115">
-        <v>2</v>
-      </c>
-      <c r="D115" t="s">
-        <v>131</v>
-      </c>
       <c r="E115">
         <v>1</v>
       </c>
       <c r="F115" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B116" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C116">
         <v>2</v>
       </c>
       <c r="D116" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E116">
         <v>1</v>
       </c>
       <c r="F116" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B117" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C117">
         <v>2</v>
       </c>
       <c r="D117" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E117">
         <v>2</v>
       </c>
       <c r="F117" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B118" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C118">
         <v>2</v>
       </c>
       <c r="D118" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E118">
         <v>2</v>
       </c>
       <c r="F118" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B119" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C119">
         <v>2</v>
       </c>
       <c r="D119" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E119">
         <v>3</v>
       </c>
       <c r="F119" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B120" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C120">
         <v>2</v>
       </c>
       <c r="D120" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E120">
         <v>3</v>
       </c>
       <c r="F120" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4803,7 +4914,7 @@
         <v>2</v>
       </c>
       <c r="D121" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E121">
         <v>1</v>
@@ -4820,7 +4931,7 @@
         <v>2</v>
       </c>
       <c r="D122" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E122">
         <v>2</v>
@@ -4837,7 +4948,7 @@
         <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E123">
         <v>3</v>
@@ -4854,7 +4965,7 @@
         <v>2</v>
       </c>
       <c r="D124" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E124">
         <v>1</v>
@@ -4871,7 +4982,7 @@
         <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E125">
         <v>2</v>
@@ -4879,22 +4990,22 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B126" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C126">
         <v>2</v>
       </c>
       <c r="D126" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E126">
         <v>3</v>
       </c>
       <c r="F126" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4908,7 +5019,7 @@
         <v>2</v>
       </c>
       <c r="D127" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E127">
         <v>1</v>
@@ -4925,7 +5036,7 @@
         <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -4942,7 +5053,7 @@
         <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E129">
         <v>3</v>
@@ -4950,10 +5061,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B130" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -4965,15 +5076,15 @@
         <v>1</v>
       </c>
       <c r="F130" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B131" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -4985,15 +5096,15 @@
         <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B132" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -5005,15 +5116,15 @@
         <v>1</v>
       </c>
       <c r="F132" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B133" t="s">
-        <v>256</v>
+        <v>654</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -5025,15 +5136,15 @@
         <v>2</v>
       </c>
       <c r="F133" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B134" t="s">
-        <v>256</v>
+        <v>696</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -5045,15 +5156,15 @@
         <v>2</v>
       </c>
       <c r="F134" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B135" t="s">
-        <v>256</v>
+        <v>695</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -5065,15 +5176,15 @@
         <v>2</v>
       </c>
       <c r="F135" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B136" t="s">
-        <v>256</v>
+        <v>697</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -5085,15 +5196,15 @@
         <v>3</v>
       </c>
       <c r="F136" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B137" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -5105,15 +5216,15 @@
         <v>3</v>
       </c>
       <c r="F137" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B138" t="s">
-        <v>256</v>
+        <v>690</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -5125,15 +5236,15 @@
         <v>4</v>
       </c>
       <c r="F138" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B139" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -5145,15 +5256,15 @@
         <v>4</v>
       </c>
       <c r="F139" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B140" t="s">
-        <v>256</v>
+        <v>698</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -5165,15 +5276,15 @@
         <v>4</v>
       </c>
       <c r="F140" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B141" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -5185,15 +5296,15 @@
         <v>4</v>
       </c>
       <c r="F141" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B142" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -5205,15 +5316,15 @@
         <v>1</v>
       </c>
       <c r="F142" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B143" t="s">
-        <v>256</v>
+        <v>686</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -5225,15 +5336,15 @@
         <v>1</v>
       </c>
       <c r="F143" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B144" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -5245,15 +5356,15 @@
         <v>1</v>
       </c>
       <c r="F144" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B145" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -5265,15 +5376,15 @@
         <v>1</v>
       </c>
       <c r="F145" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B146" t="s">
-        <v>256</v>
+        <v>679</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -5285,15 +5396,15 @@
         <v>2</v>
       </c>
       <c r="F146" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B147" t="s">
-        <v>256</v>
+        <v>656</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -5305,15 +5416,15 @@
         <v>2</v>
       </c>
       <c r="F147" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B148" t="s">
-        <v>256</v>
+        <v>691</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -5325,15 +5436,15 @@
         <v>3</v>
       </c>
       <c r="F148" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B149" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -5345,15 +5456,15 @@
         <v>3</v>
       </c>
       <c r="F149" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B150" t="s">
-        <v>256</v>
+        <v>649</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -5365,15 +5476,15 @@
         <v>4</v>
       </c>
       <c r="F150" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B151" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -5385,15 +5496,15 @@
         <v>4</v>
       </c>
       <c r="F151" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B152" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -5405,15 +5516,15 @@
         <v>4</v>
       </c>
       <c r="F152" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B153" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -5425,15 +5536,15 @@
         <v>1</v>
       </c>
       <c r="F153" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B154" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -5445,15 +5556,15 @@
         <v>2</v>
       </c>
       <c r="F154" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B155" t="s">
-        <v>256</v>
+        <v>680</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -5465,15 +5576,15 @@
         <v>2</v>
       </c>
       <c r="F155" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B156" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -5485,15 +5596,15 @@
         <v>2</v>
       </c>
       <c r="F156" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B157" t="s">
-        <v>256</v>
+        <v>665</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -5505,15 +5616,15 @@
         <v>3</v>
       </c>
       <c r="F157" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B158" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -5525,15 +5636,15 @@
         <v>3</v>
       </c>
       <c r="F158" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B159" t="s">
-        <v>256</v>
+        <v>686</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -5545,15 +5656,15 @@
         <v>3</v>
       </c>
       <c r="F159" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B160" t="s">
-        <v>256</v>
+        <v>646</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -5565,15 +5676,15 @@
         <v>4</v>
       </c>
       <c r="F160" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B161" t="s">
-        <v>256</v>
+        <v>654</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -5585,15 +5696,15 @@
         <v>4</v>
       </c>
       <c r="F161" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B162" t="s">
-        <v>256</v>
+        <v>654</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -5605,15 +5716,15 @@
         <v>4</v>
       </c>
       <c r="F162" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B163" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -5625,15 +5736,15 @@
         <v>4</v>
       </c>
       <c r="F163" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B164" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -5645,15 +5756,15 @@
         <v>1</v>
       </c>
       <c r="F164" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B165" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -5665,15 +5776,15 @@
         <v>1</v>
       </c>
       <c r="F165" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B166" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -5685,15 +5796,15 @@
         <v>1</v>
       </c>
       <c r="F166" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B167" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -5705,15 +5816,15 @@
         <v>1</v>
       </c>
       <c r="F167" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B168" t="s">
-        <v>256</v>
+        <v>652</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -5725,15 +5836,15 @@
         <v>2</v>
       </c>
       <c r="F168" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B169" t="s">
-        <v>256</v>
+        <v>668</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -5745,15 +5856,15 @@
         <v>2</v>
       </c>
       <c r="F169" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B170" t="s">
-        <v>256</v>
+        <v>646</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -5765,15 +5876,15 @@
         <v>3</v>
       </c>
       <c r="F170" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B171" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -5785,15 +5896,15 @@
         <v>3</v>
       </c>
       <c r="F171" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B172" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -5805,15 +5916,15 @@
         <v>3</v>
       </c>
       <c r="F172" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B173" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -5825,15 +5936,15 @@
         <v>4</v>
       </c>
       <c r="F173" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B174" t="s">
-        <v>256</v>
+        <v>658</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -5845,15 +5956,15 @@
         <v>4</v>
       </c>
       <c r="F174" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B175" t="s">
-        <v>256</v>
+        <v>654</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -5865,15 +5976,15 @@
         <v>4</v>
       </c>
       <c r="F175" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B176" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -5885,15 +5996,15 @@
         <v>4</v>
       </c>
       <c r="F176" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B177" t="s">
-        <v>256</v>
+        <v>658</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -5905,15 +6016,15 @@
         <v>1</v>
       </c>
       <c r="F177" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B178" t="s">
-        <v>256</v>
+        <v>665</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -5925,15 +6036,15 @@
         <v>1</v>
       </c>
       <c r="F178" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B179" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -5945,15 +6056,15 @@
         <v>2</v>
       </c>
       <c r="F179" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B180" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -5965,15 +6076,15 @@
         <v>2</v>
       </c>
       <c r="F180" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B181" t="s">
-        <v>256</v>
+        <v>646</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -5985,15 +6096,15 @@
         <v>2</v>
       </c>
       <c r="F181" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B182" t="s">
-        <v>256</v>
+        <v>647</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -6005,15 +6116,15 @@
         <v>3</v>
       </c>
       <c r="F182" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B183" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -6025,15 +6136,15 @@
         <v>3</v>
       </c>
       <c r="F183" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B184" t="s">
-        <v>256</v>
+        <v>680</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -6045,15 +6156,15 @@
         <v>3</v>
       </c>
       <c r="F184" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B185" t="s">
-        <v>256</v>
+        <v>654</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -6065,15 +6176,15 @@
         <v>3</v>
       </c>
       <c r="F185" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B186" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -6085,15 +6196,15 @@
         <v>4</v>
       </c>
       <c r="F186" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B187" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C187">
         <v>1</v>
@@ -6105,15 +6216,15 @@
         <v>4</v>
       </c>
       <c r="F187" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B188" t="s">
-        <v>256</v>
+        <v>681</v>
       </c>
       <c r="C188">
         <v>1</v>
@@ -6125,15 +6236,15 @@
         <v>4</v>
       </c>
       <c r="F188" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B189" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C189">
         <v>1</v>
@@ -6145,15 +6256,15 @@
         <v>1</v>
       </c>
       <c r="F189" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B190" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C190">
         <v>1</v>
@@ -6165,15 +6276,15 @@
         <v>1</v>
       </c>
       <c r="F190" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B191" t="s">
-        <v>256</v>
+        <v>679</v>
       </c>
       <c r="C191">
         <v>1</v>
@@ -6185,15 +6296,15 @@
         <v>1</v>
       </c>
       <c r="F191" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B192" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C192">
         <v>1</v>
@@ -6205,15 +6316,15 @@
         <v>2</v>
       </c>
       <c r="F192" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B193" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C193">
         <v>1</v>
@@ -6225,15 +6336,15 @@
         <v>2</v>
       </c>
       <c r="F193" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B194" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -6245,15 +6356,15 @@
         <v>2</v>
       </c>
       <c r="F194" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B195" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C195">
         <v>1</v>
@@ -6265,15 +6376,15 @@
         <v>3</v>
       </c>
       <c r="F195" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B196" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C196">
         <v>1</v>
@@ -6285,15 +6396,15 @@
         <v>3</v>
       </c>
       <c r="F196" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B197" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C197">
         <v>1</v>
@@ -6305,15 +6416,15 @@
         <v>3</v>
       </c>
       <c r="F197" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B198" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C198">
         <v>1</v>
@@ -6325,15 +6436,15 @@
         <v>4</v>
       </c>
       <c r="F198" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B199" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C199">
         <v>1</v>
@@ -6345,15 +6456,15 @@
         <v>4</v>
       </c>
       <c r="F199" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B200" t="s">
-        <v>256</v>
+        <v>661</v>
       </c>
       <c r="C200">
         <v>1</v>
@@ -6365,15 +6476,15 @@
         <v>1</v>
       </c>
       <c r="F200" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B201" t="s">
-        <v>256</v>
+        <v>661</v>
       </c>
       <c r="C201">
         <v>1</v>
@@ -6385,15 +6496,15 @@
         <v>1</v>
       </c>
       <c r="F201" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B202" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C202">
         <v>1</v>
@@ -6405,15 +6516,15 @@
         <v>1</v>
       </c>
       <c r="F202" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B203" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C203">
         <v>1</v>
@@ -6425,15 +6536,15 @@
         <v>2</v>
       </c>
       <c r="F203" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B204" t="s">
-        <v>256</v>
+        <v>669</v>
       </c>
       <c r="C204">
         <v>1</v>
@@ -6445,15 +6556,15 @@
         <v>2</v>
       </c>
       <c r="F204" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B205" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C205">
         <v>1</v>
@@ -6465,15 +6576,15 @@
         <v>2</v>
       </c>
       <c r="F205" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B206" t="s">
-        <v>256</v>
+        <v>678</v>
       </c>
       <c r="C206">
         <v>1</v>
@@ -6482,18 +6593,18 @@
         <v>40</v>
       </c>
       <c r="E206" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F206" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B207" t="s">
-        <v>256</v>
+        <v>677</v>
       </c>
       <c r="C207">
         <v>1</v>
@@ -6502,18 +6613,18 @@
         <v>40</v>
       </c>
       <c r="E207" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F207" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B208" t="s">
-        <v>256</v>
+        <v>676</v>
       </c>
       <c r="C208">
         <v>1</v>
@@ -6522,18 +6633,18 @@
         <v>40</v>
       </c>
       <c r="E208" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F208" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B209" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C209">
         <v>1</v>
@@ -6545,15 +6656,15 @@
         <v>1</v>
       </c>
       <c r="F209" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B210" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C210">
         <v>1</v>
@@ -6565,15 +6676,15 @@
         <v>1</v>
       </c>
       <c r="F210" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B211" t="s">
-        <v>256</v>
+        <v>649</v>
       </c>
       <c r="C211">
         <v>1</v>
@@ -6585,15 +6696,15 @@
         <v>1</v>
       </c>
       <c r="F211" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B212" t="s">
-        <v>256</v>
+        <v>674</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -6605,15 +6716,15 @@
         <v>2</v>
       </c>
       <c r="F212" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B213" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C213">
         <v>1</v>
@@ -6625,15 +6736,15 @@
         <v>2</v>
       </c>
       <c r="F213" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B214" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C214">
         <v>1</v>
@@ -6645,15 +6756,15 @@
         <v>2</v>
       </c>
       <c r="F214" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B215" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C215">
         <v>1</v>
@@ -6665,15 +6776,15 @@
         <v>3</v>
       </c>
       <c r="F215" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B216" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C216">
         <v>1</v>
@@ -6685,15 +6796,15 @@
         <v>3</v>
       </c>
       <c r="F216" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B217" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -6705,15 +6816,15 @@
         <v>3</v>
       </c>
       <c r="F217" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B218" t="s">
-        <v>256</v>
+        <v>649</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -6725,15 +6836,15 @@
         <v>4</v>
       </c>
       <c r="F218" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B219" t="s">
-        <v>256</v>
+        <v>646</v>
       </c>
       <c r="C219">
         <v>1</v>
@@ -6745,15 +6856,15 @@
         <v>4</v>
       </c>
       <c r="F219" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B220" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C220">
         <v>1</v>
@@ -6765,15 +6876,15 @@
         <v>4</v>
       </c>
       <c r="F220" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B221" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -6785,15 +6896,15 @@
         <v>1</v>
       </c>
       <c r="F221" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B222" t="s">
-        <v>256</v>
+        <v>667</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -6805,15 +6916,15 @@
         <v>1</v>
       </c>
       <c r="F222" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B223" t="s">
-        <v>256</v>
+        <v>667</v>
       </c>
       <c r="C223">
         <v>1</v>
@@ -6825,15 +6936,15 @@
         <v>1</v>
       </c>
       <c r="F223" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B224" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -6845,15 +6956,15 @@
         <v>1</v>
       </c>
       <c r="F224" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B225" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C225">
         <v>1</v>
@@ -6865,15 +6976,15 @@
         <v>2</v>
       </c>
       <c r="F225" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B226" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C226">
         <v>1</v>
@@ -6885,15 +6996,15 @@
         <v>2</v>
       </c>
       <c r="F226" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B227" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -6905,15 +7016,15 @@
         <v>2</v>
       </c>
       <c r="F227" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B228" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -6925,15 +7036,15 @@
         <v>3</v>
       </c>
       <c r="F228" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B229" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C229">
         <v>1</v>
@@ -6945,15 +7056,15 @@
         <v>3</v>
       </c>
       <c r="F229" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B230" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -6965,15 +7076,15 @@
         <v>4</v>
       </c>
       <c r="F230" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B231" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -6985,15 +7096,15 @@
         <v>4</v>
       </c>
       <c r="F231" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B232" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -7005,15 +7116,15 @@
         <v>4</v>
       </c>
       <c r="F232" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B233" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -7025,15 +7136,15 @@
         <v>1</v>
       </c>
       <c r="F233" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B234" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -7045,15 +7156,15 @@
         <v>1</v>
       </c>
       <c r="F234" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B235" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -7065,15 +7176,15 @@
         <v>1</v>
       </c>
       <c r="F235" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B236" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -7085,15 +7196,15 @@
         <v>1</v>
       </c>
       <c r="F236" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B237" t="s">
-        <v>256</v>
+        <v>658</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -7105,15 +7216,15 @@
         <v>2</v>
       </c>
       <c r="F237" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B238" t="s">
-        <v>256</v>
+        <v>660</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -7125,15 +7236,15 @@
         <v>2</v>
       </c>
       <c r="F238" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B239" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -7145,15 +7256,15 @@
         <v>2</v>
       </c>
       <c r="F239" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B240" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -7165,15 +7276,15 @@
         <v>2</v>
       </c>
       <c r="F240" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B241" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -7185,15 +7296,15 @@
         <v>3</v>
       </c>
       <c r="F241" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B242" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -7205,15 +7316,15 @@
         <v>3</v>
       </c>
       <c r="F242" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B243" t="s">
-        <v>256</v>
+        <v>669</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -7225,15 +7336,15 @@
         <v>3</v>
       </c>
       <c r="F243" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B244" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -7245,15 +7356,15 @@
         <v>3</v>
       </c>
       <c r="F244" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B245" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -7265,15 +7376,15 @@
         <v>3</v>
       </c>
       <c r="F245" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B246" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -7285,15 +7396,15 @@
         <v>3</v>
       </c>
       <c r="F246" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B247" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -7305,15 +7416,15 @@
         <v>4</v>
       </c>
       <c r="F247" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B248" t="s">
-        <v>256</v>
+        <v>670</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -7325,15 +7436,15 @@
         <v>4</v>
       </c>
       <c r="F248" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B249" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -7345,15 +7456,15 @@
         <v>1</v>
       </c>
       <c r="F249" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B250" t="s">
-        <v>256</v>
+        <v>665</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -7365,15 +7476,15 @@
         <v>1</v>
       </c>
       <c r="F250" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B251" t="s">
-        <v>256</v>
+        <v>664</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -7385,15 +7496,15 @@
         <v>1</v>
       </c>
       <c r="F251" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B252" t="s">
-        <v>256</v>
+        <v>668</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -7405,15 +7516,15 @@
         <v>2</v>
       </c>
       <c r="F252" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B253" t="s">
-        <v>256</v>
+        <v>667</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -7425,15 +7536,15 @@
         <v>2</v>
       </c>
       <c r="F253" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B254" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -7445,15 +7556,15 @@
         <v>2</v>
       </c>
       <c r="F254" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B255" t="s">
-        <v>256</v>
+        <v>646</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -7465,15 +7576,15 @@
         <v>2</v>
       </c>
       <c r="F255" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -7485,15 +7596,15 @@
         <v>3</v>
       </c>
       <c r="F256" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B257" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -7505,15 +7616,15 @@
         <v>3</v>
       </c>
       <c r="F257" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B258" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -7525,15 +7636,15 @@
         <v>3</v>
       </c>
       <c r="F258" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B259" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -7545,15 +7656,15 @@
         <v>3</v>
       </c>
       <c r="F259" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B260" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -7565,15 +7676,15 @@
         <v>4</v>
       </c>
       <c r="F260" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B261" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -7585,15 +7696,15 @@
         <v>4</v>
       </c>
       <c r="F261" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B262" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -7605,15 +7716,15 @@
         <v>4</v>
       </c>
       <c r="F262" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B263" t="s">
-        <v>256</v>
+        <v>665</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -7625,15 +7736,15 @@
         <v>4</v>
       </c>
       <c r="F263" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B264" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -7645,15 +7756,15 @@
         <v>1</v>
       </c>
       <c r="F264" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B265" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -7665,15 +7776,15 @@
         <v>1</v>
       </c>
       <c r="F265" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B266" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -7685,15 +7796,15 @@
         <v>1</v>
       </c>
       <c r="F266" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B267" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -7705,15 +7816,15 @@
         <v>2</v>
       </c>
       <c r="F267" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B268" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -7725,15 +7836,15 @@
         <v>2</v>
       </c>
       <c r="F268" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B269" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -7745,15 +7856,15 @@
         <v>2</v>
       </c>
       <c r="F269" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B270" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -7765,15 +7876,15 @@
         <v>3</v>
       </c>
       <c r="F270" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B271" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -7785,15 +7896,15 @@
         <v>3</v>
       </c>
       <c r="F271" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B272" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -7805,15 +7916,15 @@
         <v>3</v>
       </c>
       <c r="F272" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B273" t="s">
-        <v>256</v>
+        <v>664</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -7825,15 +7936,15 @@
         <v>4</v>
       </c>
       <c r="F273" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B274" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -7845,15 +7956,15 @@
         <v>4</v>
       </c>
       <c r="F274" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B275" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -7865,7 +7976,7 @@
         <v>1</v>
       </c>
       <c r="F275" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -7887,10 +7998,10 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B277" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -7902,15 +8013,15 @@
         <v>3</v>
       </c>
       <c r="F277" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B278" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -7922,15 +8033,15 @@
         <v>3</v>
       </c>
       <c r="F278" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B279" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C279">
         <v>1</v>
@@ -7942,15 +8053,15 @@
         <v>3</v>
       </c>
       <c r="F279" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B280" t="s">
-        <v>256</v>
+        <v>663</v>
       </c>
       <c r="C280">
         <v>1</v>
@@ -7962,15 +8073,15 @@
         <v>4</v>
       </c>
       <c r="F280" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B281" t="s">
-        <v>256</v>
+        <v>654</v>
       </c>
       <c r="C281">
         <v>1</v>
@@ -7982,15 +8093,15 @@
         <v>4</v>
       </c>
       <c r="F281" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B282" t="s">
-        <v>256</v>
+        <v>654</v>
       </c>
       <c r="C282">
         <v>1</v>
@@ -8002,15 +8113,15 @@
         <v>4</v>
       </c>
       <c r="F282" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B283" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C283">
         <v>1</v>
@@ -8022,15 +8133,15 @@
         <v>4</v>
       </c>
       <c r="F283" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B284" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C284">
         <v>1</v>
@@ -8042,15 +8153,15 @@
         <v>1</v>
       </c>
       <c r="F284" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B285" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C285">
         <v>1</v>
@@ -8062,15 +8173,15 @@
         <v>1</v>
       </c>
       <c r="F285" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C286">
         <v>1</v>
@@ -8082,15 +8193,15 @@
         <v>1</v>
       </c>
       <c r="F286" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B287" t="s">
-        <v>256</v>
+        <v>662</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -8102,15 +8213,15 @@
         <v>2</v>
       </c>
       <c r="F287" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C288">
         <v>1</v>
@@ -8122,15 +8233,15 @@
         <v>2</v>
       </c>
       <c r="F288" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B289" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C289">
         <v>1</v>
@@ -8142,15 +8253,15 @@
         <v>2</v>
       </c>
       <c r="F289" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B290" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -8162,15 +8273,15 @@
         <v>2</v>
       </c>
       <c r="F290" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C291">
         <v>1</v>
@@ -8182,15 +8293,15 @@
         <v>3</v>
       </c>
       <c r="F291" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B292" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C292">
         <v>1</v>
@@ -8202,15 +8313,15 @@
         <v>3</v>
       </c>
       <c r="F292" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B293" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -8222,15 +8333,15 @@
         <v>3</v>
       </c>
       <c r="F293" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B294" t="s">
-        <v>256</v>
+        <v>658</v>
       </c>
       <c r="C294">
         <v>1</v>
@@ -8242,15 +8353,15 @@
         <v>4</v>
       </c>
       <c r="F294" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B295" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C295">
         <v>1</v>
@@ -8262,15 +8373,15 @@
         <v>4</v>
       </c>
       <c r="F295" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B296" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C296">
         <v>1</v>
@@ -8282,15 +8393,15 @@
         <v>4</v>
       </c>
       <c r="F296" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B297" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C297">
         <v>1</v>
@@ -8302,15 +8413,15 @@
         <v>1</v>
       </c>
       <c r="F297" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B298" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C298">
         <v>1</v>
@@ -8322,15 +8433,15 @@
         <v>1</v>
       </c>
       <c r="F298" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B299" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C299">
         <v>1</v>
@@ -8342,15 +8453,15 @@
         <v>1</v>
       </c>
       <c r="F299" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B300" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C300">
         <v>1</v>
@@ -8362,15 +8473,15 @@
         <v>2</v>
       </c>
       <c r="F300" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B301" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C301">
         <v>1</v>
@@ -8382,15 +8493,15 @@
         <v>2</v>
       </c>
       <c r="F301" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B302" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C302">
         <v>1</v>
@@ -8402,15 +8513,15 @@
         <v>2</v>
       </c>
       <c r="F302" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B303" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C303">
         <v>1</v>
@@ -8422,15 +8533,15 @@
         <v>2</v>
       </c>
       <c r="F303" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B304" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C304">
         <v>1</v>
@@ -8442,15 +8553,15 @@
         <v>3</v>
       </c>
       <c r="F304" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B305" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C305">
         <v>1</v>
@@ -8462,15 +8573,15 @@
         <v>3</v>
       </c>
       <c r="F305" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B306" t="s">
-        <v>256</v>
+        <v>661</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -8482,15 +8593,15 @@
         <v>3</v>
       </c>
       <c r="F306" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B307" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C307">
         <v>1</v>
@@ -8502,15 +8613,15 @@
         <v>4</v>
       </c>
       <c r="F307" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B308" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C308">
         <v>1</v>
@@ -8522,15 +8633,15 @@
         <v>1</v>
       </c>
       <c r="F308" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B309" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -8542,15 +8653,15 @@
         <v>1</v>
       </c>
       <c r="F309" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B310" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C310">
         <v>1</v>
@@ -8562,15 +8673,15 @@
         <v>1</v>
       </c>
       <c r="F310" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B311" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C311">
         <v>1</v>
@@ -8582,15 +8693,15 @@
         <v>2</v>
       </c>
       <c r="F311" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B312" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C312">
         <v>1</v>
@@ -8602,15 +8713,15 @@
         <v>2</v>
       </c>
       <c r="F312" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B313" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -8622,15 +8733,15 @@
         <v>2</v>
       </c>
       <c r="F313" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B314" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C314">
         <v>1</v>
@@ -8642,15 +8753,15 @@
         <v>3</v>
       </c>
       <c r="F314" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B315" t="s">
-        <v>256</v>
+        <v>660</v>
       </c>
       <c r="C315">
         <v>1</v>
@@ -8662,15 +8773,15 @@
         <v>3</v>
       </c>
       <c r="F315" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B316" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -8682,15 +8793,15 @@
         <v>3</v>
       </c>
       <c r="F316" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B317" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -8702,15 +8813,15 @@
         <v>3</v>
       </c>
       <c r="F317" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B318" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -8722,15 +8833,15 @@
         <v>4</v>
       </c>
       <c r="F318" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B319" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -8742,15 +8853,15 @@
         <v>4</v>
       </c>
       <c r="F319" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B320" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -8762,7 +8873,7 @@
         <v>4</v>
       </c>
       <c r="F320" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>

--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\BECARIO PROCESOS\EOAT PROJECT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC522F30-779C-4B2D-942D-FAC4D34D0AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69439026-16AD-471E-902D-4DBF3AC5D20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$320</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$319</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="707">
   <si>
     <t>I-1937</t>
   </si>
@@ -1673,9 +1673,6 @@
     <t>I-1779.jpeg</t>
   </si>
   <si>
-    <t>I-1780.jpeg</t>
-  </si>
-  <si>
     <t>I-1782.jpeg</t>
   </si>
   <si>
@@ -1943,12 +1940,6 @@
     <t>I-1945</t>
   </si>
   <si>
-    <t>I-1566</t>
-  </si>
-  <si>
-    <t>I-1566.jpeg</t>
-  </si>
-  <si>
     <t>I-1581.jpeg</t>
   </si>
   <si>
@@ -2000,9 +1991,6 @@
     <t>4 ventosas</t>
   </si>
   <si>
-    <t>4 ventosas, 2 pinzas, 4 dedos</t>
-  </si>
-  <si>
     <t>2 pinzas</t>
   </si>
   <si>
@@ -2139,6 +2127,39 @@
   </si>
   <si>
     <t>3 dedos, 2 pinzas</t>
+  </si>
+  <si>
+    <t>I-1556</t>
+  </si>
+  <si>
+    <t>I-1556.jpeg</t>
+  </si>
+  <si>
+    <t>8 ventosas</t>
+  </si>
+  <si>
+    <t>8 pinzas</t>
+  </si>
+  <si>
+    <t>4 dedos, 1 pinza</t>
+  </si>
+  <si>
+    <t>2 dedos, 3 pinzas</t>
+  </si>
+  <si>
+    <t>12 pinzas, 2 dedos</t>
+  </si>
+  <si>
+    <t>6 ventosas, 2 pinzas</t>
+  </si>
+  <si>
+    <t>2 ventosas, 4 dedos, 2 pinzas (I-1782)</t>
+  </si>
+  <si>
+    <t>2 pinzas, 2 dedos</t>
+  </si>
+  <si>
+    <t>2 ventosas, 4 dedos, 2 pinzas (I-1780)</t>
   </si>
 </sst>
 </file>
@@ -2516,7 +2537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-  <dimension ref="A1:F320"/>
+  <dimension ref="A1:F319"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -2552,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -2572,7 +2593,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -2612,7 +2633,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -2632,7 +2653,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -2692,7 +2713,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -2712,7 +2733,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -2732,7 +2753,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -2752,7 +2773,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -2792,7 +2813,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -2812,7 +2833,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -2832,7 +2853,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -2852,7 +2873,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C17">
         <v>3</v>
@@ -2872,7 +2893,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C18">
         <v>3</v>
@@ -2892,7 +2913,7 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -2912,7 +2933,7 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C20">
         <v>3</v>
@@ -2932,7 +2953,7 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -2952,7 +2973,7 @@
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C22">
         <v>3</v>
@@ -2992,7 +3013,7 @@
         <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -3049,7 +3070,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B27" t="s">
         <v>254</v>
@@ -3064,12 +3085,12 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B28" t="s">
         <v>254</v>
@@ -3084,7 +3105,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -3112,7 +3133,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C30">
         <v>3</v>
@@ -3212,7 +3233,7 @@
         <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C35">
         <v>3</v>
@@ -3232,7 +3253,7 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="C36">
         <v>3</v>
@@ -3352,7 +3373,7 @@
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C42">
         <v>3</v>
@@ -3372,7 +3393,7 @@
         <v>47</v>
       </c>
       <c r="B43" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C43">
         <v>3</v>
@@ -3412,7 +3433,7 @@
         <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C45">
         <v>3</v>
@@ -3432,7 +3453,7 @@
         <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C46">
         <v>3</v>
@@ -3541,7 +3562,7 @@
         <v>56</v>
       </c>
       <c r="E51" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F51" t="s">
         <v>186</v>
@@ -3552,7 +3573,7 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -3561,7 +3582,7 @@
         <v>56</v>
       </c>
       <c r="E52" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F52" t="s">
         <v>188</v>
@@ -3871,7 +3892,7 @@
         <v>98</v>
       </c>
       <c r="B69" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C69">
         <v>3</v>
@@ -4145,7 +4166,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B83" t="s">
         <v>254</v>
@@ -4160,7 +4181,7 @@
         <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -4168,7 +4189,7 @@
         <v>71</v>
       </c>
       <c r="B84" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C84">
         <v>2</v>
@@ -4228,7 +4249,7 @@
         <v>75</v>
       </c>
       <c r="B87" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C87">
         <v>2</v>
@@ -4248,7 +4269,7 @@
         <v>77</v>
       </c>
       <c r="B88" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C88">
         <v>2</v>
@@ -4268,7 +4289,7 @@
         <v>78</v>
       </c>
       <c r="B89" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C89">
         <v>2</v>
@@ -4288,7 +4309,7 @@
         <v>79</v>
       </c>
       <c r="B90" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C90">
         <v>2</v>
@@ -4328,7 +4349,7 @@
         <v>81</v>
       </c>
       <c r="B92" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C92">
         <v>2</v>
@@ -4388,7 +4409,7 @@
         <v>85</v>
       </c>
       <c r="B95" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="C95">
         <v>2</v>
@@ -4408,7 +4429,7 @@
         <v>86</v>
       </c>
       <c r="B96" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C96">
         <v>2</v>
@@ -4428,7 +4449,7 @@
         <v>87</v>
       </c>
       <c r="B97" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C97">
         <v>2</v>
@@ -4728,7 +4749,7 @@
         <v>124</v>
       </c>
       <c r="B112" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C112">
         <v>2</v>
@@ -4888,7 +4909,7 @@
         <v>135</v>
       </c>
       <c r="B120" t="s">
-        <v>254</v>
+        <v>698</v>
       </c>
       <c r="C120">
         <v>2</v>
@@ -4990,7 +5011,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B126" t="s">
         <v>254</v>
@@ -5005,7 +5026,7 @@
         <v>3</v>
       </c>
       <c r="F126" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -5061,7 +5082,7 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B130" t="s">
         <v>254</v>
@@ -5076,7 +5097,7 @@
         <v>1</v>
       </c>
       <c r="F130" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -5096,7 +5117,7 @@
         <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -5116,7 +5137,7 @@
         <v>1</v>
       </c>
       <c r="F132" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -5124,7 +5145,7 @@
         <v>429</v>
       </c>
       <c r="B133" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -5136,7 +5157,7 @@
         <v>2</v>
       </c>
       <c r="F133" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -5144,7 +5165,7 @@
         <v>433</v>
       </c>
       <c r="B134" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -5156,7 +5177,7 @@
         <v>2</v>
       </c>
       <c r="F134" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -5164,7 +5185,7 @@
         <v>436</v>
       </c>
       <c r="B135" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -5176,7 +5197,7 @@
         <v>2</v>
       </c>
       <c r="F135" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -5184,7 +5205,7 @@
         <v>435</v>
       </c>
       <c r="B136" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -5196,7 +5217,7 @@
         <v>3</v>
       </c>
       <c r="F136" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -5216,7 +5237,7 @@
         <v>3</v>
       </c>
       <c r="F137" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -5224,7 +5245,7 @@
         <v>432</v>
       </c>
       <c r="B138" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -5236,7 +5257,7 @@
         <v>4</v>
       </c>
       <c r="F138" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -5244,7 +5265,7 @@
         <v>431</v>
       </c>
       <c r="B139" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -5256,7 +5277,7 @@
         <v>4</v>
       </c>
       <c r="F139" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -5264,7 +5285,7 @@
         <v>434</v>
       </c>
       <c r="B140" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -5276,15 +5297,15 @@
         <v>4</v>
       </c>
       <c r="F140" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B141" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -5296,12 +5317,12 @@
         <v>4</v>
       </c>
       <c r="F141" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B142" t="s">
         <v>254</v>
@@ -5316,7 +5337,7 @@
         <v>1</v>
       </c>
       <c r="F142" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -5324,7 +5345,7 @@
         <v>419</v>
       </c>
       <c r="B143" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -5336,7 +5357,7 @@
         <v>1</v>
       </c>
       <c r="F143" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -5356,7 +5377,7 @@
         <v>1</v>
       </c>
       <c r="F144" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -5376,7 +5397,7 @@
         <v>1</v>
       </c>
       <c r="F145" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -5384,7 +5405,7 @@
         <v>421</v>
       </c>
       <c r="B146" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -5396,7 +5417,7 @@
         <v>2</v>
       </c>
       <c r="F146" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -5404,7 +5425,7 @@
         <v>420</v>
       </c>
       <c r="B147" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -5416,7 +5437,7 @@
         <v>2</v>
       </c>
       <c r="F147" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -5424,7 +5445,7 @@
         <v>423</v>
       </c>
       <c r="B148" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -5436,7 +5457,7 @@
         <v>3</v>
       </c>
       <c r="F148" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -5456,7 +5477,7 @@
         <v>3</v>
       </c>
       <c r="F149" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -5464,7 +5485,7 @@
         <v>427</v>
       </c>
       <c r="B150" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -5476,7 +5497,7 @@
         <v>4</v>
       </c>
       <c r="F150" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -5496,7 +5517,7 @@
         <v>4</v>
       </c>
       <c r="F151" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -5504,7 +5525,7 @@
         <v>424</v>
       </c>
       <c r="B152" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -5516,7 +5537,7 @@
         <v>4</v>
       </c>
       <c r="F152" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -5524,7 +5545,7 @@
         <v>407</v>
       </c>
       <c r="B153" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -5536,7 +5557,7 @@
         <v>1</v>
       </c>
       <c r="F153" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -5556,7 +5577,7 @@
         <v>2</v>
       </c>
       <c r="F154" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5564,7 +5585,7 @@
         <v>408</v>
       </c>
       <c r="B155" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -5576,15 +5597,15 @@
         <v>2</v>
       </c>
       <c r="F155" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B156" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -5596,7 +5617,7 @@
         <v>2</v>
       </c>
       <c r="F156" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5604,7 +5625,7 @@
         <v>412</v>
       </c>
       <c r="B157" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -5616,7 +5637,7 @@
         <v>3</v>
       </c>
       <c r="F157" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5636,7 +5657,7 @@
         <v>3</v>
       </c>
       <c r="F158" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5644,7 +5665,7 @@
         <v>410</v>
       </c>
       <c r="B159" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -5656,7 +5677,7 @@
         <v>3</v>
       </c>
       <c r="F159" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5664,7 +5685,7 @@
         <v>416</v>
       </c>
       <c r="B160" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -5676,7 +5697,7 @@
         <v>4</v>
       </c>
       <c r="F160" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5684,7 +5705,7 @@
         <v>415</v>
       </c>
       <c r="B161" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -5696,7 +5717,7 @@
         <v>4</v>
       </c>
       <c r="F161" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5704,7 +5725,7 @@
         <v>414</v>
       </c>
       <c r="B162" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -5716,7 +5737,7 @@
         <v>4</v>
       </c>
       <c r="F162" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -5736,7 +5757,7 @@
         <v>4</v>
       </c>
       <c r="F163" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5744,7 +5765,7 @@
         <v>397</v>
       </c>
       <c r="B164" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -5756,7 +5777,7 @@
         <v>1</v>
       </c>
       <c r="F164" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5776,7 +5797,7 @@
         <v>1</v>
       </c>
       <c r="F165" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5784,7 +5805,7 @@
         <v>395</v>
       </c>
       <c r="B166" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -5796,7 +5817,7 @@
         <v>1</v>
       </c>
       <c r="F166" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5804,7 +5825,7 @@
         <v>394</v>
       </c>
       <c r="B167" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -5816,7 +5837,7 @@
         <v>1</v>
       </c>
       <c r="F167" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -5824,7 +5845,7 @@
         <v>400</v>
       </c>
       <c r="B168" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -5836,7 +5857,7 @@
         <v>2</v>
       </c>
       <c r="F168" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5844,7 +5865,7 @@
         <v>399</v>
       </c>
       <c r="B169" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -5856,7 +5877,7 @@
         <v>2</v>
       </c>
       <c r="F169" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5864,7 +5885,7 @@
         <v>402</v>
       </c>
       <c r="B170" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -5876,7 +5897,7 @@
         <v>3</v>
       </c>
       <c r="F170" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5884,7 +5905,7 @@
         <v>401</v>
       </c>
       <c r="B171" t="s">
-        <v>254</v>
+        <v>651</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -5896,7 +5917,7 @@
         <v>3</v>
       </c>
       <c r="F171" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5904,7 +5925,7 @@
         <v>398</v>
       </c>
       <c r="B172" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -5916,7 +5937,7 @@
         <v>3</v>
       </c>
       <c r="F172" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5936,7 +5957,7 @@
         <v>4</v>
       </c>
       <c r="F173" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5944,7 +5965,7 @@
         <v>405</v>
       </c>
       <c r="B174" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -5956,7 +5977,7 @@
         <v>4</v>
       </c>
       <c r="F174" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5964,7 +5985,7 @@
         <v>404</v>
       </c>
       <c r="B175" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -5976,7 +5997,7 @@
         <v>4</v>
       </c>
       <c r="F175" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5984,7 +6005,7 @@
         <v>403</v>
       </c>
       <c r="B176" t="s">
-        <v>254</v>
+        <v>705</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -5996,7 +6017,7 @@
         <v>4</v>
       </c>
       <c r="F176" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -6004,7 +6025,7 @@
         <v>383</v>
       </c>
       <c r="B177" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -6016,7 +6037,7 @@
         <v>1</v>
       </c>
       <c r="F177" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -6024,7 +6045,7 @@
         <v>382</v>
       </c>
       <c r="B178" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -6036,7 +6057,7 @@
         <v>1</v>
       </c>
       <c r="F178" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -6044,7 +6065,7 @@
         <v>386</v>
       </c>
       <c r="B179" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -6056,7 +6077,7 @@
         <v>2</v>
       </c>
       <c r="F179" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -6064,7 +6085,7 @@
         <v>385</v>
       </c>
       <c r="B180" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -6076,7 +6097,7 @@
         <v>2</v>
       </c>
       <c r="F180" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6084,7 +6105,7 @@
         <v>384</v>
       </c>
       <c r="B181" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -6096,7 +6117,7 @@
         <v>2</v>
       </c>
       <c r="F181" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -6104,7 +6125,7 @@
         <v>390</v>
       </c>
       <c r="B182" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -6116,7 +6137,7 @@
         <v>3</v>
       </c>
       <c r="F182" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -6124,7 +6145,7 @@
         <v>389</v>
       </c>
       <c r="B183" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -6136,7 +6157,7 @@
         <v>3</v>
       </c>
       <c r="F183" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6144,7 +6165,7 @@
         <v>388</v>
       </c>
       <c r="B184" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -6156,7 +6177,7 @@
         <v>3</v>
       </c>
       <c r="F184" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6164,7 +6185,7 @@
         <v>387</v>
       </c>
       <c r="B185" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -6176,7 +6197,7 @@
         <v>3</v>
       </c>
       <c r="F185" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6184,7 +6205,7 @@
         <v>393</v>
       </c>
       <c r="B186" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -6196,7 +6217,7 @@
         <v>4</v>
       </c>
       <c r="F186" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6204,7 +6225,7 @@
         <v>392</v>
       </c>
       <c r="B187" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C187">
         <v>1</v>
@@ -6216,7 +6237,7 @@
         <v>4</v>
       </c>
       <c r="F187" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6224,7 +6245,7 @@
         <v>391</v>
       </c>
       <c r="B188" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C188">
         <v>1</v>
@@ -6236,7 +6257,7 @@
         <v>4</v>
       </c>
       <c r="F188" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6244,7 +6265,7 @@
         <v>374</v>
       </c>
       <c r="B189" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C189">
         <v>1</v>
@@ -6264,7 +6285,7 @@
         <v>373</v>
       </c>
       <c r="B190" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C190">
         <v>1</v>
@@ -6284,7 +6305,7 @@
         <v>372</v>
       </c>
       <c r="B191" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C191">
         <v>1</v>
@@ -6304,7 +6325,7 @@
         <v>376</v>
       </c>
       <c r="B192" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C192">
         <v>1</v>
@@ -6324,7 +6345,7 @@
         <v>375</v>
       </c>
       <c r="B193" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C193">
         <v>1</v>
@@ -6341,7 +6362,7 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="B194" t="s">
         <v>254</v>
@@ -6356,7 +6377,7 @@
         <v>2</v>
       </c>
       <c r="F194" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -6364,7 +6385,7 @@
         <v>381</v>
       </c>
       <c r="B195" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C195">
         <v>1</v>
@@ -6376,7 +6397,7 @@
         <v>3</v>
       </c>
       <c r="F195" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -6384,7 +6405,7 @@
         <v>380</v>
       </c>
       <c r="B196" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C196">
         <v>1</v>
@@ -6396,7 +6417,7 @@
         <v>3</v>
       </c>
       <c r="F196" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -6404,7 +6425,7 @@
         <v>379</v>
       </c>
       <c r="B197" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C197">
         <v>1</v>
@@ -6416,7 +6437,7 @@
         <v>3</v>
       </c>
       <c r="F197" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -6424,7 +6445,7 @@
         <v>378</v>
       </c>
       <c r="B198" t="s">
-        <v>653</v>
+        <v>706</v>
       </c>
       <c r="C198">
         <v>1</v>
@@ -6436,7 +6457,7 @@
         <v>4</v>
       </c>
       <c r="F198" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6444,7 +6465,7 @@
         <v>377</v>
       </c>
       <c r="B199" t="s">
-        <v>254</v>
+        <v>704</v>
       </c>
       <c r="C199">
         <v>1</v>
@@ -6464,7 +6485,7 @@
         <v>365</v>
       </c>
       <c r="B200" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="C200">
         <v>1</v>
@@ -6484,7 +6505,7 @@
         <v>364</v>
       </c>
       <c r="B201" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="C201">
         <v>1</v>
@@ -6504,7 +6525,7 @@
         <v>363</v>
       </c>
       <c r="B202" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C202">
         <v>1</v>
@@ -6524,7 +6545,7 @@
         <v>368</v>
       </c>
       <c r="B203" t="s">
-        <v>254</v>
+        <v>703</v>
       </c>
       <c r="C203">
         <v>1</v>
@@ -6544,7 +6565,7 @@
         <v>367</v>
       </c>
       <c r="B204" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C204">
         <v>1</v>
@@ -6564,7 +6585,7 @@
         <v>366</v>
       </c>
       <c r="B205" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C205">
         <v>1</v>
@@ -6584,7 +6605,7 @@
         <v>371</v>
       </c>
       <c r="B206" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="C206">
         <v>1</v>
@@ -6593,7 +6614,7 @@
         <v>40</v>
       </c>
       <c r="E206" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F206" t="s">
         <v>538</v>
@@ -6604,7 +6625,7 @@
         <v>370</v>
       </c>
       <c r="B207" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="C207">
         <v>1</v>
@@ -6613,7 +6634,7 @@
         <v>40</v>
       </c>
       <c r="E207" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F207" t="s">
         <v>537</v>
@@ -6624,7 +6645,7 @@
         <v>369</v>
       </c>
       <c r="B208" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="C208">
         <v>1</v>
@@ -6633,7 +6654,7 @@
         <v>40</v>
       </c>
       <c r="E208" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F208" t="s">
         <v>536</v>
@@ -6644,7 +6665,7 @@
         <v>353</v>
       </c>
       <c r="B209" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C209">
         <v>1</v>
@@ -6664,7 +6685,7 @@
         <v>352</v>
       </c>
       <c r="B210" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C210">
         <v>1</v>
@@ -6684,7 +6705,7 @@
         <v>351</v>
       </c>
       <c r="B211" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C211">
         <v>1</v>
@@ -6704,7 +6725,7 @@
         <v>356</v>
       </c>
       <c r="B212" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -6724,7 +6745,7 @@
         <v>355</v>
       </c>
       <c r="B213" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C213">
         <v>1</v>
@@ -6744,7 +6765,7 @@
         <v>354</v>
       </c>
       <c r="B214" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C214">
         <v>1</v>
@@ -6764,7 +6785,7 @@
         <v>359</v>
       </c>
       <c r="B215" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C215">
         <v>1</v>
@@ -6784,7 +6805,7 @@
         <v>358</v>
       </c>
       <c r="B216" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C216">
         <v>1</v>
@@ -6804,7 +6825,7 @@
         <v>357</v>
       </c>
       <c r="B217" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -6824,7 +6845,7 @@
         <v>362</v>
       </c>
       <c r="B218" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -6844,7 +6865,7 @@
         <v>361</v>
       </c>
       <c r="B219" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C219">
         <v>1</v>
@@ -6864,7 +6885,7 @@
         <v>360</v>
       </c>
       <c r="B220" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C220">
         <v>1</v>
@@ -6884,7 +6905,7 @@
         <v>342</v>
       </c>
       <c r="B221" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -6904,7 +6925,7 @@
         <v>341</v>
       </c>
       <c r="B222" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -6924,7 +6945,7 @@
         <v>340</v>
       </c>
       <c r="B223" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C223">
         <v>1</v>
@@ -6944,7 +6965,7 @@
         <v>339</v>
       </c>
       <c r="B224" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -6964,7 +6985,7 @@
         <v>345</v>
       </c>
       <c r="B225" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C225">
         <v>1</v>
@@ -6984,7 +7005,7 @@
         <v>344</v>
       </c>
       <c r="B226" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C226">
         <v>1</v>
@@ -7004,7 +7025,7 @@
         <v>343</v>
       </c>
       <c r="B227" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -7024,7 +7045,7 @@
         <v>347</v>
       </c>
       <c r="B228" t="s">
-        <v>254</v>
+        <v>675</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -7044,7 +7065,7 @@
         <v>346</v>
       </c>
       <c r="B229" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C229">
         <v>1</v>
@@ -7064,7 +7085,7 @@
         <v>350</v>
       </c>
       <c r="B230" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -7084,7 +7105,7 @@
         <v>349</v>
       </c>
       <c r="B231" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -7104,7 +7125,7 @@
         <v>348</v>
       </c>
       <c r="B232" t="s">
-        <v>254</v>
+        <v>702</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -7124,7 +7145,7 @@
         <v>326</v>
       </c>
       <c r="B233" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -7144,7 +7165,7 @@
         <v>325</v>
       </c>
       <c r="B234" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -7164,7 +7185,7 @@
         <v>324</v>
       </c>
       <c r="B235" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -7184,7 +7205,7 @@
         <v>323</v>
       </c>
       <c r="B236" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -7204,7 +7225,7 @@
         <v>330</v>
       </c>
       <c r="B237" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -7224,7 +7245,7 @@
         <v>329</v>
       </c>
       <c r="B238" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -7244,7 +7265,7 @@
         <v>328</v>
       </c>
       <c r="B239" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -7264,7 +7285,7 @@
         <v>327</v>
       </c>
       <c r="B240" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -7284,7 +7305,7 @@
         <v>336</v>
       </c>
       <c r="B241" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -7304,7 +7325,7 @@
         <v>335</v>
       </c>
       <c r="B242" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -7324,7 +7345,7 @@
         <v>334</v>
       </c>
       <c r="B243" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -7344,7 +7365,7 @@
         <v>333</v>
       </c>
       <c r="B244" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -7364,7 +7385,7 @@
         <v>332</v>
       </c>
       <c r="B245" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -7384,7 +7405,7 @@
         <v>331</v>
       </c>
       <c r="B246" t="s">
-        <v>254</v>
+        <v>651</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -7404,7 +7425,7 @@
         <v>338</v>
       </c>
       <c r="B247" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -7424,7 +7445,7 @@
         <v>337</v>
       </c>
       <c r="B248" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -7444,7 +7465,7 @@
         <v>310</v>
       </c>
       <c r="B249" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -7464,7 +7485,7 @@
         <v>309</v>
       </c>
       <c r="B250" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -7484,7 +7505,7 @@
         <v>308</v>
       </c>
       <c r="B251" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -7504,7 +7525,7 @@
         <v>314</v>
       </c>
       <c r="B252" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -7524,7 +7545,7 @@
         <v>313</v>
       </c>
       <c r="B253" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -7544,7 +7565,7 @@
         <v>312</v>
       </c>
       <c r="B254" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -7564,7 +7585,7 @@
         <v>311</v>
       </c>
       <c r="B255" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -7584,7 +7605,7 @@
         <v>318</v>
       </c>
       <c r="B256" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -7604,7 +7625,7 @@
         <v>317</v>
       </c>
       <c r="B257" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -7624,7 +7645,7 @@
         <v>316</v>
       </c>
       <c r="B258" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -7644,7 +7665,7 @@
         <v>315</v>
       </c>
       <c r="B259" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -7664,7 +7685,7 @@
         <v>322</v>
       </c>
       <c r="B260" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -7684,7 +7705,7 @@
         <v>321</v>
       </c>
       <c r="B261" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -7704,7 +7725,7 @@
         <v>320</v>
       </c>
       <c r="B262" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -7724,7 +7745,7 @@
         <v>319</v>
       </c>
       <c r="B263" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -7744,7 +7765,7 @@
         <v>300</v>
       </c>
       <c r="B264" t="s">
-        <v>254</v>
+        <v>679</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -7764,7 +7785,7 @@
         <v>299</v>
       </c>
       <c r="B265" t="s">
-        <v>254</v>
+        <v>647</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -7784,7 +7805,7 @@
         <v>298</v>
       </c>
       <c r="B266" t="s">
-        <v>254</v>
+        <v>651</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -7804,7 +7825,7 @@
         <v>303</v>
       </c>
       <c r="B267" t="s">
-        <v>254</v>
+        <v>651</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -7824,7 +7845,7 @@
         <v>302</v>
       </c>
       <c r="B268" t="s">
-        <v>254</v>
+        <v>700</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -7844,7 +7865,7 @@
         <v>301</v>
       </c>
       <c r="B269" t="s">
-        <v>254</v>
+        <v>650</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -7861,7 +7882,7 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B270" t="s">
         <v>254</v>
@@ -7876,7 +7897,7 @@
         <v>3</v>
       </c>
       <c r="F270" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -7904,7 +7925,7 @@
         <v>304</v>
       </c>
       <c r="B272" t="s">
-        <v>254</v>
+        <v>651</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -7924,7 +7945,7 @@
         <v>307</v>
       </c>
       <c r="B273" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -7944,7 +7965,7 @@
         <v>306</v>
       </c>
       <c r="B274" t="s">
-        <v>254</v>
+        <v>663</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -7964,7 +7985,7 @@
         <v>292</v>
       </c>
       <c r="B275" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -7981,10 +8002,10 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>89</v>
+        <v>696</v>
       </c>
       <c r="B276" t="s">
-        <v>89</v>
+        <v>651</v>
       </c>
       <c r="C276">
         <v>1</v>
@@ -7994,6 +8015,9 @@
       </c>
       <c r="E276">
         <v>2</v>
+      </c>
+      <c r="F276" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -8001,7 +8025,7 @@
         <v>295</v>
       </c>
       <c r="B277" t="s">
-        <v>254</v>
+        <v>700</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -8021,7 +8045,7 @@
         <v>294</v>
       </c>
       <c r="B278" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -8041,7 +8065,7 @@
         <v>293</v>
       </c>
       <c r="B279" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C279">
         <v>1</v>
@@ -8061,7 +8085,7 @@
         <v>437</v>
       </c>
       <c r="B280" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="C280">
         <v>1</v>
@@ -8073,15 +8097,15 @@
         <v>4</v>
       </c>
       <c r="F280" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B281" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C281">
         <v>1</v>
@@ -8093,7 +8117,7 @@
         <v>4</v>
       </c>
       <c r="F281" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -8101,7 +8125,7 @@
         <v>297</v>
       </c>
       <c r="B282" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C282">
         <v>1</v>
@@ -8121,7 +8145,7 @@
         <v>296</v>
       </c>
       <c r="B283" t="s">
-        <v>254</v>
+        <v>701</v>
       </c>
       <c r="C283">
         <v>1</v>
@@ -8141,7 +8165,7 @@
         <v>286</v>
       </c>
       <c r="B284" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C284">
         <v>1</v>
@@ -8161,7 +8185,7 @@
         <v>285</v>
       </c>
       <c r="B285" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C285">
         <v>1</v>
@@ -8181,7 +8205,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C286">
         <v>1</v>
@@ -8201,7 +8225,7 @@
         <v>288</v>
       </c>
       <c r="B287" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -8221,7 +8245,7 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="C288">
         <v>1</v>
@@ -8238,10 +8262,10 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B289" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C289">
         <v>1</v>
@@ -8253,15 +8277,15 @@
         <v>2</v>
       </c>
       <c r="F289" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B290" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -8273,7 +8297,7 @@
         <v>2</v>
       </c>
       <c r="F290" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8281,7 +8305,7 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C291">
         <v>1</v>
@@ -8301,7 +8325,7 @@
         <v>289</v>
       </c>
       <c r="B292" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C292">
         <v>1</v>
@@ -8318,10 +8342,10 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B293" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -8333,7 +8357,7 @@
         <v>3</v>
       </c>
       <c r="F293" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8341,7 +8365,7 @@
         <v>291</v>
       </c>
       <c r="B294" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="C294">
         <v>1</v>
@@ -8358,10 +8382,10 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B295" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C295">
         <v>1</v>
@@ -8373,7 +8397,7 @@
         <v>4</v>
       </c>
       <c r="F295" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8381,7 +8405,7 @@
         <v>283</v>
       </c>
       <c r="B296" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C296">
         <v>1</v>
@@ -8401,7 +8425,7 @@
         <v>276</v>
       </c>
       <c r="B297" t="s">
-        <v>254</v>
+        <v>699</v>
       </c>
       <c r="C297">
         <v>1</v>
@@ -8418,10 +8442,10 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B298" t="s">
-        <v>254</v>
+        <v>652</v>
       </c>
       <c r="C298">
         <v>1</v>
@@ -8433,7 +8457,7 @@
         <v>1</v>
       </c>
       <c r="F298" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8441,7 +8465,7 @@
         <v>275</v>
       </c>
       <c r="B299" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C299">
         <v>1</v>
@@ -8458,10 +8482,10 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>634</v>
+        <v>279</v>
       </c>
       <c r="B300" t="s">
-        <v>254</v>
+        <v>651</v>
       </c>
       <c r="C300">
         <v>1</v>
@@ -8473,15 +8497,15 @@
         <v>2</v>
       </c>
       <c r="F300" t="s">
-        <v>635</v>
+        <v>446</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B301" t="s">
-        <v>254</v>
+        <v>663</v>
       </c>
       <c r="C301">
         <v>1</v>
@@ -8493,15 +8517,15 @@
         <v>2</v>
       </c>
       <c r="F301" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B302" t="s">
-        <v>254</v>
+        <v>650</v>
       </c>
       <c r="C302">
         <v>1</v>
@@ -8513,15 +8537,15 @@
         <v>2</v>
       </c>
       <c r="F302" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B303" t="s">
-        <v>254</v>
+        <v>654</v>
       </c>
       <c r="C303">
         <v>1</v>
@@ -8530,15 +8554,15 @@
         <v>76</v>
       </c>
       <c r="E303">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F303" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B304" t="s">
         <v>254</v>
@@ -8553,15 +8577,15 @@
         <v>3</v>
       </c>
       <c r="F304" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B305" t="s">
-        <v>254</v>
+        <v>657</v>
       </c>
       <c r="C305">
         <v>1</v>
@@ -8573,15 +8597,15 @@
         <v>3</v>
       </c>
       <c r="F305" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>280</v>
+        <v>128</v>
       </c>
       <c r="B306" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -8590,38 +8614,38 @@
         <v>76</v>
       </c>
       <c r="E306">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F306" t="s">
-        <v>447</v>
+        <v>241</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>128</v>
+        <v>258</v>
       </c>
       <c r="B307" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C307">
         <v>1</v>
       </c>
       <c r="D307" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E307">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F307" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B308" t="s">
-        <v>254</v>
+        <v>651</v>
       </c>
       <c r="C308">
         <v>1</v>
@@ -8633,15 +8657,15 @@
         <v>1</v>
       </c>
       <c r="F308" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B309" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -8653,15 +8677,15 @@
         <v>1</v>
       </c>
       <c r="F309" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B310" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C310">
         <v>1</v>
@@ -8670,18 +8694,18 @@
         <v>83</v>
       </c>
       <c r="E310">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F310" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B311" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C311">
         <v>1</v>
@@ -8693,15 +8717,15 @@
         <v>2</v>
       </c>
       <c r="F311" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B312" t="s">
-        <v>254</v>
+        <v>649</v>
       </c>
       <c r="C312">
         <v>1</v>
@@ -8713,15 +8737,15 @@
         <v>2</v>
       </c>
       <c r="F312" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B313" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -8730,18 +8754,18 @@
         <v>83</v>
       </c>
       <c r="E313">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F313" t="s">
-        <v>266</v>
+        <v>438</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>271</v>
+        <v>616</v>
       </c>
       <c r="B314" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C314">
         <v>1</v>
@@ -8753,15 +8777,15 @@
         <v>3</v>
       </c>
       <c r="F314" t="s">
-        <v>438</v>
+        <v>624</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>617</v>
+        <v>263</v>
       </c>
       <c r="B315" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="C315">
         <v>1</v>
@@ -8773,15 +8797,15 @@
         <v>3</v>
       </c>
       <c r="F315" t="s">
-        <v>625</v>
+        <v>270</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B316" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -8793,12 +8817,12 @@
         <v>3</v>
       </c>
       <c r="F316" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B317" t="s">
         <v>655</v>
@@ -8810,18 +8834,18 @@
         <v>83</v>
       </c>
       <c r="E317">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F317" t="s">
-        <v>269</v>
+        <v>441</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B318" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -8833,15 +8857,15 @@
         <v>4</v>
       </c>
       <c r="F318" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B319" t="s">
-        <v>659</v>
+        <v>645</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -8853,43 +8877,23 @@
         <v>4</v>
       </c>
       <c r="F319" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A320" t="s">
-        <v>272</v>
-      </c>
-      <c r="B320" t="s">
-        <v>648</v>
-      </c>
-      <c r="C320">
-        <v>1</v>
-      </c>
-      <c r="D320" t="s">
-        <v>83</v>
-      </c>
-      <c r="E320">
-        <v>4</v>
-      </c>
-      <c r="F320" t="s">
         <v>439</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F320" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F320">
-      <sortCondition descending="1" ref="C2:C320"/>
-      <sortCondition ref="D2:D320"/>
-      <sortCondition ref="E2:E320"/>
-      <sortCondition descending="1" ref="A2:A320"/>
+  <autoFilter ref="A1:F319" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F319">
+      <sortCondition descending="1" ref="C2:C319"/>
+      <sortCondition ref="D2:D319"/>
+      <sortCondition ref="E2:E319"/>
+      <sortCondition descending="1" ref="A2:A319"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F319">
-    <sortCondition descending="1" ref="C2:C319"/>
-    <sortCondition ref="D2:D319"/>
-    <sortCondition ref="E2:E319"/>
-    <sortCondition descending="1" ref="A2:A319"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F318">
+    <sortCondition descending="1" ref="C2:C318"/>
+    <sortCondition ref="D2:D318"/>
+    <sortCondition ref="E2:E318"/>
+    <sortCondition descending="1" ref="A2:A318"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\BECARIO PROCESOS\EOAT PROJECT\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69439026-16AD-471E-902D-4DBF3AC5D20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3900B35B-5EF8-43E7-90E9-E735DBA75242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$319</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$313</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1241" uniqueCount="716">
   <si>
     <t>I-1937</t>
   </si>
@@ -137,15 +137,9 @@
     <t>I-1720</t>
   </si>
   <si>
-    <t>I-1799</t>
-  </si>
-  <si>
     <t>C06</t>
   </si>
   <si>
-    <t>I-1798</t>
-  </si>
-  <si>
     <t>I-1788</t>
   </si>
   <si>
@@ -239,9 +233,6 @@
     <t>C12</t>
   </si>
   <si>
-    <t>I-1595</t>
-  </si>
-  <si>
     <t>C13</t>
   </si>
   <si>
@@ -353,9 +344,6 @@
     <t>I-1901</t>
   </si>
   <si>
-    <t>I-1797</t>
-  </si>
-  <si>
     <t>I-1501</t>
   </si>
   <si>
@@ -365,9 +353,6 @@
     <t>I-1706</t>
   </si>
   <si>
-    <t>I-1571</t>
-  </si>
-  <si>
     <t>C21</t>
   </si>
   <si>
@@ -437,9 +422,6 @@
     <t>I-1688</t>
   </si>
   <si>
-    <t>I-1466</t>
-  </si>
-  <si>
     <t>I-1429</t>
   </si>
   <si>
@@ -539,12 +521,6 @@
     <t>I-1720.jpeg</t>
   </si>
   <si>
-    <t>I-1799.jpeg</t>
-  </si>
-  <si>
-    <t>I-1798.jpeg</t>
-  </si>
-  <si>
     <t>I-1788.jpeg</t>
   </si>
   <si>
@@ -617,9 +593,6 @@
     <t>I-1553.jpeg</t>
   </si>
   <si>
-    <t>I-1595.jpeg</t>
-  </si>
-  <si>
     <t>I-1593.jpeg</t>
   </si>
   <si>
@@ -704,9 +677,6 @@
     <t>I-1901.jpeg</t>
   </si>
   <si>
-    <t>I-1797.jpeg</t>
-  </si>
-  <si>
     <t>I-1501.jpeg</t>
   </si>
   <si>
@@ -716,9 +686,6 @@
     <t>I-1706.jpeg</t>
   </si>
   <si>
-    <t>I-1571.jpeg</t>
-  </si>
-  <si>
     <t>I-1552.jpeg</t>
   </si>
   <si>
@@ -773,9 +740,6 @@
     <t>I-1688.jpeg</t>
   </si>
   <si>
-    <t>I-1466.jpeg</t>
-  </si>
-  <si>
     <t>I-1429.jpeg</t>
   </si>
   <si>
@@ -1859,15 +1823,9 @@
     <t>I-1612.jpeg</t>
   </si>
   <si>
-    <t>I-1565</t>
-  </si>
-  <si>
     <t>I-1699</t>
   </si>
   <si>
-    <t>I-1565.jpeg</t>
-  </si>
-  <si>
     <t>I-1699.jpeg</t>
   </si>
   <si>
@@ -1946,12 +1904,6 @@
     <t>I-1581</t>
   </si>
   <si>
-    <t>I-1774</t>
-  </si>
-  <si>
-    <t>I-1774.jpeg</t>
-  </si>
-  <si>
     <t>I-1930</t>
   </si>
   <si>
@@ -2153,13 +2105,88 @@
     <t>6 ventosas, 2 pinzas</t>
   </si>
   <si>
-    <t>2 ventosas, 4 dedos, 2 pinzas (I-1782)</t>
-  </si>
-  <si>
     <t>2 pinzas, 2 dedos</t>
   </si>
   <si>
-    <t>2 ventosas, 4 dedos, 2 pinzas (I-1780)</t>
+    <t>I-1780.jpeg</t>
+  </si>
+  <si>
+    <t>2 ventosas, 4 dedos, 2 pinzas</t>
+  </si>
+  <si>
+    <t>13 ventosas</t>
+  </si>
+  <si>
+    <t>3 pinzas, 2 ventosas</t>
+  </si>
+  <si>
+    <t>3 pinzas, 1 dedo</t>
+  </si>
+  <si>
+    <t>6 pinzas, 4 ventosas</t>
+  </si>
+  <si>
+    <t>10 pinzas de goma, 8 pinzas, 2 dedos</t>
+  </si>
+  <si>
+    <t>2 ventosas, 5 dedos, 8 pinzas</t>
+  </si>
+  <si>
+    <t>10 pinzas, 2 ventosas</t>
+  </si>
+  <si>
+    <t>7 dedos, 4 pinzas</t>
+  </si>
+  <si>
+    <t>6 ventosas, 4 dedos, 6 pinzas</t>
+  </si>
+  <si>
+    <t>5 ventosas con pistones, 1 dedo</t>
+  </si>
+  <si>
+    <t>7 dedos, 2 ventosas</t>
+  </si>
+  <si>
+    <t>4 ventosas con pistones</t>
+  </si>
+  <si>
+    <t>8 pistones pinza, 8 pinzas</t>
+  </si>
+  <si>
+    <t>4 pistones</t>
+  </si>
+  <si>
+    <t>4 ventosas, 2 dedos</t>
+  </si>
+  <si>
+    <t>5 dedos, 2 pinzas</t>
+  </si>
+  <si>
+    <t>4 pinzas, 2 dedos</t>
+  </si>
+  <si>
+    <t>6 dedos, 2 pinzas, 2 pernos guías</t>
+  </si>
+  <si>
+    <t>5 pinzas, 2 dedos</t>
+  </si>
+  <si>
+    <t>2 dedos GFR20, 3 dedos de abrazadera ancha, 2 ventosas</t>
+  </si>
+  <si>
+    <t>6 dedos</t>
+  </si>
+  <si>
+    <t>3 ventosas</t>
+  </si>
+  <si>
+    <t>4 dedos, 2 ventosas</t>
+  </si>
+  <si>
+    <t>4 ventosas, 4 dedos, 1 pinza</t>
+  </si>
+  <si>
+    <t>4 ventosas, 2 pinzas, 4 dedos</t>
   </si>
 </sst>
 </file>
@@ -2537,7 +2564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-  <dimension ref="A1:F319"/>
+  <dimension ref="A1:F313"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -2550,22 +2577,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="B1" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="E1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="F1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2573,7 +2600,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>695</v>
+        <v>679</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -2585,7 +2612,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2593,7 +2620,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>690</v>
+        <v>674</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -2605,7 +2632,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2613,7 +2640,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>254</v>
+        <v>691</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -2625,7 +2652,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2633,7 +2660,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>689</v>
+        <v>673</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -2645,7 +2672,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2653,7 +2680,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -2665,7 +2692,7 @@
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2673,7 +2700,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -2685,7 +2712,7 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2693,7 +2720,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>254</v>
+        <v>628</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -2705,7 +2732,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2713,7 +2740,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>688</v>
+        <v>672</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -2725,7 +2752,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2733,7 +2760,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>686</v>
+        <v>670</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -2745,7 +2772,7 @@
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2753,7 +2780,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>685</v>
+        <v>669</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -2765,7 +2792,7 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2773,7 +2800,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -2785,7 +2812,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2793,7 +2820,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -2805,7 +2832,7 @@
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2813,7 +2840,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -2825,7 +2852,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2833,7 +2860,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -2845,7 +2872,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2853,7 +2880,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>642</v>
+        <v>626</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -2865,7 +2892,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2873,7 +2900,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>681</v>
+        <v>665</v>
       </c>
       <c r="C17">
         <v>3</v>
@@ -2885,7 +2912,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2893,7 +2920,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
       <c r="C18">
         <v>3</v>
@@ -2905,7 +2932,7 @@
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2913,7 +2940,7 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>663</v>
+        <v>647</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -2925,7 +2952,7 @@
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2933,7 +2960,7 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="C20">
         <v>3</v>
@@ -2945,7 +2972,7 @@
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2953,7 +2980,7 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -2965,7 +2992,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2973,7 +3000,7 @@
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
       <c r="C22">
         <v>3</v>
@@ -2985,7 +3012,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2993,7 +3020,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>254</v>
+        <v>628</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -3005,7 +3032,7 @@
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -3013,7 +3040,7 @@
         <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>641</v>
+        <v>625</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -3025,7 +3052,7 @@
         <v>2</v>
       </c>
       <c r="F24" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -3033,7 +3060,7 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>254</v>
+        <v>692</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -3045,7 +3072,7 @@
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -3053,7 +3080,7 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>254</v>
+        <v>646</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -3065,15 +3092,15 @@
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
       <c r="B27" t="s">
-        <v>254</v>
+        <v>693</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -3085,15 +3112,15 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>609</v>
+        <v>595</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>606</v>
+        <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>254</v>
+        <v>627</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -3102,18 +3129,18 @@
         <v>29</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>608</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>254</v>
+        <v>653</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -3122,50 +3149,47 @@
         <v>29</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
-        <v>669</v>
+        <v>86</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E30">
-        <v>3</v>
-      </c>
-      <c r="F30" t="s">
-        <v>165</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>694</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31" t="s">
         <v>32</v>
       </c>
-      <c r="B31" t="s">
-        <v>254</v>
-      </c>
-      <c r="C31">
-        <v>3</v>
-      </c>
-      <c r="D31" t="s">
-        <v>33</v>
-      </c>
       <c r="E31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -3173,19 +3197,19 @@
         <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>254</v>
+        <v>695</v>
       </c>
       <c r="C32">
         <v>3</v>
       </c>
       <c r="D32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -3193,19 +3217,19 @@
         <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>254</v>
+        <v>652</v>
       </c>
       <c r="C33">
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -3213,19 +3237,19 @@
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>254</v>
+        <v>651</v>
       </c>
       <c r="C34">
         <v>3</v>
       </c>
       <c r="D34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -3233,59 +3257,59 @@
         <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>668</v>
+        <v>651</v>
       </c>
       <c r="C35">
         <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" t="s">
+        <v>242</v>
+      </c>
+      <c r="C36">
+        <v>3</v>
+      </c>
+      <c r="D36" t="s">
         <v>38</v>
       </c>
-      <c r="B36" t="s">
-        <v>667</v>
-      </c>
-      <c r="C36">
-        <v>3</v>
-      </c>
-      <c r="D36" t="s">
-        <v>33</v>
-      </c>
       <c r="E36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>254</v>
+        <v>696</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3293,19 +3317,19 @@
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C38">
         <v>3</v>
       </c>
       <c r="D38" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3313,19 +3337,19 @@
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>254</v>
+        <v>697</v>
       </c>
       <c r="C39">
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3333,59 +3357,59 @@
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>254</v>
+        <v>631</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" t="s">
+        <v>630</v>
+      </c>
+      <c r="C41">
+        <v>3</v>
+      </c>
+      <c r="D41" t="s">
         <v>44</v>
       </c>
-      <c r="B41" t="s">
-        <v>254</v>
-      </c>
-      <c r="C41">
-        <v>3</v>
-      </c>
-      <c r="D41" t="s">
-        <v>40</v>
-      </c>
       <c r="E41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>647</v>
+        <v>698</v>
       </c>
       <c r="C42">
         <v>3</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -3399,13 +3423,13 @@
         <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F43" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -3413,19 +3437,19 @@
         <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>254</v>
+        <v>626</v>
       </c>
       <c r="C44">
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -3433,59 +3457,59 @@
         <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>662</v>
+        <v>242</v>
       </c>
       <c r="C45">
         <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46" t="s">
+        <v>699</v>
+      </c>
+      <c r="C46">
+        <v>3</v>
+      </c>
+      <c r="D46" t="s">
         <v>50</v>
       </c>
-      <c r="B46" t="s">
-        <v>642</v>
-      </c>
-      <c r="C46">
-        <v>3</v>
-      </c>
-      <c r="D46" t="s">
-        <v>46</v>
-      </c>
       <c r="E46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C47">
         <v>3</v>
       </c>
       <c r="D47" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F47" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3493,119 +3517,119 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>254</v>
+        <v>663</v>
       </c>
       <c r="C48">
         <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" t="s">
+        <v>242</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
+      <c r="D49" t="s">
         <v>54</v>
       </c>
-      <c r="B49" t="s">
-        <v>254</v>
-      </c>
-      <c r="C49">
-        <v>3</v>
-      </c>
-      <c r="D49" t="s">
-        <v>52</v>
-      </c>
-      <c r="E49">
-        <v>3</v>
+      <c r="E49" t="s">
+        <v>613</v>
       </c>
       <c r="F49" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>254</v>
+        <v>614</v>
       </c>
       <c r="C50">
         <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>56</v>
-      </c>
-      <c r="E50">
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="E50" t="s">
+        <v>613</v>
       </c>
       <c r="F50" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>254</v>
+        <v>700</v>
       </c>
       <c r="C51">
         <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>56</v>
-      </c>
-      <c r="E51" t="s">
-        <v>627</v>
+        <v>59</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" t="s">
+        <v>633</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+      <c r="D52" t="s">
         <v>59</v>
       </c>
-      <c r="B52" t="s">
-        <v>628</v>
-      </c>
-      <c r="C52">
-        <v>3</v>
-      </c>
-      <c r="D52" t="s">
-        <v>56</v>
-      </c>
-      <c r="E52" t="s">
-        <v>627</v>
+      <c r="E52">
+        <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B53" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C53">
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3613,161 +3637,161 @@
         <v>62</v>
       </c>
       <c r="B54" t="s">
-        <v>254</v>
+        <v>62</v>
       </c>
       <c r="C54">
         <v>3</v>
       </c>
       <c r="D54" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E54">
-        <v>1</v>
-      </c>
-      <c r="F54" t="s">
-        <v>190</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55" t="s">
         <v>63</v>
       </c>
-      <c r="B55" t="s">
-        <v>254</v>
-      </c>
-      <c r="C55">
-        <v>3</v>
-      </c>
-      <c r="D55" t="s">
-        <v>61</v>
-      </c>
       <c r="E55">
-        <v>2</v>
-      </c>
-      <c r="F55" t="s">
-        <v>191</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C56">
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E56">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C57">
         <v>3</v>
       </c>
       <c r="D57" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="B58" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="C58">
         <v>3</v>
       </c>
       <c r="D58" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="B59" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="C59">
         <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="B60" t="s">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="C60">
         <v>3</v>
       </c>
       <c r="D60" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F60" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>88</v>
+      </c>
+      <c r="B61" t="s">
+        <v>242</v>
+      </c>
+      <c r="C61">
+        <v>3</v>
+      </c>
+      <c r="D61" t="s">
         <v>89</v>
       </c>
-      <c r="B61" t="s">
-        <v>89</v>
-      </c>
-      <c r="C61">
-        <v>3</v>
-      </c>
-      <c r="D61" t="s">
-        <v>90</v>
-      </c>
       <c r="E61">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F61" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="B62" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C62">
         <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F62" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3775,76 +3799,76 @@
         <v>91</v>
       </c>
       <c r="B63" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C63">
         <v>3</v>
       </c>
       <c r="D63" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B64" t="s">
-        <v>254</v>
+        <v>86</v>
       </c>
       <c r="C64">
         <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E64">
-        <v>2</v>
-      </c>
-      <c r="F64" t="s">
-        <v>212</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B65" t="s">
-        <v>254</v>
+        <v>701</v>
       </c>
       <c r="C65">
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B66" t="s">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="C66">
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E66">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F66" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -3852,79 +3876,79 @@
         <v>95</v>
       </c>
       <c r="B67" t="s">
-        <v>254</v>
+        <v>632</v>
       </c>
       <c r="C67">
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B68" t="s">
-        <v>254</v>
+        <v>702</v>
       </c>
       <c r="C68">
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B69" t="s">
-        <v>648</v>
+        <v>242</v>
       </c>
       <c r="C69">
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F69" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>98</v>
+      </c>
+      <c r="B70" t="s">
+        <v>703</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="D70" t="s">
         <v>99</v>
       </c>
-      <c r="B70" t="s">
-        <v>254</v>
-      </c>
-      <c r="C70">
-        <v>3</v>
-      </c>
-      <c r="D70" t="s">
-        <v>96</v>
-      </c>
       <c r="E70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3932,19 +3956,19 @@
         <v>100</v>
       </c>
       <c r="B71" t="s">
-        <v>254</v>
+        <v>633</v>
       </c>
       <c r="C71">
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F71" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3952,536 +3976,533 @@
         <v>101</v>
       </c>
       <c r="B72" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C72">
         <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B73" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C73">
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B74" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C74">
         <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="B75" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="B76" t="s">
-        <v>254</v>
+        <v>86</v>
       </c>
       <c r="C76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D76" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="E76">
-        <v>3</v>
-      </c>
-      <c r="F76" t="s">
-        <v>223</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="B77" t="s">
-        <v>254</v>
+        <v>635</v>
       </c>
       <c r="C77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D77" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="E77">
         <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>224</v>
+        <v>185</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B78" t="s">
-        <v>254</v>
+        <v>704</v>
       </c>
       <c r="C78">
         <v>2</v>
       </c>
       <c r="D78" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F78" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>68</v>
+        <v>618</v>
       </c>
       <c r="B79" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C79">
         <v>2</v>
       </c>
       <c r="D79" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E79">
         <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>193</v>
+        <v>617</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="B80" t="s">
-        <v>89</v>
+        <v>626</v>
       </c>
       <c r="C80">
         <v>2</v>
       </c>
       <c r="D80" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E80">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F80" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>70</v>
+      </c>
+      <c r="B81" t="s">
+        <v>705</v>
+      </c>
+      <c r="C81">
+        <v>2</v>
+      </c>
+      <c r="D81" t="s">
         <v>69</v>
       </c>
-      <c r="B81" t="s">
-        <v>254</v>
-      </c>
-      <c r="C81">
-        <v>2</v>
-      </c>
-      <c r="D81" t="s">
-        <v>67</v>
-      </c>
       <c r="E81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F81" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B82" t="s">
-        <v>254</v>
+        <v>655</v>
       </c>
       <c r="C82">
         <v>2</v>
       </c>
       <c r="D82" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E82">
         <v>3</v>
       </c>
       <c r="F82" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>632</v>
+        <v>72</v>
       </c>
       <c r="B83" t="s">
-        <v>254</v>
+        <v>627</v>
       </c>
       <c r="C83">
         <v>2</v>
       </c>
       <c r="D83" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E83">
         <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>631</v>
+        <v>190</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B84" t="s">
-        <v>642</v>
+        <v>627</v>
       </c>
       <c r="C84">
         <v>2</v>
       </c>
       <c r="D84" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E84">
         <v>1</v>
       </c>
       <c r="F84" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>75</v>
+      </c>
+      <c r="B85" t="s">
+        <v>634</v>
+      </c>
+      <c r="C85">
+        <v>2</v>
+      </c>
+      <c r="D85" t="s">
         <v>73</v>
       </c>
-      <c r="B85" t="s">
-        <v>254</v>
-      </c>
-      <c r="C85">
-        <v>2</v>
-      </c>
-      <c r="D85" t="s">
-        <v>72</v>
-      </c>
       <c r="E85">
         <v>2</v>
       </c>
       <c r="F85" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B86" t="s">
-        <v>254</v>
+        <v>633</v>
       </c>
       <c r="C86">
         <v>2</v>
       </c>
       <c r="D86" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F86" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B87" t="s">
-        <v>643</v>
+        <v>706</v>
       </c>
       <c r="C87">
         <v>2</v>
       </c>
       <c r="D87" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F87" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B88" t="s">
-        <v>643</v>
+        <v>629</v>
       </c>
       <c r="C88">
         <v>2</v>
       </c>
       <c r="D88" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E88">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F88" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B89" t="s">
-        <v>650</v>
+        <v>242</v>
       </c>
       <c r="C89">
         <v>2</v>
       </c>
       <c r="D89" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B90" t="s">
-        <v>649</v>
+        <v>242</v>
       </c>
       <c r="C90">
         <v>2</v>
       </c>
       <c r="D90" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F90" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>82</v>
+      </c>
+      <c r="B91" t="s">
+        <v>655</v>
+      </c>
+      <c r="C91">
+        <v>2</v>
+      </c>
+      <c r="D91" t="s">
         <v>80</v>
       </c>
-      <c r="B91" t="s">
-        <v>254</v>
-      </c>
-      <c r="C91">
-        <v>2</v>
-      </c>
-      <c r="D91" t="s">
-        <v>76</v>
-      </c>
       <c r="E91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F91" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B92" t="s">
-        <v>645</v>
+        <v>627</v>
       </c>
       <c r="C92">
         <v>2</v>
       </c>
       <c r="D92" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F92" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B93" t="s">
-        <v>254</v>
+        <v>633</v>
       </c>
       <c r="C93">
         <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F93" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B94" t="s">
-        <v>254</v>
+        <v>707</v>
       </c>
       <c r="C94">
         <v>2</v>
       </c>
       <c r="D94" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E94">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F94" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B95" t="s">
-        <v>671</v>
+        <v>86</v>
       </c>
       <c r="C95">
         <v>2</v>
       </c>
       <c r="D95" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="E95">
-        <v>2</v>
-      </c>
-      <c r="F95" t="s">
-        <v>207</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="B96" t="s">
-        <v>643</v>
+        <v>708</v>
       </c>
       <c r="C96">
         <v>2</v>
       </c>
       <c r="D96" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="E96">
         <v>2</v>
       </c>
       <c r="F96" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="B97" t="s">
-        <v>649</v>
+        <v>709</v>
       </c>
       <c r="C97">
         <v>2</v>
       </c>
       <c r="D97" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="E97">
         <v>3</v>
       </c>
       <c r="F97" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="B98" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C98">
         <v>2</v>
       </c>
       <c r="D98" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="E98">
         <v>3</v>
       </c>
       <c r="F98" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -4489,7 +4510,7 @@
         <v>108</v>
       </c>
       <c r="B99" t="s">
-        <v>254</v>
+        <v>705</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -4501,7 +4522,7 @@
         <v>1</v>
       </c>
       <c r="F99" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -4509,7 +4530,7 @@
         <v>110</v>
       </c>
       <c r="B100" t="s">
-        <v>254</v>
+        <v>710</v>
       </c>
       <c r="C100">
         <v>2</v>
@@ -4521,7 +4542,7 @@
         <v>2</v>
       </c>
       <c r="F100" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -4529,7 +4550,7 @@
         <v>111</v>
       </c>
       <c r="B101" t="s">
-        <v>254</v>
+        <v>663</v>
       </c>
       <c r="C101">
         <v>2</v>
@@ -4538,10 +4559,10 @@
         <v>109</v>
       </c>
       <c r="E101">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F101" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -4549,7 +4570,7 @@
         <v>112</v>
       </c>
       <c r="B102" t="s">
-        <v>254</v>
+        <v>635</v>
       </c>
       <c r="C102">
         <v>2</v>
@@ -4561,7 +4582,7 @@
         <v>3</v>
       </c>
       <c r="F102" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -4569,79 +4590,79 @@
         <v>113</v>
       </c>
       <c r="B103" t="s">
-        <v>254</v>
+        <v>711</v>
       </c>
       <c r="C103">
         <v>2</v>
       </c>
       <c r="D103" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E103">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F103" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>114</v>
+      </c>
+      <c r="B104" t="s">
+        <v>661</v>
+      </c>
+      <c r="C104">
+        <v>2</v>
+      </c>
+      <c r="D104" t="s">
         <v>115</v>
       </c>
-      <c r="B104" t="s">
-        <v>254</v>
-      </c>
-      <c r="C104">
-        <v>2</v>
-      </c>
-      <c r="D104" t="s">
-        <v>114</v>
-      </c>
       <c r="E104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F104" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B105" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C105">
         <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E105">
         <v>2</v>
       </c>
       <c r="F105" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B106" t="s">
-        <v>254</v>
+        <v>638</v>
       </c>
       <c r="C106">
         <v>2</v>
       </c>
       <c r="D106" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E106">
         <v>3</v>
       </c>
       <c r="F106" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4649,19 +4670,19 @@
         <v>118</v>
       </c>
       <c r="B107" t="s">
-        <v>254</v>
+        <v>712</v>
       </c>
       <c r="C107">
         <v>2</v>
       </c>
       <c r="D107" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E107">
         <v>3</v>
       </c>
       <c r="F107" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4669,7 +4690,7 @@
         <v>119</v>
       </c>
       <c r="B108" t="s">
-        <v>254</v>
+        <v>627</v>
       </c>
       <c r="C108">
         <v>2</v>
@@ -4681,15 +4702,15 @@
         <v>1</v>
       </c>
       <c r="F108" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B109" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C109">
         <v>2</v>
@@ -4701,15 +4722,15 @@
         <v>2</v>
       </c>
       <c r="F109" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B110" t="s">
-        <v>254</v>
+        <v>707</v>
       </c>
       <c r="C110">
         <v>2</v>
@@ -4721,35 +4742,35 @@
         <v>3</v>
       </c>
       <c r="F110" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B111" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C111">
         <v>2</v>
       </c>
       <c r="D111" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E111">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F111" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B112" t="s">
-        <v>643</v>
+        <v>713</v>
       </c>
       <c r="C112">
         <v>2</v>
@@ -4761,15 +4782,15 @@
         <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B113" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C113">
         <v>2</v>
@@ -4781,15 +4802,15 @@
         <v>2</v>
       </c>
       <c r="F113" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B114" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C114">
         <v>2</v>
@@ -4801,7 +4822,7 @@
         <v>3</v>
       </c>
       <c r="F114" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -4809,27 +4830,27 @@
         <v>129</v>
       </c>
       <c r="B115" t="s">
-        <v>254</v>
+        <v>682</v>
       </c>
       <c r="C115">
         <v>2</v>
       </c>
       <c r="D115" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E115">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F115" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="B116" t="s">
-        <v>254</v>
+        <v>86</v>
       </c>
       <c r="C116">
         <v>2</v>
@@ -4840,16 +4861,13 @@
       <c r="E116">
         <v>1</v>
       </c>
-      <c r="F116" t="s">
-        <v>243</v>
-      </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
       <c r="B117" t="s">
-        <v>254</v>
+        <v>86</v>
       </c>
       <c r="C117">
         <v>2</v>
@@ -4860,16 +4878,13 @@
       <c r="E117">
         <v>2</v>
       </c>
-      <c r="F117" t="s">
-        <v>244</v>
-      </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="B118" t="s">
-        <v>254</v>
+        <v>86</v>
       </c>
       <c r="C118">
         <v>2</v>
@@ -4878,214 +4893,220 @@
         <v>130</v>
       </c>
       <c r="E118">
-        <v>2</v>
-      </c>
-      <c r="F118" t="s">
-        <v>245</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="B119" t="s">
-        <v>254</v>
+        <v>86</v>
       </c>
       <c r="C119">
         <v>2</v>
       </c>
       <c r="D119" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E119">
-        <v>3</v>
-      </c>
-      <c r="F119" t="s">
-        <v>246</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="B120" t="s">
-        <v>698</v>
+        <v>86</v>
       </c>
       <c r="C120">
         <v>2</v>
       </c>
       <c r="D120" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E120">
-        <v>3</v>
-      </c>
-      <c r="F120" t="s">
-        <v>247</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>89</v>
+        <v>615</v>
       </c>
       <c r="B121" t="s">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="C121">
         <v>2</v>
       </c>
       <c r="D121" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E121">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F121" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B122" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C122">
         <v>2</v>
       </c>
       <c r="D122" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E122">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B123" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C123">
         <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E123">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B124" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C124">
         <v>2</v>
       </c>
       <c r="D124" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E124">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>89</v>
+        <v>621</v>
       </c>
       <c r="B125" t="s">
-        <v>89</v>
+        <v>627</v>
       </c>
       <c r="C125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D125" t="s">
-        <v>137</v>
+        <v>1</v>
       </c>
       <c r="E125">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F125" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>629</v>
+        <v>416</v>
       </c>
       <c r="B126" t="s">
-        <v>254</v>
+        <v>647</v>
       </c>
       <c r="C126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D126" t="s">
-        <v>137</v>
+        <v>1</v>
       </c>
       <c r="E126">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F126" t="s">
-        <v>630</v>
+        <v>582</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>89</v>
+        <v>414</v>
       </c>
       <c r="B127" t="s">
-        <v>89</v>
+        <v>636</v>
       </c>
       <c r="C127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D127" t="s">
-        <v>138</v>
+        <v>1</v>
       </c>
       <c r="E127">
         <v>1</v>
+      </c>
+      <c r="F127" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>89</v>
+        <v>417</v>
       </c>
       <c r="B128" t="s">
-        <v>89</v>
+        <v>634</v>
       </c>
       <c r="C128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D128" t="s">
-        <v>138</v>
+        <v>1</v>
       </c>
       <c r="E128">
         <v>2</v>
+      </c>
+      <c r="F128" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>89</v>
+        <v>421</v>
       </c>
       <c r="B129" t="s">
-        <v>89</v>
+        <v>676</v>
       </c>
       <c r="C129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D129" t="s">
-        <v>138</v>
+        <v>1</v>
       </c>
       <c r="E129">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="F129" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>637</v>
+        <v>424</v>
       </c>
       <c r="B130" t="s">
-        <v>254</v>
+        <v>675</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -5094,18 +5115,18 @@
         <v>1</v>
       </c>
       <c r="E130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" t="s">
-        <v>638</v>
+        <v>590</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B131" t="s">
-        <v>254</v>
+        <v>677</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -5114,18 +5135,18 @@
         <v>1</v>
       </c>
       <c r="E131">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F131" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="B132" t="s">
-        <v>254</v>
+        <v>634</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -5134,18 +5155,18 @@
         <v>1</v>
       </c>
       <c r="E132">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F132" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="B133" t="s">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -5154,18 +5175,18 @@
         <v>1</v>
       </c>
       <c r="E133">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F133" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="B134" t="s">
-        <v>692</v>
+        <v>628</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -5174,18 +5195,18 @@
         <v>1</v>
       </c>
       <c r="E134">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F134" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="B135" t="s">
-        <v>691</v>
+        <v>678</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -5194,18 +5215,18 @@
         <v>1</v>
       </c>
       <c r="E135">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F135" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>435</v>
+        <v>596</v>
       </c>
       <c r="B136" t="s">
-        <v>693</v>
+        <v>635</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -5214,118 +5235,118 @@
         <v>1</v>
       </c>
       <c r="E136">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F136" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>430</v>
+        <v>623</v>
       </c>
       <c r="B137" t="s">
-        <v>254</v>
+        <v>633</v>
       </c>
       <c r="C137">
         <v>1</v>
       </c>
       <c r="D137" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E137">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F137" t="s">
-        <v>596</v>
+        <v>624</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>432</v>
+        <v>407</v>
       </c>
       <c r="B138" t="s">
-        <v>686</v>
+        <v>666</v>
       </c>
       <c r="C138">
         <v>1</v>
       </c>
       <c r="D138" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E138">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F138" t="s">
-        <v>598</v>
+        <v>573</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>431</v>
+        <v>406</v>
       </c>
       <c r="B139" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="C139">
         <v>1</v>
       </c>
       <c r="D139" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E139">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F139" t="s">
-        <v>597</v>
+        <v>572</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>434</v>
+        <v>405</v>
       </c>
       <c r="B140" t="s">
-        <v>694</v>
+        <v>242</v>
       </c>
       <c r="C140">
         <v>1</v>
       </c>
       <c r="D140" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E140">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F140" t="s">
-        <v>600</v>
+        <v>571</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>610</v>
+        <v>409</v>
       </c>
       <c r="B141" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="C141">
         <v>1</v>
       </c>
       <c r="D141" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E141">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F141" t="s">
-        <v>618</v>
+        <v>575</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>639</v>
+        <v>408</v>
       </c>
       <c r="B142" t="s">
-        <v>254</v>
+        <v>636</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -5334,18 +5355,18 @@
         <v>8</v>
       </c>
       <c r="E142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F142" t="s">
-        <v>640</v>
+        <v>574</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="B143" t="s">
-        <v>682</v>
+        <v>671</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -5354,18 +5375,18 @@
         <v>8</v>
       </c>
       <c r="E143">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F143" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="B144" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -5374,18 +5395,18 @@
         <v>8</v>
       </c>
       <c r="E144">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F144" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B145" t="s">
-        <v>254</v>
+        <v>630</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -5394,18 +5415,18 @@
         <v>8</v>
       </c>
       <c r="E145">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F145" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="B146" t="s">
-        <v>675</v>
+        <v>242</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -5414,18 +5435,18 @@
         <v>8</v>
       </c>
       <c r="E146">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F146" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="B147" t="s">
-        <v>652</v>
+        <v>627</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -5434,118 +5455,118 @@
         <v>8</v>
       </c>
       <c r="E147">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F147" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>423</v>
+        <v>395</v>
       </c>
       <c r="B148" t="s">
-        <v>687</v>
+        <v>629</v>
       </c>
       <c r="C148">
         <v>1</v>
       </c>
       <c r="D148" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E148">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F148" t="s">
-        <v>589</v>
+        <v>561</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>422</v>
+        <v>397</v>
       </c>
       <c r="B149" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C149">
         <v>1</v>
       </c>
       <c r="D149" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E149">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F149" t="s">
-        <v>588</v>
+        <v>563</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>427</v>
+        <v>396</v>
       </c>
       <c r="B150" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="C150">
         <v>1</v>
       </c>
       <c r="D150" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E150">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F150" t="s">
-        <v>593</v>
+        <v>562</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>425</v>
+        <v>597</v>
       </c>
       <c r="B151" t="s">
-        <v>254</v>
+        <v>629</v>
       </c>
       <c r="C151">
         <v>1</v>
       </c>
       <c r="D151" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E151">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F151" t="s">
-        <v>591</v>
+        <v>605</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="B152" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C152">
         <v>1</v>
       </c>
       <c r="D152" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E152">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F152" t="s">
-        <v>590</v>
+        <v>566</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B153" t="s">
-        <v>645</v>
+        <v>714</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -5554,18 +5575,18 @@
         <v>15</v>
       </c>
       <c r="E153">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F153" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="B154" t="s">
-        <v>254</v>
+        <v>666</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -5574,18 +5595,18 @@
         <v>15</v>
       </c>
       <c r="E154">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F154" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B155" t="s">
-        <v>676</v>
+        <v>627</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -5594,18 +5615,18 @@
         <v>15</v>
       </c>
       <c r="E155">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F155" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>611</v>
+        <v>403</v>
       </c>
       <c r="B156" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -5614,18 +5635,18 @@
         <v>15</v>
       </c>
       <c r="E156">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F156" t="s">
-        <v>619</v>
+        <v>569</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="B157" t="s">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -5634,18 +5655,18 @@
         <v>15</v>
       </c>
       <c r="E157">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F157" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="B158" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -5654,118 +5675,118 @@
         <v>15</v>
       </c>
       <c r="E158">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F158" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="B159" t="s">
-        <v>682</v>
+        <v>635</v>
       </c>
       <c r="C159">
         <v>1</v>
       </c>
       <c r="D159" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E159">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F159" t="s">
-        <v>576</v>
+        <v>551</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="B160" t="s">
-        <v>643</v>
+        <v>242</v>
       </c>
       <c r="C160">
         <v>1</v>
       </c>
       <c r="D160" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E160">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F160" t="s">
-        <v>582</v>
+        <v>550</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>415</v>
+        <v>383</v>
       </c>
       <c r="B161" t="s">
-        <v>650</v>
+        <v>635</v>
       </c>
       <c r="C161">
         <v>1</v>
       </c>
       <c r="D161" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E161">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F161" t="s">
-        <v>581</v>
+        <v>549</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>414</v>
+        <v>382</v>
       </c>
       <c r="B162" t="s">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="C162">
         <v>1</v>
       </c>
       <c r="D162" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E162">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F162" t="s">
-        <v>580</v>
+        <v>548</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
       <c r="B163" t="s">
-        <v>254</v>
+        <v>633</v>
       </c>
       <c r="C163">
         <v>1</v>
       </c>
       <c r="D163" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E163">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F163" t="s">
-        <v>579</v>
+        <v>554</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="B164" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -5774,18 +5795,18 @@
         <v>23</v>
       </c>
       <c r="E164">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F164" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B165" t="s">
-        <v>254</v>
+        <v>627</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -5794,18 +5815,18 @@
         <v>23</v>
       </c>
       <c r="E165">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F165" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B166" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -5814,18 +5835,18 @@
         <v>23</v>
       </c>
       <c r="E166">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F166" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="B167" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -5834,18 +5855,18 @@
         <v>23</v>
       </c>
       <c r="E167">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F167" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B168" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -5854,18 +5875,18 @@
         <v>23</v>
       </c>
       <c r="E168">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F168" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B169" t="s">
-        <v>664</v>
+        <v>638</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -5874,18 +5895,18 @@
         <v>23</v>
       </c>
       <c r="E169">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F169" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="B170" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -5894,18 +5915,18 @@
         <v>23</v>
       </c>
       <c r="E170">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F170" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="B171" t="s">
-        <v>651</v>
+        <v>688</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -5914,118 +5935,118 @@
         <v>23</v>
       </c>
       <c r="E171">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F171" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>398</v>
+        <v>371</v>
       </c>
       <c r="B172" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="C172">
         <v>1</v>
       </c>
       <c r="D172" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E172">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F172" t="s">
-        <v>564</v>
+        <v>537</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>406</v>
+        <v>370</v>
       </c>
       <c r="B173" t="s">
-        <v>254</v>
+        <v>645</v>
       </c>
       <c r="C173">
         <v>1</v>
       </c>
       <c r="D173" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E173">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F173" t="s">
-        <v>572</v>
+        <v>536</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>405</v>
+        <v>374</v>
       </c>
       <c r="B174" t="s">
-        <v>654</v>
+        <v>629</v>
       </c>
       <c r="C174">
         <v>1</v>
       </c>
       <c r="D174" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E174">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F174" t="s">
-        <v>571</v>
+        <v>540</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="B175" t="s">
-        <v>650</v>
+        <v>629</v>
       </c>
       <c r="C175">
         <v>1</v>
       </c>
       <c r="D175" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E175">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F175" t="s">
-        <v>570</v>
+        <v>539</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>403</v>
+        <v>372</v>
       </c>
       <c r="B176" t="s">
-        <v>705</v>
+        <v>627</v>
       </c>
       <c r="C176">
         <v>1</v>
       </c>
       <c r="D176" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E176">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F176" t="s">
-        <v>569</v>
+        <v>538</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="B177" t="s">
-        <v>654</v>
+        <v>628</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -6034,18 +6055,18 @@
         <v>29</v>
       </c>
       <c r="E177">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F177" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B178" t="s">
-        <v>661</v>
+        <v>629</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -6054,18 +6075,18 @@
         <v>29</v>
       </c>
       <c r="E178">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F178" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="B179" t="s">
-        <v>645</v>
+        <v>660</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -6074,18 +6095,18 @@
         <v>29</v>
       </c>
       <c r="E179">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F179" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="B180" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -6094,18 +6115,18 @@
         <v>29</v>
       </c>
       <c r="E180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F180" t="s">
-        <v>551</v>
+        <v>541</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B181" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -6114,18 +6135,18 @@
         <v>29</v>
       </c>
       <c r="E181">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F181" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="B182" t="s">
-        <v>644</v>
+        <v>633</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -6134,18 +6155,18 @@
         <v>29</v>
       </c>
       <c r="E182">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F182" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="B183" t="s">
-        <v>645</v>
+        <v>661</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -6154,355 +6175,355 @@
         <v>29</v>
       </c>
       <c r="E183">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F183" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="B184" t="s">
-        <v>676</v>
+        <v>629</v>
       </c>
       <c r="C184">
         <v>1</v>
       </c>
       <c r="D184" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E184">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F184" t="s">
-        <v>554</v>
+        <v>529</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
       <c r="B185" t="s">
-        <v>650</v>
+        <v>629</v>
       </c>
       <c r="C185">
         <v>1</v>
       </c>
       <c r="D185" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E185">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F185" t="s">
-        <v>553</v>
+        <v>528</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>393</v>
+        <v>360</v>
       </c>
       <c r="B186" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="C186">
         <v>1</v>
       </c>
       <c r="D186" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E186">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F186" t="s">
-        <v>559</v>
+        <v>527</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="B187" t="s">
-        <v>649</v>
+        <v>627</v>
       </c>
       <c r="C187">
         <v>1</v>
       </c>
       <c r="D187" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E187">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F187" t="s">
-        <v>558</v>
+        <v>531</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="B188" t="s">
-        <v>677</v>
+        <v>627</v>
       </c>
       <c r="C188">
         <v>1</v>
       </c>
       <c r="D188" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E188">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F188" t="s">
-        <v>557</v>
+        <v>530</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B189" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="C189">
         <v>1</v>
       </c>
       <c r="D189" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E189">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F189" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B190" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="C190">
         <v>1</v>
       </c>
       <c r="D190" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E190">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F190" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B191" t="s">
-        <v>675</v>
+        <v>629</v>
       </c>
       <c r="C191">
         <v>1</v>
       </c>
       <c r="D191" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E191">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F191" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="B192" t="s">
-        <v>643</v>
+        <v>715</v>
       </c>
       <c r="C192">
         <v>1</v>
       </c>
       <c r="D192" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E192">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F192" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="B193" t="s">
-        <v>643</v>
+        <v>690</v>
       </c>
       <c r="C193">
         <v>1</v>
       </c>
       <c r="D193" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E193">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F193" t="s">
-        <v>542</v>
+        <v>689</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>635</v>
+        <v>353</v>
       </c>
       <c r="B194" t="s">
-        <v>254</v>
+        <v>641</v>
       </c>
       <c r="C194">
         <v>1</v>
       </c>
       <c r="D194" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E194">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F194" t="s">
-        <v>636</v>
+        <v>520</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="B195" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="C195">
         <v>1</v>
       </c>
       <c r="D195" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E195">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F195" t="s">
-        <v>547</v>
+        <v>519</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>380</v>
+        <v>351</v>
       </c>
       <c r="B196" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="C196">
         <v>1</v>
       </c>
       <c r="D196" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E196">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F196" t="s">
-        <v>546</v>
+        <v>518</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>379</v>
+        <v>356</v>
       </c>
       <c r="B197" t="s">
-        <v>645</v>
+        <v>687</v>
       </c>
       <c r="C197">
         <v>1</v>
       </c>
       <c r="D197" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E197">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F197" t="s">
-        <v>545</v>
+        <v>523</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>378</v>
+        <v>355</v>
       </c>
       <c r="B198" t="s">
-        <v>706</v>
+        <v>649</v>
       </c>
       <c r="C198">
         <v>1</v>
       </c>
       <c r="D198" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E198">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F198" t="s">
-        <v>544</v>
+        <v>522</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>377</v>
+        <v>354</v>
       </c>
       <c r="B199" t="s">
-        <v>704</v>
+        <v>635</v>
       </c>
       <c r="C199">
         <v>1</v>
       </c>
       <c r="D199" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E199">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F199" t="s">
-        <v>544</v>
+        <v>521</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B200" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C200">
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>40</v>
-      </c>
-      <c r="E200">
-        <v>1</v>
+        <v>38</v>
+      </c>
+      <c r="E200" t="s">
+        <v>612</v>
       </c>
       <c r="F200" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B201" t="s">
         <v>657</v>
@@ -6511,673 +6532,673 @@
         <v>1</v>
       </c>
       <c r="D201" t="s">
-        <v>40</v>
-      </c>
-      <c r="E201">
-        <v>1</v>
+        <v>38</v>
+      </c>
+      <c r="E201" t="s">
+        <v>612</v>
       </c>
       <c r="F201" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B202" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="C202">
         <v>1</v>
       </c>
       <c r="D202" t="s">
-        <v>40</v>
-      </c>
-      <c r="E202">
-        <v>1</v>
+        <v>38</v>
+      </c>
+      <c r="E202" t="s">
+        <v>612</v>
       </c>
       <c r="F202" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>368</v>
+        <v>341</v>
       </c>
       <c r="B203" t="s">
-        <v>703</v>
+        <v>635</v>
       </c>
       <c r="C203">
         <v>1</v>
       </c>
       <c r="D203" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E203">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F203" t="s">
-        <v>535</v>
+        <v>508</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>367</v>
+        <v>340</v>
       </c>
       <c r="B204" t="s">
-        <v>665</v>
+        <v>629</v>
       </c>
       <c r="C204">
         <v>1</v>
       </c>
       <c r="D204" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E204">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F204" t="s">
-        <v>534</v>
+        <v>507</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>366</v>
+        <v>339</v>
       </c>
       <c r="B205" t="s">
-        <v>651</v>
+        <v>630</v>
       </c>
       <c r="C205">
         <v>1</v>
       </c>
       <c r="D205" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E205">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F205" t="s">
-        <v>533</v>
+        <v>506</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>371</v>
+        <v>344</v>
       </c>
       <c r="B206" t="s">
-        <v>674</v>
+        <v>654</v>
       </c>
       <c r="C206">
         <v>1</v>
       </c>
       <c r="D206" t="s">
-        <v>40</v>
-      </c>
-      <c r="E206" t="s">
-        <v>626</v>
+        <v>44</v>
+      </c>
+      <c r="E206">
+        <v>2</v>
       </c>
       <c r="F206" t="s">
-        <v>538</v>
+        <v>511</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>370</v>
+        <v>343</v>
       </c>
       <c r="B207" t="s">
-        <v>673</v>
+        <v>635</v>
       </c>
       <c r="C207">
         <v>1</v>
       </c>
       <c r="D207" t="s">
-        <v>40</v>
-      </c>
-      <c r="E207" t="s">
-        <v>626</v>
+        <v>44</v>
+      </c>
+      <c r="E207">
+        <v>2</v>
       </c>
       <c r="F207" t="s">
-        <v>537</v>
+        <v>510</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>369</v>
+        <v>342</v>
       </c>
       <c r="B208" t="s">
-        <v>672</v>
+        <v>635</v>
       </c>
       <c r="C208">
         <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>40</v>
-      </c>
-      <c r="E208" t="s">
-        <v>626</v>
+        <v>44</v>
+      </c>
+      <c r="E208">
+        <v>2</v>
       </c>
       <c r="F208" t="s">
-        <v>536</v>
+        <v>509</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B209" t="s">
-        <v>651</v>
+        <v>629</v>
       </c>
       <c r="C209">
         <v>1</v>
       </c>
       <c r="D209" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E209">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F209" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B210" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="C210">
         <v>1</v>
       </c>
       <c r="D210" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E210">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F210" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B211" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="C211">
         <v>1</v>
       </c>
       <c r="D211" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E211">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F211" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B212" t="s">
-        <v>670</v>
+        <v>630</v>
       </c>
       <c r="C212">
         <v>1</v>
       </c>
       <c r="D212" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E212">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F212" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B213" t="s">
-        <v>651</v>
+        <v>627</v>
       </c>
       <c r="C213">
         <v>1</v>
       </c>
       <c r="D213" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E213">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F213" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B214" t="s">
-        <v>651</v>
+        <v>629</v>
       </c>
       <c r="C214">
         <v>1</v>
       </c>
       <c r="D214" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E214">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F214" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="B215" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="C215">
         <v>1</v>
       </c>
       <c r="D215" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E215">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F215" t="s">
-        <v>526</v>
+        <v>497</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="B216" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C216">
         <v>1</v>
       </c>
       <c r="D216" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E216">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F216" t="s">
-        <v>525</v>
+        <v>496</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="B217" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C217">
         <v>1</v>
       </c>
       <c r="D217" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E217">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F217" t="s">
-        <v>524</v>
+        <v>495</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>362</v>
+        <v>327</v>
       </c>
       <c r="B218" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="C218">
         <v>1</v>
       </c>
       <c r="D218" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E218">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F218" t="s">
-        <v>529</v>
+        <v>494</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="B219" t="s">
-        <v>643</v>
+        <v>629</v>
       </c>
       <c r="C219">
         <v>1</v>
       </c>
       <c r="D219" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E219">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F219" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>360</v>
+        <v>332</v>
       </c>
       <c r="B220" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="C220">
         <v>1</v>
       </c>
       <c r="D220" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E220">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F220" t="s">
-        <v>527</v>
+        <v>499</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="B221" t="s">
-        <v>651</v>
+        <v>627</v>
       </c>
       <c r="C221">
         <v>1</v>
       </c>
       <c r="D221" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E221">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F221" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B222" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="C222">
         <v>1</v>
       </c>
       <c r="D222" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E222">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F222" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B223" t="s">
-        <v>663</v>
+        <v>635</v>
       </c>
       <c r="C223">
         <v>1</v>
       </c>
       <c r="D223" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E223">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F223" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B224" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="C224">
         <v>1</v>
       </c>
       <c r="D224" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E224">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F224" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="B225" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="C225">
         <v>1</v>
       </c>
       <c r="D225" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E225">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F225" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="B226" t="s">
-        <v>645</v>
+        <v>686</v>
       </c>
       <c r="C226">
         <v>1</v>
       </c>
       <c r="D226" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E226">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F226" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="B227" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="C227">
         <v>1</v>
       </c>
       <c r="D227" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E227">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F227" t="s">
-        <v>510</v>
+        <v>481</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>347</v>
+        <v>313</v>
       </c>
       <c r="B228" t="s">
-        <v>675</v>
+        <v>635</v>
       </c>
       <c r="C228">
         <v>1</v>
       </c>
       <c r="D228" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E228">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F228" t="s">
-        <v>514</v>
+        <v>480</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>346</v>
+        <v>312</v>
       </c>
       <c r="B229" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="C229">
         <v>1</v>
       </c>
       <c r="D229" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E229">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F229" t="s">
-        <v>513</v>
+        <v>479</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>350</v>
+        <v>311</v>
       </c>
       <c r="B230" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="C230">
         <v>1</v>
       </c>
       <c r="D230" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E230">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F230" t="s">
-        <v>517</v>
+        <v>478</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>349</v>
+        <v>318</v>
       </c>
       <c r="B231" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="C231">
         <v>1</v>
       </c>
       <c r="D231" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E231">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F231" t="s">
-        <v>516</v>
+        <v>485</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>348</v>
+        <v>317</v>
       </c>
       <c r="B232" t="s">
-        <v>702</v>
+        <v>640</v>
       </c>
       <c r="C232">
         <v>1</v>
       </c>
       <c r="D232" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E232">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F232" t="s">
-        <v>515</v>
+        <v>484</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="B233" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="C233">
         <v>1</v>
       </c>
       <c r="D233" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E233">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F233" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="B234" t="s">
-        <v>651</v>
+        <v>629</v>
       </c>
       <c r="C234">
         <v>1</v>
       </c>
       <c r="D234" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E234">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F234" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -7185,16 +7206,16 @@
         <v>324</v>
       </c>
       <c r="B235" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="C235">
         <v>1</v>
       </c>
       <c r="D235" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E235">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F235" t="s">
         <v>491</v>
@@ -7205,16 +7226,16 @@
         <v>323</v>
       </c>
       <c r="B236" t="s">
-        <v>651</v>
+        <v>630</v>
       </c>
       <c r="C236">
         <v>1</v>
       </c>
       <c r="D236" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E236">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F236" t="s">
         <v>490</v>
@@ -7222,147 +7243,147 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="B237" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="C237">
         <v>1</v>
       </c>
       <c r="D237" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E237">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F237" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B238" t="s">
-        <v>656</v>
+        <v>629</v>
       </c>
       <c r="C238">
         <v>1</v>
       </c>
       <c r="D238" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E238">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F238" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B239" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="C239">
         <v>1</v>
       </c>
       <c r="D239" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E239">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F239" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="B240" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="C240">
         <v>1</v>
       </c>
       <c r="D240" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E240">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F240" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="B241" t="s">
-        <v>651</v>
+        <v>629</v>
       </c>
       <c r="C241">
         <v>1</v>
       </c>
       <c r="D241" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E241">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F241" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="B242" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="C242">
         <v>1</v>
       </c>
       <c r="D242" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E242">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F242" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>334</v>
+        <v>298</v>
       </c>
       <c r="B243" t="s">
-        <v>665</v>
+        <v>635</v>
       </c>
       <c r="C243">
         <v>1</v>
       </c>
       <c r="D243" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E243">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F243" t="s">
-        <v>501</v>
+        <v>465</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="B244" t="s">
         <v>645</v>
@@ -7371,258 +7392,258 @@
         <v>1</v>
       </c>
       <c r="D244" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E244">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F244" t="s">
-        <v>500</v>
+        <v>464</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>332</v>
+        <v>296</v>
       </c>
       <c r="B245" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="C245">
         <v>1</v>
       </c>
       <c r="D245" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E245">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F245" t="s">
-        <v>499</v>
+        <v>463</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>331</v>
+        <v>302</v>
       </c>
       <c r="B246" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C246">
         <v>1</v>
       </c>
       <c r="D246" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E246">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F246" t="s">
-        <v>498</v>
+        <v>469</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>338</v>
+        <v>301</v>
       </c>
       <c r="B247" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C247">
         <v>1</v>
       </c>
       <c r="D247" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E247">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F247" t="s">
-        <v>505</v>
+        <v>468</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>337</v>
+        <v>300</v>
       </c>
       <c r="B248" t="s">
-        <v>666</v>
+        <v>629</v>
       </c>
       <c r="C248">
         <v>1</v>
       </c>
       <c r="D248" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E248">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F248" t="s">
-        <v>504</v>
+        <v>467</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="B249" t="s">
-        <v>651</v>
+        <v>627</v>
       </c>
       <c r="C249">
         <v>1</v>
       </c>
       <c r="D249" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E249">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F249" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B250" t="s">
-        <v>661</v>
+        <v>629</v>
       </c>
       <c r="C250">
         <v>1</v>
       </c>
       <c r="D250" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E250">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F250" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B251" t="s">
-        <v>660</v>
+        <v>629</v>
       </c>
       <c r="C251">
         <v>1</v>
       </c>
       <c r="D251" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E251">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F251" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="B252" t="s">
-        <v>664</v>
+        <v>629</v>
       </c>
       <c r="C252">
         <v>1</v>
       </c>
       <c r="D252" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E252">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F252" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="B253" t="s">
-        <v>663</v>
+        <v>629</v>
       </c>
       <c r="C253">
         <v>1</v>
       </c>
       <c r="D253" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E253">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F253" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B254" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="C254">
         <v>1</v>
       </c>
       <c r="D254" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E254">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F254" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B255" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="C255">
         <v>1</v>
       </c>
       <c r="D255" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E255">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F255" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="B256" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="C256">
         <v>1</v>
       </c>
       <c r="D256" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E256">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F256" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="B257" t="s">
         <v>645</v>
@@ -7631,1269 +7652,1149 @@
         <v>1</v>
       </c>
       <c r="D257" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E257">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F257" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="B258" t="s">
-        <v>645</v>
+        <v>663</v>
       </c>
       <c r="C258">
         <v>1</v>
       </c>
       <c r="D258" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E258">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F258" t="s">
-        <v>483</v>
+        <v>455</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>315</v>
+        <v>287</v>
       </c>
       <c r="B259" t="s">
-        <v>645</v>
+        <v>631</v>
       </c>
       <c r="C259">
         <v>1</v>
       </c>
       <c r="D259" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E259">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F259" t="s">
-        <v>482</v>
+        <v>454</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>322</v>
+        <v>286</v>
       </c>
       <c r="B260" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="C260">
         <v>1</v>
       </c>
       <c r="D260" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E260">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F260" t="s">
-        <v>489</v>
+        <v>453</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>321</v>
+        <v>291</v>
       </c>
       <c r="B261" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="C261">
         <v>1</v>
       </c>
       <c r="D261" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E261">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F261" t="s">
-        <v>488</v>
+        <v>458</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="B262" t="s">
-        <v>645</v>
+        <v>684</v>
       </c>
       <c r="C262">
         <v>1</v>
       </c>
       <c r="D262" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E262">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F262" t="s">
-        <v>487</v>
+        <v>457</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>319</v>
+        <v>289</v>
       </c>
       <c r="B263" t="s">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="C263">
         <v>1</v>
       </c>
       <c r="D263" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E263">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F263" t="s">
-        <v>486</v>
+        <v>456</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>300</v>
+        <v>603</v>
       </c>
       <c r="B264" t="s">
-        <v>679</v>
+        <v>242</v>
       </c>
       <c r="C264">
         <v>1</v>
       </c>
       <c r="D264" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E264">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F264" t="s">
-        <v>467</v>
+        <v>611</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B265" t="s">
-        <v>647</v>
+        <v>242</v>
       </c>
       <c r="C265">
         <v>1</v>
       </c>
       <c r="D265" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E265">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F265" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B266" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="C266">
         <v>1</v>
       </c>
       <c r="D266" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E266">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F266" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="B267" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="C267">
         <v>1</v>
       </c>
       <c r="D267" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E267">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F267" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="B268" t="s">
-        <v>700</v>
+        <v>647</v>
       </c>
       <c r="C268">
         <v>1</v>
       </c>
       <c r="D268" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E268">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F268" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="B269" t="s">
-        <v>650</v>
+        <v>635</v>
       </c>
       <c r="C269">
         <v>1</v>
       </c>
       <c r="D269" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E269">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F269" t="s">
-        <v>468</v>
+        <v>447</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>617</v>
+        <v>680</v>
       </c>
       <c r="B270" t="s">
-        <v>254</v>
+        <v>635</v>
       </c>
       <c r="C270">
         <v>1</v>
       </c>
       <c r="D270" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E270">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F270" t="s">
-        <v>625</v>
+        <v>681</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="B271" t="s">
-        <v>254</v>
+        <v>684</v>
       </c>
       <c r="C271">
         <v>1</v>
       </c>
       <c r="D271" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E271">
         <v>3</v>
       </c>
       <c r="F271" t="s">
-        <v>472</v>
+        <v>450</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>304</v>
+        <v>282</v>
       </c>
       <c r="B272" t="s">
-        <v>651</v>
+        <v>629</v>
       </c>
       <c r="C272">
         <v>1</v>
       </c>
       <c r="D272" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E272">
         <v>3</v>
       </c>
       <c r="F272" t="s">
-        <v>471</v>
+        <v>449</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>307</v>
+        <v>281</v>
       </c>
       <c r="B273" t="s">
-        <v>660</v>
+        <v>635</v>
       </c>
       <c r="C273">
         <v>1</v>
       </c>
       <c r="D273" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E273">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F273" t="s">
-        <v>474</v>
+        <v>448</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>306</v>
+        <v>425</v>
       </c>
       <c r="B274" t="s">
-        <v>663</v>
+        <v>643</v>
       </c>
       <c r="C274">
         <v>1</v>
       </c>
       <c r="D274" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E274">
         <v>4</v>
       </c>
       <c r="F274" t="s">
-        <v>473</v>
+        <v>591</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>292</v>
+        <v>592</v>
       </c>
       <c r="B275" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="C275">
         <v>1</v>
       </c>
       <c r="D275" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E275">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F275" t="s">
-        <v>459</v>
+        <v>593</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>696</v>
+        <v>285</v>
       </c>
       <c r="B276" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="C276">
         <v>1</v>
       </c>
       <c r="D276" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E276">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F276" t="s">
-        <v>697</v>
+        <v>452</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="B277" t="s">
-        <v>700</v>
+        <v>685</v>
       </c>
       <c r="C277">
         <v>1</v>
       </c>
       <c r="D277" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E277">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F277" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="B278" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="C278">
         <v>1</v>
       </c>
       <c r="D278" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E278">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F278" t="s">
-        <v>461</v>
+        <v>441</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="B279" t="s">
-        <v>651</v>
+        <v>637</v>
       </c>
       <c r="C279">
         <v>1</v>
       </c>
       <c r="D279" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E279">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F279" t="s">
-        <v>460</v>
+        <v>440</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>437</v>
+        <v>272</v>
       </c>
       <c r="B280" t="s">
-        <v>659</v>
+        <v>633</v>
       </c>
       <c r="C280">
         <v>1</v>
       </c>
       <c r="D280" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E280">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F280" t="s">
-        <v>603</v>
+        <v>439</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>604</v>
+        <v>276</v>
       </c>
       <c r="B281" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="C281">
         <v>1</v>
       </c>
       <c r="D281" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E281">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F281" t="s">
-        <v>605</v>
+        <v>443</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="B282" t="s">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="C282">
         <v>1</v>
       </c>
       <c r="D282" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E282">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F282" t="s">
-        <v>464</v>
+        <v>442</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>296</v>
+        <v>600</v>
       </c>
       <c r="B283" t="s">
-        <v>701</v>
+        <v>630</v>
       </c>
       <c r="C283">
         <v>1</v>
       </c>
       <c r="D283" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E283">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F283" t="s">
-        <v>463</v>
+        <v>608</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>286</v>
+        <v>599</v>
       </c>
       <c r="B284" t="s">
-        <v>653</v>
+        <v>638</v>
       </c>
       <c r="C284">
         <v>1</v>
       </c>
       <c r="D284" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E284">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F284" t="s">
-        <v>453</v>
+        <v>607</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B285" t="s">
-        <v>653</v>
+        <v>635</v>
       </c>
       <c r="C285">
         <v>1</v>
       </c>
       <c r="D285" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E285">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F285" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B286" t="s">
-        <v>649</v>
+        <v>627</v>
       </c>
       <c r="C286">
         <v>1</v>
       </c>
       <c r="D286" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E286">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F286" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>288</v>
+        <v>601</v>
       </c>
       <c r="B287" t="s">
-        <v>658</v>
+        <v>638</v>
       </c>
       <c r="C287">
         <v>1</v>
       </c>
       <c r="D287" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E287">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F287" t="s">
-        <v>455</v>
+        <v>609</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B288" t="s">
-        <v>654</v>
+        <v>638</v>
       </c>
       <c r="C288">
         <v>1</v>
       </c>
       <c r="D288" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E288">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F288" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="B289" t="s">
-        <v>646</v>
+        <v>630</v>
       </c>
       <c r="C289">
         <v>1</v>
       </c>
       <c r="D289" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E289">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F289" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>613</v>
+        <v>271</v>
       </c>
       <c r="B290" t="s">
-        <v>654</v>
+        <v>629</v>
       </c>
       <c r="C290">
         <v>1</v>
       </c>
       <c r="D290" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E290">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F290" t="s">
-        <v>621</v>
+        <v>438</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="B291" t="s">
-        <v>651</v>
+        <v>683</v>
       </c>
       <c r="C291">
         <v>1</v>
       </c>
       <c r="D291" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E291">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F291" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>289</v>
+        <v>598</v>
       </c>
       <c r="B292" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="C292">
         <v>1</v>
       </c>
       <c r="D292" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E292">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F292" t="s">
-        <v>456</v>
+        <v>606</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>615</v>
+        <v>263</v>
       </c>
       <c r="B293" t="s">
-        <v>654</v>
+        <v>636</v>
       </c>
       <c r="C293">
         <v>1</v>
       </c>
       <c r="D293" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E293">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F293" t="s">
-        <v>623</v>
+        <v>430</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="B294" t="s">
-        <v>654</v>
+        <v>635</v>
       </c>
       <c r="C294">
         <v>1</v>
       </c>
       <c r="D294" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E294">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F294" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>634</v>
+        <v>266</v>
       </c>
       <c r="B295" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C295">
         <v>1</v>
       </c>
       <c r="D295" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E295">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F295" t="s">
-        <v>633</v>
+        <v>433</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="B296" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="C296">
         <v>1</v>
       </c>
       <c r="D296" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E296">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F296" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B297" t="s">
-        <v>699</v>
+        <v>638</v>
       </c>
       <c r="C297">
         <v>1</v>
       </c>
       <c r="D297" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E297">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F297" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>612</v>
+        <v>269</v>
       </c>
       <c r="B298" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="C298">
         <v>1</v>
       </c>
       <c r="D298" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E298">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F298" t="s">
-        <v>620</v>
+        <v>436</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B299" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="C299">
         <v>1</v>
       </c>
       <c r="D299" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E299">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F299" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>279</v>
+        <v>123</v>
       </c>
       <c r="B300" t="s">
-        <v>651</v>
+        <v>629</v>
       </c>
       <c r="C300">
         <v>1</v>
       </c>
       <c r="D300" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E300">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F300" t="s">
-        <v>446</v>
+        <v>230</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="B301" t="s">
-        <v>663</v>
+        <v>635</v>
       </c>
       <c r="C301">
         <v>1</v>
       </c>
       <c r="D301" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E301">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F301" t="s">
-        <v>445</v>
+        <v>253</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>277</v>
+        <v>245</v>
       </c>
       <c r="B302" t="s">
-        <v>650</v>
+        <v>635</v>
       </c>
       <c r="C302">
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E302">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F302" t="s">
-        <v>444</v>
+        <v>252</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>282</v>
+        <v>243</v>
       </c>
       <c r="B303" t="s">
-        <v>654</v>
+        <v>634</v>
       </c>
       <c r="C303">
         <v>1</v>
       </c>
       <c r="D303" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E303">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F303" t="s">
-        <v>449</v>
+        <v>244</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="B304" t="s">
-        <v>254</v>
+        <v>634</v>
       </c>
       <c r="C304">
         <v>1</v>
       </c>
       <c r="D304" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E304">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F304" t="s">
-        <v>448</v>
+        <v>256</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>280</v>
+        <v>248</v>
       </c>
       <c r="B305" t="s">
-        <v>657</v>
+        <v>635</v>
       </c>
       <c r="C305">
         <v>1</v>
       </c>
       <c r="D305" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E305">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F305" t="s">
-        <v>447</v>
+        <v>255</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>128</v>
+        <v>247</v>
       </c>
       <c r="B306" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="C306">
         <v>1</v>
       </c>
       <c r="D306" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E306">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F306" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B307" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="C307">
         <v>1</v>
       </c>
       <c r="D307" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E307">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F307" t="s">
-        <v>265</v>
+        <v>426</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>257</v>
+        <v>602</v>
       </c>
       <c r="B308" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="C308">
         <v>1</v>
       </c>
       <c r="D308" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E308">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F308" t="s">
-        <v>264</v>
+        <v>610</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B309" t="s">
-        <v>650</v>
+        <v>633</v>
       </c>
       <c r="C309">
         <v>1</v>
       </c>
       <c r="D309" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E309">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F309" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="B310" t="s">
-        <v>650</v>
+        <v>635</v>
       </c>
       <c r="C310">
         <v>1</v>
       </c>
       <c r="D310" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E310">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F310" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B311" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="C311">
         <v>1</v>
       </c>
       <c r="D311" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E311">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F311" t="s">
-        <v>267</v>
+        <v>429</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B312" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="C312">
         <v>1</v>
       </c>
       <c r="D312" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E312">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F312" t="s">
-        <v>266</v>
+        <v>428</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="B313" t="s">
-        <v>651</v>
+        <v>629</v>
       </c>
       <c r="C313">
         <v>1</v>
       </c>
       <c r="D313" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E313">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F313" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
-        <v>616</v>
-      </c>
-      <c r="B314" t="s">
-        <v>656</v>
-      </c>
-      <c r="C314">
-        <v>1</v>
-      </c>
-      <c r="D314" t="s">
-        <v>83</v>
-      </c>
-      <c r="E314">
-        <v>3</v>
-      </c>
-      <c r="F314" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
-        <v>263</v>
-      </c>
-      <c r="B315" t="s">
-        <v>649</v>
-      </c>
-      <c r="C315">
-        <v>1</v>
-      </c>
-      <c r="D315" t="s">
-        <v>83</v>
-      </c>
-      <c r="E315">
-        <v>3</v>
-      </c>
-      <c r="F315" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
-        <v>262</v>
-      </c>
-      <c r="B316" t="s">
-        <v>651</v>
-      </c>
-      <c r="C316">
-        <v>1</v>
-      </c>
-      <c r="D316" t="s">
-        <v>83</v>
-      </c>
-      <c r="E316">
-        <v>3</v>
-      </c>
-      <c r="F316" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A317" t="s">
-        <v>274</v>
-      </c>
-      <c r="B317" t="s">
-        <v>655</v>
-      </c>
-      <c r="C317">
-        <v>1</v>
-      </c>
-      <c r="D317" t="s">
-        <v>83</v>
-      </c>
-      <c r="E317">
-        <v>4</v>
-      </c>
-      <c r="F317" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A318" t="s">
-        <v>273</v>
-      </c>
-      <c r="B318" t="s">
-        <v>655</v>
-      </c>
-      <c r="C318">
-        <v>1</v>
-      </c>
-      <c r="D318" t="s">
-        <v>83</v>
-      </c>
-      <c r="E318">
-        <v>4</v>
-      </c>
-      <c r="F318" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A319" t="s">
-        <v>272</v>
-      </c>
-      <c r="B319" t="s">
-        <v>645</v>
-      </c>
-      <c r="C319">
-        <v>1</v>
-      </c>
-      <c r="D319" t="s">
-        <v>83</v>
-      </c>
-      <c r="E319">
-        <v>4</v>
-      </c>
-      <c r="F319" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F319" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F319">
-      <sortCondition descending="1" ref="C2:C319"/>
-      <sortCondition ref="D2:D319"/>
-      <sortCondition ref="E2:E319"/>
-      <sortCondition descending="1" ref="A2:A319"/>
+  <autoFilter ref="A1:F313" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F313">
+      <sortCondition descending="1" ref="C2:C313"/>
+      <sortCondition ref="D2:D313"/>
+      <sortCondition ref="E2:E313"/>
+      <sortCondition descending="1" ref="A2:A313"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F318">
-    <sortCondition descending="1" ref="C2:C318"/>
-    <sortCondition ref="D2:D318"/>
-    <sortCondition ref="E2:E318"/>
-    <sortCondition descending="1" ref="A2:A318"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F312">
+    <sortCondition descending="1" ref="C2:C312"/>
+    <sortCondition ref="D2:D312"/>
+    <sortCondition ref="E2:E312"/>
+    <sortCondition descending="1" ref="A2:A312"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\BECARIO PROCESOS\EOAT PROJECT\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\BECARIO PROCESOS\EOAT PROJECT\Inventario_repo_v3\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3900B35B-5EF8-43E7-90E9-E735DBA75242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1D1F16-7B66-40EE-AF0F-DE0160BBC991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$313</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$319</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1241" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="738">
   <si>
     <t>I-1937</t>
   </si>
@@ -2187,6 +2187,72 @@
   </si>
   <si>
     <t>4 ventosas, 2 pinzas, 4 dedos</t>
+  </si>
+  <si>
+    <t>Tarjetería electrónica, 2 dedos, 5 pinzas, 1 ventosa</t>
+  </si>
+  <si>
+    <t>6 pinzas, 2 dedos</t>
+  </si>
+  <si>
+    <t>Tarjetería electrónica, 10 pinzas, 1 ventosa</t>
+  </si>
+  <si>
+    <t>I-1768</t>
+  </si>
+  <si>
+    <t>I-1768.jpeg</t>
+  </si>
+  <si>
+    <t>I-1770</t>
+  </si>
+  <si>
+    <t>I-1770.jpeg</t>
+  </si>
+  <si>
+    <t>I-1864 (2)</t>
+  </si>
+  <si>
+    <t>I-1969</t>
+  </si>
+  <si>
+    <t>I-1973</t>
+  </si>
+  <si>
+    <t>I-1969.jpeg</t>
+  </si>
+  <si>
+    <t>I-1973.jpeg</t>
+  </si>
+  <si>
+    <t>I-1972</t>
+  </si>
+  <si>
+    <t>I-1972.jpeg</t>
+  </si>
+  <si>
+    <t>I-1976</t>
+  </si>
+  <si>
+    <t>I-1976.jpeg</t>
+  </si>
+  <si>
+    <t>I-1831</t>
+  </si>
+  <si>
+    <t>I-1971</t>
+  </si>
+  <si>
+    <t>I-1831.jpeg</t>
+  </si>
+  <si>
+    <t>I-1971.jpeg</t>
+  </si>
+  <si>
+    <t>I-1947</t>
+  </si>
+  <si>
+    <t>I-1947.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2564,7 +2630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-  <dimension ref="A1:F313"/>
+  <dimension ref="A1:F319"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -2820,7 +2886,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>242</v>
+        <v>716</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -3117,10 +3183,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>723</v>
       </c>
       <c r="B28" t="s">
-        <v>627</v>
+        <v>242</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -3132,15 +3198,15 @@
         <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>653</v>
+        <v>627</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -3149,55 +3215,58 @@
         <v>29</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>728</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F30" t="s">
+        <v>729</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>694</v>
+        <v>653</v>
       </c>
       <c r="C31">
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>732</v>
       </c>
       <c r="B32" t="s">
-        <v>695</v>
+        <v>242</v>
       </c>
       <c r="C32">
         <v>3</v>
@@ -3206,18 +3275,18 @@
         <v>32</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>161</v>
+        <v>734</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>733</v>
       </c>
       <c r="B33" t="s">
-        <v>652</v>
+        <v>242</v>
       </c>
       <c r="C33">
         <v>3</v>
@@ -3226,18 +3295,18 @@
         <v>32</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>162</v>
+        <v>735</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>651</v>
+        <v>694</v>
       </c>
       <c r="C34">
         <v>3</v>
@@ -3246,78 +3315,78 @@
         <v>32</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>651</v>
+        <v>695</v>
       </c>
       <c r="C35">
         <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>242</v>
+        <v>652</v>
       </c>
       <c r="C36">
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>696</v>
+        <v>651</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>242</v>
+        <v>651</v>
       </c>
       <c r="C38">
         <v>3</v>
@@ -3326,18 +3395,18 @@
         <v>38</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B39" t="s">
-        <v>697</v>
+        <v>717</v>
       </c>
       <c r="C39">
         <v>3</v>
@@ -3346,78 +3415,78 @@
         <v>38</v>
       </c>
       <c r="E39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>631</v>
+        <v>696</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>630</v>
+        <v>718</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C42">
         <v>3</v>
       </c>
       <c r="D42" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>646</v>
+        <v>631</v>
       </c>
       <c r="C43">
         <v>3</v>
@@ -3426,18 +3495,18 @@
         <v>44</v>
       </c>
       <c r="E43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="C44">
         <v>3</v>
@@ -3446,198 +3515,198 @@
         <v>44</v>
       </c>
       <c r="E44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>242</v>
+        <v>698</v>
       </c>
       <c r="C45">
         <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>699</v>
+        <v>646</v>
       </c>
       <c r="C46">
         <v>3</v>
       </c>
       <c r="D46" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>242</v>
+        <v>626</v>
       </c>
       <c r="C47">
         <v>3</v>
       </c>
       <c r="D47" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E47">
         <v>3</v>
       </c>
       <c r="F47" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>663</v>
+        <v>242</v>
       </c>
       <c r="C48">
         <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>242</v>
+        <v>699</v>
       </c>
       <c r="C49">
         <v>3</v>
       </c>
       <c r="D49" t="s">
-        <v>54</v>
-      </c>
-      <c r="E49" t="s">
-        <v>613</v>
+        <v>50</v>
+      </c>
+      <c r="E49">
+        <v>2</v>
       </c>
       <c r="F49" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B50" t="s">
-        <v>614</v>
+        <v>242</v>
       </c>
       <c r="C50">
         <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>54</v>
-      </c>
-      <c r="E50" t="s">
-        <v>613</v>
+        <v>50</v>
+      </c>
+      <c r="E50">
+        <v>3</v>
       </c>
       <c r="F50" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B51" t="s">
-        <v>700</v>
+        <v>663</v>
       </c>
       <c r="C51">
         <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E51">
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>633</v>
+        <v>242</v>
       </c>
       <c r="C52">
         <v>3</v>
       </c>
       <c r="D52" t="s">
-        <v>59</v>
-      </c>
-      <c r="E52">
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="E52" t="s">
+        <v>613</v>
       </c>
       <c r="F52" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B53" t="s">
-        <v>242</v>
+        <v>614</v>
       </c>
       <c r="C53">
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>59</v>
-      </c>
-      <c r="E53">
-        <v>2</v>
+        <v>54</v>
+      </c>
+      <c r="E53" t="s">
+        <v>613</v>
       </c>
       <c r="F53" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B54" t="s">
-        <v>62</v>
+        <v>700</v>
       </c>
       <c r="C54">
         <v>3</v>
@@ -3646,41 +3715,50 @@
         <v>59</v>
       </c>
       <c r="E54">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F54" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>633</v>
       </c>
       <c r="C55">
         <v>3</v>
       </c>
       <c r="D55" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E55">
         <v>1</v>
+      </c>
+      <c r="F55" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B56" t="s">
-        <v>62</v>
+        <v>242</v>
       </c>
       <c r="C56">
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E56">
         <v>2</v>
+      </c>
+      <c r="F56" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3694,7 +3772,7 @@
         <v>3</v>
       </c>
       <c r="D57" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E57">
         <v>3</v>
@@ -3702,16 +3780,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="B58" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C58">
         <v>3</v>
       </c>
       <c r="D58" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -3719,24 +3797,27 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>86</v>
+        <v>721</v>
       </c>
       <c r="B59" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="C59">
         <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="E59">
         <v>2</v>
+      </c>
+      <c r="F59" t="s">
+        <v>722</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>56</v>
+        <v>719</v>
       </c>
       <c r="B60" t="s">
         <v>242</v>
@@ -3745,115 +3826,109 @@
         <v>3</v>
       </c>
       <c r="D60" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="E60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F60" t="s">
-        <v>179</v>
+        <v>720</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>242</v>
+        <v>62</v>
       </c>
       <c r="C61">
         <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="E61">
-        <v>1</v>
-      </c>
-      <c r="F61" t="s">
-        <v>202</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B62" t="s">
-        <v>242</v>
+        <v>86</v>
       </c>
       <c r="C62">
         <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E62">
-        <v>2</v>
-      </c>
-      <c r="F62" t="s">
-        <v>203</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B63" t="s">
-        <v>242</v>
+        <v>86</v>
       </c>
       <c r="C63">
         <v>3</v>
       </c>
       <c r="D63" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E63">
         <v>2</v>
-      </c>
-      <c r="F63" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="B64" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="C64">
         <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E64">
         <v>3</v>
+      </c>
+      <c r="F64" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B65" t="s">
-        <v>701</v>
+        <v>242</v>
       </c>
       <c r="C65">
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E65">
         <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B66" t="s">
         <v>242</v>
@@ -3862,61 +3937,58 @@
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B67" t="s">
-        <v>632</v>
+        <v>242</v>
       </c>
       <c r="C67">
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E67">
         <v>2</v>
       </c>
       <c r="F67" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B68" t="s">
-        <v>702</v>
+        <v>86</v>
       </c>
       <c r="C68">
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E68">
-        <v>2</v>
-      </c>
-      <c r="F68" t="s">
-        <v>208</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B69" t="s">
-        <v>242</v>
+        <v>701</v>
       </c>
       <c r="C69">
         <v>3</v>
@@ -3925,75 +3997,75 @@
         <v>93</v>
       </c>
       <c r="E69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B70" t="s">
-        <v>703</v>
+        <v>242</v>
       </c>
       <c r="C70">
         <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E70">
         <v>1</v>
       </c>
       <c r="F70" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B71" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C71">
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B72" t="s">
-        <v>242</v>
+        <v>702</v>
       </c>
       <c r="C72">
         <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E72">
         <v>2</v>
       </c>
       <c r="F72" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B73" t="s">
         <v>242</v>
@@ -4002,21 +4074,21 @@
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E73">
         <v>3</v>
       </c>
       <c r="F73" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B74" t="s">
-        <v>242</v>
+        <v>703</v>
       </c>
       <c r="C74">
         <v>3</v>
@@ -4025,92 +4097,95 @@
         <v>99</v>
       </c>
       <c r="E74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F74" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="B75" t="s">
-        <v>242</v>
+        <v>633</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="E75">
         <v>1</v>
       </c>
       <c r="F75" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="B76" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="E76">
         <v>2</v>
+      </c>
+      <c r="F76" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="B77" t="s">
-        <v>635</v>
+        <v>242</v>
       </c>
       <c r="C77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="E77">
         <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="B78" t="s">
-        <v>704</v>
+        <v>242</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D78" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="E78">
         <v>3</v>
       </c>
       <c r="F78" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>618</v>
+        <v>65</v>
       </c>
       <c r="B79" t="s">
         <v>242</v>
@@ -4119,635 +4194,638 @@
         <v>2</v>
       </c>
       <c r="D79" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E79">
         <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>617</v>
+        <v>184</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>68</v>
+        <v>724</v>
       </c>
       <c r="B80" t="s">
-        <v>626</v>
+        <v>242</v>
       </c>
       <c r="C80">
         <v>2</v>
       </c>
       <c r="D80" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" t="s">
-        <v>187</v>
+        <v>726</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>70</v>
+        <v>725</v>
       </c>
       <c r="B81" t="s">
-        <v>705</v>
+        <v>242</v>
       </c>
       <c r="C81">
         <v>2</v>
       </c>
       <c r="D81" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E81">
         <v>2</v>
       </c>
       <c r="F81" t="s">
-        <v>188</v>
+        <v>727</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B82" t="s">
-        <v>655</v>
+        <v>635</v>
       </c>
       <c r="C82">
         <v>2</v>
       </c>
       <c r="D82" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E82">
         <v>3</v>
       </c>
       <c r="F82" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B83" t="s">
-        <v>627</v>
+        <v>704</v>
       </c>
       <c r="C83">
         <v>2</v>
       </c>
       <c r="D83" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F83" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>74</v>
+        <v>618</v>
       </c>
       <c r="B84" t="s">
-        <v>627</v>
+        <v>712</v>
       </c>
       <c r="C84">
         <v>2</v>
       </c>
       <c r="D84" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E84">
         <v>1</v>
       </c>
       <c r="F84" t="s">
-        <v>191</v>
+        <v>617</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B85" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="C85">
         <v>2</v>
       </c>
       <c r="D85" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F85" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>76</v>
+        <v>730</v>
       </c>
       <c r="B86" t="s">
-        <v>633</v>
+        <v>242</v>
       </c>
       <c r="C86">
         <v>2</v>
       </c>
       <c r="D86" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E86">
         <v>2</v>
       </c>
       <c r="F86" t="s">
-        <v>193</v>
+        <v>731</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B87" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C87">
         <v>2</v>
       </c>
       <c r="D87" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F87" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B88" t="s">
-        <v>629</v>
+        <v>655</v>
       </c>
       <c r="C88">
         <v>2</v>
       </c>
       <c r="D88" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E88">
         <v>3</v>
       </c>
       <c r="F88" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B89" t="s">
-        <v>242</v>
+        <v>627</v>
       </c>
       <c r="C89">
         <v>2</v>
       </c>
       <c r="D89" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E89">
         <v>1</v>
       </c>
       <c r="F89" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B90" t="s">
-        <v>242</v>
+        <v>627</v>
       </c>
       <c r="C90">
         <v>2</v>
       </c>
       <c r="D90" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E90">
         <v>1</v>
       </c>
       <c r="F90" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B91" t="s">
-        <v>655</v>
+        <v>634</v>
       </c>
       <c r="C91">
         <v>2</v>
       </c>
       <c r="D91" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E91">
         <v>2</v>
       </c>
       <c r="F91" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B92" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="C92">
         <v>2</v>
       </c>
       <c r="D92" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E92">
         <v>2</v>
       </c>
       <c r="F92" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B93" t="s">
-        <v>633</v>
+        <v>706</v>
       </c>
       <c r="C93">
         <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E93">
         <v>3</v>
       </c>
       <c r="F93" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B94" t="s">
-        <v>707</v>
+        <v>629</v>
       </c>
       <c r="C94">
         <v>2</v>
       </c>
       <c r="D94" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E94">
         <v>3</v>
       </c>
       <c r="F94" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B95" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="C95">
         <v>2</v>
       </c>
       <c r="D95" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="E95">
         <v>1</v>
+      </c>
+      <c r="F95" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="B96" t="s">
-        <v>708</v>
+        <v>242</v>
       </c>
       <c r="C96">
         <v>2</v>
       </c>
       <c r="D96" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="E96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F96" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="B97" t="s">
-        <v>709</v>
+        <v>655</v>
       </c>
       <c r="C97">
         <v>2</v>
       </c>
       <c r="D97" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="E97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F97" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="B98" t="s">
-        <v>242</v>
+        <v>627</v>
       </c>
       <c r="C98">
         <v>2</v>
       </c>
       <c r="D98" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="E98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F98" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="B99" t="s">
-        <v>705</v>
+        <v>633</v>
       </c>
       <c r="C99">
         <v>2</v>
       </c>
       <c r="D99" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="E99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F99" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="B100" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C100">
         <v>2</v>
       </c>
       <c r="D100" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="E100">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F100" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>111</v>
+        <v>736</v>
       </c>
       <c r="B101" t="s">
-        <v>663</v>
+        <v>242</v>
       </c>
       <c r="C101">
         <v>2</v>
       </c>
       <c r="D101" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F101" t="s">
-        <v>220</v>
+        <v>737</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B102" t="s">
-        <v>635</v>
+        <v>708</v>
       </c>
       <c r="C102">
         <v>2</v>
       </c>
       <c r="D102" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E102">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F102" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B103" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C103">
         <v>2</v>
       </c>
       <c r="D103" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E103">
         <v>3</v>
       </c>
       <c r="F103" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B104" t="s">
-        <v>661</v>
+        <v>242</v>
       </c>
       <c r="C104">
         <v>2</v>
       </c>
       <c r="D104" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="E104">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F104" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B105" t="s">
-        <v>242</v>
+        <v>705</v>
       </c>
       <c r="C105">
         <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F105" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B106" t="s">
-        <v>638</v>
+        <v>710</v>
       </c>
       <c r="C106">
         <v>2</v>
       </c>
       <c r="D106" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F106" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B107" t="s">
-        <v>712</v>
+        <v>663</v>
       </c>
       <c r="C107">
         <v>2</v>
       </c>
       <c r="D107" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E107">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F107" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B108" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C108">
         <v>2</v>
       </c>
       <c r="D108" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="E108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F108" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B109" t="s">
-        <v>242</v>
+        <v>711</v>
       </c>
       <c r="C109">
         <v>2</v>
       </c>
       <c r="D109" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="E109">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F109" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B110" t="s">
-        <v>707</v>
+        <v>661</v>
       </c>
       <c r="C110">
         <v>2</v>
       </c>
       <c r="D110" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E110">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F110" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B111" t="s">
         <v>242</v>
@@ -4756,198 +4834,213 @@
         <v>2</v>
       </c>
       <c r="D111" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B112" t="s">
-        <v>713</v>
+        <v>638</v>
       </c>
       <c r="C112">
         <v>2</v>
       </c>
       <c r="D112" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E112">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F112" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>242</v>
+        <v>712</v>
       </c>
       <c r="C113">
         <v>2</v>
       </c>
       <c r="D113" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E113">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F113" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>242</v>
+        <v>627</v>
       </c>
       <c r="C114">
         <v>2</v>
       </c>
       <c r="D114" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E114">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F114" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B115" t="s">
-        <v>682</v>
+        <v>242</v>
       </c>
       <c r="C115">
         <v>2</v>
       </c>
       <c r="D115" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E115">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F115" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="B116" t="s">
-        <v>86</v>
+        <v>707</v>
       </c>
       <c r="C116">
         <v>2</v>
       </c>
       <c r="D116" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E116">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F116" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="B117" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="C117">
         <v>2</v>
       </c>
       <c r="D117" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E117">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F117" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="B118" t="s">
-        <v>86</v>
+        <v>713</v>
       </c>
       <c r="C118">
         <v>2</v>
       </c>
       <c r="D118" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E118">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F118" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="B119" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="C119">
         <v>2</v>
       </c>
       <c r="D119" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E119">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F119" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="B120" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="C120">
         <v>2</v>
       </c>
       <c r="D120" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E120">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="F120" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>615</v>
+        <v>129</v>
       </c>
       <c r="B121" t="s">
-        <v>242</v>
+        <v>682</v>
       </c>
       <c r="C121">
         <v>2</v>
       </c>
       <c r="D121" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E121">
         <v>3</v>
       </c>
       <c r="F121" t="s">
-        <v>616</v>
+        <v>235</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4961,7 +5054,7 @@
         <v>2</v>
       </c>
       <c r="D122" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E122">
         <v>1</v>
@@ -4978,7 +5071,7 @@
         <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E123">
         <v>2</v>
@@ -4995,7 +5088,7 @@
         <v>2</v>
       </c>
       <c r="D124" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E124">
         <v>3</v>
@@ -5003,130 +5096,115 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>621</v>
+        <v>86</v>
       </c>
       <c r="B125" t="s">
-        <v>627</v>
+        <v>86</v>
       </c>
       <c r="C125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>1</v>
+        <v>131</v>
       </c>
       <c r="E125">
         <v>1</v>
-      </c>
-      <c r="F125" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>416</v>
+        <v>86</v>
       </c>
       <c r="B126" t="s">
-        <v>647</v>
+        <v>86</v>
       </c>
       <c r="C126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D126" t="s">
-        <v>1</v>
+        <v>131</v>
       </c>
       <c r="E126">
-        <v>1</v>
-      </c>
-      <c r="F126" t="s">
-        <v>582</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>414</v>
+        <v>615</v>
       </c>
       <c r="B127" t="s">
-        <v>636</v>
+        <v>242</v>
       </c>
       <c r="C127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D127" t="s">
-        <v>1</v>
+        <v>131</v>
       </c>
       <c r="E127">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F127" t="s">
-        <v>580</v>
+        <v>616</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>417</v>
+        <v>86</v>
       </c>
       <c r="B128" t="s">
-        <v>634</v>
+        <v>86</v>
       </c>
       <c r="C128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="E128">
-        <v>2</v>
-      </c>
-      <c r="F128" t="s">
-        <v>583</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>421</v>
+        <v>86</v>
       </c>
       <c r="B129" t="s">
-        <v>676</v>
+        <v>86</v>
       </c>
       <c r="C129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="E129">
         <v>2</v>
-      </c>
-      <c r="F129" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>424</v>
+        <v>86</v>
       </c>
       <c r="B130" t="s">
-        <v>675</v>
+        <v>86</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D130" t="s">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="E130">
-        <v>2</v>
-      </c>
-      <c r="F130" t="s">
-        <v>590</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>423</v>
+        <v>621</v>
       </c>
       <c r="B131" t="s">
-        <v>677</v>
+        <v>627</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -5135,18 +5213,18 @@
         <v>1</v>
       </c>
       <c r="E131">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>589</v>
+        <v>622</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B132" t="s">
-        <v>634</v>
+        <v>647</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -5155,18 +5233,18 @@
         <v>1</v>
       </c>
       <c r="E132">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F132" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B133" t="s">
-        <v>670</v>
+        <v>636</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -5175,18 +5253,18 @@
         <v>1</v>
       </c>
       <c r="E133">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F133" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B134" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -5195,18 +5273,18 @@
         <v>1</v>
       </c>
       <c r="E134">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F134" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B135" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -5215,18 +5293,18 @@
         <v>1</v>
       </c>
       <c r="E135">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F135" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>596</v>
+        <v>424</v>
       </c>
       <c r="B136" t="s">
-        <v>635</v>
+        <v>675</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -5235,138 +5313,138 @@
         <v>1</v>
       </c>
       <c r="E136">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F136" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>623</v>
+        <v>423</v>
       </c>
       <c r="B137" t="s">
-        <v>633</v>
+        <v>677</v>
       </c>
       <c r="C137">
         <v>1</v>
       </c>
       <c r="D137" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E137">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F137" t="s">
-        <v>624</v>
+        <v>589</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="B138" t="s">
-        <v>666</v>
+        <v>634</v>
       </c>
       <c r="C138">
         <v>1</v>
       </c>
       <c r="D138" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E138">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F138" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="B139" t="s">
-        <v>635</v>
+        <v>670</v>
       </c>
       <c r="C139">
         <v>1</v>
       </c>
       <c r="D139" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E139">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F139" t="s">
-        <v>572</v>
+        <v>586</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="B140" t="s">
-        <v>242</v>
+        <v>628</v>
       </c>
       <c r="C140">
         <v>1</v>
       </c>
       <c r="D140" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E140">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F140" t="s">
-        <v>571</v>
+        <v>585</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="B141" t="s">
-        <v>659</v>
+        <v>678</v>
       </c>
       <c r="C141">
         <v>1</v>
       </c>
       <c r="D141" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E141">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F141" t="s">
-        <v>575</v>
+        <v>588</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>408</v>
+        <v>596</v>
       </c>
       <c r="B142" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C142">
         <v>1</v>
       </c>
       <c r="D142" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E142">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F142" t="s">
-        <v>574</v>
+        <v>604</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>411</v>
+        <v>623</v>
       </c>
       <c r="B143" t="s">
-        <v>671</v>
+        <v>633</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -5375,18 +5453,18 @@
         <v>8</v>
       </c>
       <c r="E143">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F143" t="s">
-        <v>577</v>
+        <v>624</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B144" t="s">
-        <v>242</v>
+        <v>666</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -5395,18 +5473,18 @@
         <v>8</v>
       </c>
       <c r="E144">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F144" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="B145" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -5415,15 +5493,15 @@
         <v>8</v>
       </c>
       <c r="E145">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F145" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="B146" t="s">
         <v>242</v>
@@ -5435,18 +5513,18 @@
         <v>8</v>
       </c>
       <c r="E146">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F146" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B147" t="s">
-        <v>627</v>
+        <v>659</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -5455,138 +5533,138 @@
         <v>8</v>
       </c>
       <c r="E147">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F147" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="B148" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="C148">
         <v>1</v>
       </c>
       <c r="D148" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E148">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F148" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="B149" t="s">
-        <v>242</v>
+        <v>671</v>
       </c>
       <c r="C149">
         <v>1</v>
       </c>
       <c r="D149" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E149">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F149" t="s">
-        <v>563</v>
+        <v>577</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="B150" t="s">
-        <v>660</v>
+        <v>242</v>
       </c>
       <c r="C150">
         <v>1</v>
       </c>
       <c r="D150" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E150">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F150" t="s">
-        <v>562</v>
+        <v>576</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>597</v>
+        <v>415</v>
       </c>
       <c r="B151" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C151">
         <v>1</v>
       </c>
       <c r="D151" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E151">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F151" t="s">
-        <v>605</v>
+        <v>581</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="B152" t="s">
-        <v>645</v>
+        <v>242</v>
       </c>
       <c r="C152">
         <v>1</v>
       </c>
       <c r="D152" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E152">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F152" t="s">
-        <v>566</v>
+        <v>579</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="B153" t="s">
-        <v>714</v>
+        <v>627</v>
       </c>
       <c r="C153">
         <v>1</v>
       </c>
       <c r="D153" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E153">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F153" t="s">
-        <v>565</v>
+        <v>578</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B154" t="s">
-        <v>666</v>
+        <v>629</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -5595,18 +5673,18 @@
         <v>15</v>
       </c>
       <c r="E154">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F154" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="B155" t="s">
-        <v>627</v>
+        <v>242</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -5615,18 +5693,18 @@
         <v>15</v>
       </c>
       <c r="E155">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F155" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B156" t="s">
-        <v>634</v>
+        <v>660</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -5635,18 +5713,18 @@
         <v>15</v>
       </c>
       <c r="E156">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F156" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>402</v>
+        <v>597</v>
       </c>
       <c r="B157" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -5655,18 +5733,18 @@
         <v>15</v>
       </c>
       <c r="E157">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F157" t="s">
-        <v>568</v>
+        <v>605</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B158" t="s">
-        <v>242</v>
+        <v>645</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -5675,138 +5753,138 @@
         <v>15</v>
       </c>
       <c r="E158">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F158" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="B159" t="s">
-        <v>635</v>
+        <v>714</v>
       </c>
       <c r="C159">
         <v>1</v>
       </c>
       <c r="D159" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E159">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F159" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="B160" t="s">
-        <v>242</v>
+        <v>666</v>
       </c>
       <c r="C160">
         <v>1</v>
       </c>
       <c r="D160" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E160">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F160" t="s">
-        <v>550</v>
+        <v>564</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="B161" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="C161">
         <v>1</v>
       </c>
       <c r="D161" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E161">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F161" t="s">
-        <v>549</v>
+        <v>570</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="B162" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="C162">
         <v>1</v>
       </c>
       <c r="D162" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E162">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F162" t="s">
-        <v>548</v>
+        <v>569</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="B163" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C163">
         <v>1</v>
       </c>
       <c r="D163" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E163">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F163" t="s">
-        <v>554</v>
+        <v>568</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="B164" t="s">
-        <v>648</v>
+        <v>242</v>
       </c>
       <c r="C164">
         <v>1</v>
       </c>
       <c r="D164" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E164">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F164" t="s">
-        <v>553</v>
+        <v>567</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B165" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -5815,18 +5893,18 @@
         <v>23</v>
       </c>
       <c r="E165">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F165" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B166" t="s">
-        <v>635</v>
+        <v>242</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -5835,15 +5913,15 @@
         <v>23</v>
       </c>
       <c r="E166">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F166" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B167" t="s">
         <v>635</v>
@@ -5855,18 +5933,18 @@
         <v>23</v>
       </c>
       <c r="E167">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F167" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="B168" t="s">
-        <v>647</v>
+        <v>630</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -5875,18 +5953,18 @@
         <v>23</v>
       </c>
       <c r="E168">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F168" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B169" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -5895,18 +5973,18 @@
         <v>23</v>
       </c>
       <c r="E169">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F169" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B170" t="s">
-        <v>634</v>
+        <v>648</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -5915,18 +5993,18 @@
         <v>23</v>
       </c>
       <c r="E170">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F170" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B171" t="s">
-        <v>688</v>
+        <v>627</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -5935,138 +6013,138 @@
         <v>23</v>
       </c>
       <c r="E171">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F171" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="B172" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C172">
         <v>1</v>
       </c>
       <c r="D172" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E172">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F172" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="B173" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="C173">
         <v>1</v>
       </c>
       <c r="D173" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E173">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F173" t="s">
-        <v>536</v>
+        <v>552</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="B174" t="s">
-        <v>629</v>
+        <v>647</v>
       </c>
       <c r="C174">
         <v>1</v>
       </c>
       <c r="D174" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E174">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F174" t="s">
-        <v>540</v>
+        <v>560</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="B175" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="C175">
         <v>1</v>
       </c>
       <c r="D175" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E175">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F175" t="s">
-        <v>539</v>
+        <v>559</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="B176" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="C176">
         <v>1</v>
       </c>
       <c r="D176" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E176">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F176" t="s">
-        <v>538</v>
+        <v>558</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="B177" t="s">
-        <v>628</v>
+        <v>688</v>
       </c>
       <c r="C177">
         <v>1</v>
       </c>
       <c r="D177" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E177">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F177" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B178" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -6075,18 +6153,18 @@
         <v>29</v>
       </c>
       <c r="E178">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F178" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B179" t="s">
-        <v>660</v>
+        <v>645</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -6095,18 +6173,18 @@
         <v>29</v>
       </c>
       <c r="E179">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F179" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B180" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -6115,18 +6193,18 @@
         <v>29</v>
       </c>
       <c r="E180">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F180" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="B181" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -6135,18 +6213,18 @@
         <v>29</v>
       </c>
       <c r="E181">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F181" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B182" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -6155,18 +6233,18 @@
         <v>29</v>
       </c>
       <c r="E182">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F182" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B183" t="s">
-        <v>661</v>
+        <v>628</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -6175,15 +6253,15 @@
         <v>29</v>
       </c>
       <c r="E183">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F183" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="B184" t="s">
         <v>629</v>
@@ -6192,118 +6270,118 @@
         <v>1</v>
       </c>
       <c r="D184" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E184">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F184" t="s">
-        <v>529</v>
+        <v>543</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="B185" t="s">
-        <v>629</v>
+        <v>660</v>
       </c>
       <c r="C185">
         <v>1</v>
       </c>
       <c r="D185" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E185">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F185" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="B186" t="s">
-        <v>659</v>
+        <v>634</v>
       </c>
       <c r="C186">
         <v>1</v>
       </c>
       <c r="D186" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E186">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F186" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="B187" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C187">
         <v>1</v>
       </c>
       <c r="D187" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E187">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F187" t="s">
-        <v>531</v>
+        <v>547</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="B188" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="C188">
         <v>1</v>
       </c>
       <c r="D188" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E188">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F188" t="s">
-        <v>530</v>
+        <v>546</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="B189" t="s">
-        <v>629</v>
+        <v>661</v>
       </c>
       <c r="C189">
         <v>1</v>
       </c>
       <c r="D189" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E189">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F189" t="s">
-        <v>535</v>
+        <v>545</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="B190" t="s">
         <v>629</v>
@@ -6315,15 +6393,15 @@
         <v>32</v>
       </c>
       <c r="E190">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F190" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="B191" t="s">
         <v>629</v>
@@ -6335,18 +6413,18 @@
         <v>32</v>
       </c>
       <c r="E191">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F191" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="B192" t="s">
-        <v>715</v>
+        <v>659</v>
       </c>
       <c r="C192">
         <v>1</v>
@@ -6355,18 +6433,18 @@
         <v>32</v>
       </c>
       <c r="E192">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F192" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B193" t="s">
-        <v>690</v>
+        <v>627</v>
       </c>
       <c r="C193">
         <v>1</v>
@@ -6375,55 +6453,55 @@
         <v>32</v>
       </c>
       <c r="E193">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F193" t="s">
-        <v>689</v>
+        <v>531</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="B194" t="s">
-        <v>641</v>
+        <v>627</v>
       </c>
       <c r="C194">
         <v>1</v>
       </c>
       <c r="D194" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E194">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F194" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="B195" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="C195">
         <v>1</v>
       </c>
       <c r="D195" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E195">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F195" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="B196" t="s">
         <v>629</v>
@@ -6432,81 +6510,81 @@
         <v>1</v>
       </c>
       <c r="D196" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E196">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F196" t="s">
-        <v>518</v>
+        <v>534</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="B197" t="s">
-        <v>687</v>
+        <v>629</v>
       </c>
       <c r="C197">
         <v>1</v>
       </c>
       <c r="D197" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E197">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F197" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B198" t="s">
-        <v>649</v>
+        <v>715</v>
       </c>
       <c r="C198">
         <v>1</v>
       </c>
       <c r="D198" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E198">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F198" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="B199" t="s">
-        <v>635</v>
+        <v>690</v>
       </c>
       <c r="C199">
         <v>1</v>
       </c>
       <c r="D199" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E199">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F199" t="s">
-        <v>521</v>
+        <v>689</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="B200" t="s">
-        <v>658</v>
+        <v>641</v>
       </c>
       <c r="C200">
         <v>1</v>
@@ -6514,19 +6592,19 @@
       <c r="D200" t="s">
         <v>38</v>
       </c>
-      <c r="E200" t="s">
-        <v>612</v>
+      <c r="E200">
+        <v>1</v>
       </c>
       <c r="F200" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B201" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
       <c r="C201">
         <v>1</v>
@@ -6534,19 +6612,19 @@
       <c r="D201" t="s">
         <v>38</v>
       </c>
-      <c r="E201" t="s">
-        <v>612</v>
+      <c r="E201">
+        <v>1</v>
       </c>
       <c r="F201" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B202" t="s">
-        <v>656</v>
+        <v>629</v>
       </c>
       <c r="C202">
         <v>1</v>
@@ -6554,139 +6632,139 @@
       <c r="D202" t="s">
         <v>38</v>
       </c>
-      <c r="E202" t="s">
-        <v>612</v>
+      <c r="E202">
+        <v>1</v>
       </c>
       <c r="F202" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="B203" t="s">
-        <v>635</v>
+        <v>687</v>
       </c>
       <c r="C203">
         <v>1</v>
       </c>
       <c r="D203" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E203">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F203" t="s">
-        <v>508</v>
+        <v>523</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="B204" t="s">
-        <v>629</v>
+        <v>649</v>
       </c>
       <c r="C204">
         <v>1</v>
       </c>
       <c r="D204" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E204">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F204" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="B205" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="C205">
         <v>1</v>
       </c>
       <c r="D205" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E205">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F205" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="B206" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C206">
         <v>1</v>
       </c>
       <c r="D206" t="s">
-        <v>44</v>
-      </c>
-      <c r="E206">
-        <v>2</v>
+        <v>38</v>
+      </c>
+      <c r="E206" t="s">
+        <v>612</v>
       </c>
       <c r="F206" t="s">
-        <v>511</v>
+        <v>526</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="B207" t="s">
-        <v>635</v>
+        <v>657</v>
       </c>
       <c r="C207">
         <v>1</v>
       </c>
       <c r="D207" t="s">
-        <v>44</v>
-      </c>
-      <c r="E207">
-        <v>2</v>
+        <v>38</v>
+      </c>
+      <c r="E207" t="s">
+        <v>612</v>
       </c>
       <c r="F207" t="s">
-        <v>510</v>
+        <v>525</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="B208" t="s">
-        <v>635</v>
+        <v>656</v>
       </c>
       <c r="C208">
         <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>44</v>
-      </c>
-      <c r="E208">
-        <v>2</v>
+        <v>38</v>
+      </c>
+      <c r="E208" t="s">
+        <v>612</v>
       </c>
       <c r="F208" t="s">
-        <v>509</v>
+        <v>524</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B209" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C209">
         <v>1</v>
@@ -6695,18 +6773,18 @@
         <v>44</v>
       </c>
       <c r="E209">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F209" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B210" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C210">
         <v>1</v>
@@ -6715,18 +6793,18 @@
         <v>44</v>
       </c>
       <c r="E210">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F210" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B211" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="C211">
         <v>1</v>
@@ -6735,18 +6813,18 @@
         <v>44</v>
       </c>
       <c r="E211">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F211" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B212" t="s">
-        <v>630</v>
+        <v>654</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -6755,18 +6833,18 @@
         <v>44</v>
       </c>
       <c r="E212">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F212" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="B213" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C213">
         <v>1</v>
@@ -6775,18 +6853,18 @@
         <v>44</v>
       </c>
       <c r="E213">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F213" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B214" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C214">
         <v>1</v>
@@ -6795,115 +6873,115 @@
         <v>44</v>
       </c>
       <c r="E214">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F214" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="B215" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C215">
         <v>1</v>
       </c>
       <c r="D215" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E215">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F215" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="B216" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="C216">
         <v>1</v>
       </c>
       <c r="D216" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E216">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F216" t="s">
-        <v>496</v>
+        <v>513</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="B217" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="C217">
         <v>1</v>
       </c>
       <c r="D217" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E217">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F217" t="s">
-        <v>495</v>
+        <v>512</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
       <c r="B218" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="C218">
         <v>1</v>
       </c>
       <c r="D218" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E218">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F218" t="s">
-        <v>494</v>
+        <v>517</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="B219" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C219">
         <v>1</v>
       </c>
       <c r="D219" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E219">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F219" t="s">
-        <v>500</v>
+        <v>516</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="B220" t="s">
         <v>629</v>
@@ -6912,21 +6990,21 @@
         <v>1</v>
       </c>
       <c r="D220" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E220">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F220" t="s">
-        <v>499</v>
+        <v>515</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B221" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -6935,18 +7013,18 @@
         <v>50</v>
       </c>
       <c r="E221">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F221" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B222" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -6955,18 +7033,18 @@
         <v>50</v>
       </c>
       <c r="E222">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F222" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B223" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="C223">
         <v>1</v>
@@ -6975,15 +7053,15 @@
         <v>50</v>
       </c>
       <c r="E223">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F223" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="B224" t="s">
         <v>635</v>
@@ -6995,18 +7073,18 @@
         <v>50</v>
       </c>
       <c r="E224">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F224" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B225" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C225">
         <v>1</v>
@@ -7015,18 +7093,18 @@
         <v>50</v>
       </c>
       <c r="E225">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F225" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B226" t="s">
-        <v>686</v>
+        <v>629</v>
       </c>
       <c r="C226">
         <v>1</v>
@@ -7035,55 +7113,55 @@
         <v>50</v>
       </c>
       <c r="E226">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F226" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="B227" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="C227">
         <v>1</v>
       </c>
       <c r="D227" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E227">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F227" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="B228" t="s">
-        <v>635</v>
+        <v>659</v>
       </c>
       <c r="C228">
         <v>1</v>
       </c>
       <c r="D228" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E228">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F228" t="s">
-        <v>480</v>
+        <v>502</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="B229" t="s">
         <v>635</v>
@@ -7092,18 +7170,18 @@
         <v>1</v>
       </c>
       <c r="D229" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E229">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F229" t="s">
-        <v>479</v>
+        <v>501</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="B230" t="s">
         <v>635</v>
@@ -7112,58 +7190,58 @@
         <v>1</v>
       </c>
       <c r="D230" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E230">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F230" t="s">
-        <v>478</v>
+        <v>505</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="B231" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C231">
         <v>1</v>
       </c>
       <c r="D231" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E231">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F231" t="s">
-        <v>485</v>
+        <v>504</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="B232" t="s">
-        <v>640</v>
+        <v>686</v>
       </c>
       <c r="C232">
         <v>1</v>
       </c>
       <c r="D232" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E232">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F232" t="s">
-        <v>484</v>
+        <v>503</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B233" t="s">
         <v>635</v>
@@ -7175,18 +7253,18 @@
         <v>54</v>
       </c>
       <c r="E233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F233" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B234" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -7195,15 +7273,15 @@
         <v>54</v>
       </c>
       <c r="E234">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F234" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B235" t="s">
         <v>635</v>
@@ -7215,18 +7293,18 @@
         <v>54</v>
       </c>
       <c r="E235">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F235" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="B236" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -7235,18 +7313,18 @@
         <v>54</v>
       </c>
       <c r="E236">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F236" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B237" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -7255,18 +7333,18 @@
         <v>54</v>
       </c>
       <c r="E237">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F237" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B238" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -7275,15 +7353,15 @@
         <v>54</v>
       </c>
       <c r="E238">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F238" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B239" t="s">
         <v>635</v>
@@ -7295,18 +7373,18 @@
         <v>54</v>
       </c>
       <c r="E239">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F239" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B240" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -7315,18 +7393,18 @@
         <v>54</v>
       </c>
       <c r="E240">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F240" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B241" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -7335,18 +7413,18 @@
         <v>54</v>
       </c>
       <c r="E241">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F241" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B242" t="s">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -7355,138 +7433,138 @@
         <v>54</v>
       </c>
       <c r="E242">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F242" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="B243" t="s">
-        <v>635</v>
+        <v>649</v>
       </c>
       <c r="C243">
         <v>1</v>
       </c>
       <c r="D243" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E243">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F243" t="s">
-        <v>465</v>
+        <v>489</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>297</v>
+        <v>321</v>
       </c>
       <c r="B244" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="C244">
         <v>1</v>
       </c>
       <c r="D244" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E244">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F244" t="s">
-        <v>464</v>
+        <v>488</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="B245" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="C245">
         <v>1</v>
       </c>
       <c r="D245" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E245">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F245" t="s">
-        <v>463</v>
+        <v>487</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="B246" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="C246">
         <v>1</v>
       </c>
       <c r="D246" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E246">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F246" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="B247" t="s">
-        <v>647</v>
+        <v>629</v>
       </c>
       <c r="C247">
         <v>1</v>
       </c>
       <c r="D247" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E247">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F247" t="s">
-        <v>468</v>
+        <v>493</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="B248" t="s">
-        <v>629</v>
+        <v>650</v>
       </c>
       <c r="C248">
         <v>1</v>
       </c>
       <c r="D248" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E248">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F248" t="s">
-        <v>467</v>
+        <v>492</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B249" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -7495,18 +7573,18 @@
         <v>59</v>
       </c>
       <c r="E249">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F249" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="B250" t="s">
-        <v>629</v>
+        <v>645</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -7515,18 +7593,18 @@
         <v>59</v>
       </c>
       <c r="E250">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F250" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B251" t="s">
-        <v>629</v>
+        <v>644</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -7535,18 +7613,18 @@
         <v>59</v>
       </c>
       <c r="E251">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F251" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B252" t="s">
-        <v>629</v>
+        <v>648</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -7555,18 +7633,18 @@
         <v>59</v>
       </c>
       <c r="E252">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F252" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B253" t="s">
-        <v>629</v>
+        <v>647</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -7575,18 +7653,18 @@
         <v>59</v>
       </c>
       <c r="E253">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F253" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="B254" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -7595,18 +7673,18 @@
         <v>59</v>
       </c>
       <c r="E254">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F254" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="B255" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -7615,15 +7693,15 @@
         <v>59</v>
       </c>
       <c r="E255">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F255" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B256" t="s">
         <v>629</v>
@@ -7635,18 +7713,18 @@
         <v>59</v>
       </c>
       <c r="E256">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F256" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B257" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -7655,55 +7733,55 @@
         <v>59</v>
       </c>
       <c r="E257">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F257" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="B258" t="s">
-        <v>663</v>
+        <v>629</v>
       </c>
       <c r="C258">
         <v>1</v>
       </c>
       <c r="D258" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E258">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F258" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="B259" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C259">
         <v>1</v>
       </c>
       <c r="D259" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E259">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F259" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="B260" t="s">
         <v>635</v>
@@ -7712,18 +7790,18 @@
         <v>1</v>
       </c>
       <c r="D260" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E260">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F260" t="s">
-        <v>453</v>
+        <v>477</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="B261" t="s">
         <v>635</v>
@@ -7732,61 +7810,61 @@
         <v>1</v>
       </c>
       <c r="D261" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E261">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F261" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="B262" t="s">
-        <v>684</v>
+        <v>629</v>
       </c>
       <c r="C262">
         <v>1</v>
       </c>
       <c r="D262" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E262">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F262" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="B263" t="s">
-        <v>634</v>
+        <v>645</v>
       </c>
       <c r="C263">
         <v>1</v>
       </c>
       <c r="D263" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E263">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F263" t="s">
-        <v>456</v>
+        <v>474</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>603</v>
+        <v>288</v>
       </c>
       <c r="B264" t="s">
-        <v>242</v>
+        <v>663</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -7795,18 +7873,18 @@
         <v>63</v>
       </c>
       <c r="E264">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F264" t="s">
-        <v>611</v>
+        <v>455</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B265" t="s">
-        <v>242</v>
+        <v>631</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -7815,15 +7893,15 @@
         <v>63</v>
       </c>
       <c r="E265">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F265" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B266" t="s">
         <v>635</v>
@@ -7835,18 +7913,18 @@
         <v>63</v>
       </c>
       <c r="E266">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F266" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B267" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -7855,18 +7933,18 @@
         <v>63</v>
       </c>
       <c r="E267">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F267" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B268" t="s">
-        <v>647</v>
+        <v>684</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -7875,138 +7953,138 @@
         <v>63</v>
       </c>
       <c r="E268">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F268" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B269" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C269">
         <v>1</v>
       </c>
       <c r="D269" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E269">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F269" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>680</v>
+        <v>603</v>
       </c>
       <c r="B270" t="s">
-        <v>635</v>
+        <v>242</v>
       </c>
       <c r="C270">
         <v>1</v>
       </c>
       <c r="D270" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E270">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F270" t="s">
-        <v>681</v>
+        <v>611</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B271" t="s">
-        <v>684</v>
+        <v>242</v>
       </c>
       <c r="C271">
         <v>1</v>
       </c>
       <c r="D271" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E271">
         <v>3</v>
       </c>
       <c r="F271" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="B272" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C272">
         <v>1</v>
       </c>
       <c r="D272" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E272">
         <v>3</v>
       </c>
       <c r="F272" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="B273" t="s">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="C273">
         <v>1</v>
       </c>
       <c r="D273" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E273">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F273" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>425</v>
+        <v>294</v>
       </c>
       <c r="B274" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C274">
         <v>1</v>
       </c>
       <c r="D274" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E274">
         <v>4</v>
       </c>
       <c r="F274" t="s">
-        <v>591</v>
+        <v>461</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>592</v>
+        <v>280</v>
       </c>
       <c r="B275" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -8015,18 +8093,18 @@
         <v>64</v>
       </c>
       <c r="E275">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F275" t="s">
-        <v>593</v>
+        <v>447</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>285</v>
+        <v>680</v>
       </c>
       <c r="B276" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C276">
         <v>1</v>
@@ -8035,18 +8113,18 @@
         <v>64</v>
       </c>
       <c r="E276">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F276" t="s">
-        <v>452</v>
+        <v>681</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B277" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -8055,138 +8133,138 @@
         <v>64</v>
       </c>
       <c r="E277">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F277" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B278" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="C278">
         <v>1</v>
       </c>
       <c r="D278" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E278">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F278" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B279" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C279">
         <v>1</v>
       </c>
       <c r="D279" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E279">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F279" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>272</v>
+        <v>425</v>
       </c>
       <c r="B280" t="s">
-        <v>633</v>
+        <v>643</v>
       </c>
       <c r="C280">
         <v>1</v>
       </c>
       <c r="D280" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E280">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F280" t="s">
-        <v>439</v>
+        <v>591</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>276</v>
+        <v>592</v>
       </c>
       <c r="B281" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="C281">
         <v>1</v>
       </c>
       <c r="D281" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E281">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F281" t="s">
-        <v>443</v>
+        <v>593</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="B282" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C282">
         <v>1</v>
       </c>
       <c r="D282" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E282">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F282" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>600</v>
+        <v>284</v>
       </c>
       <c r="B283" t="s">
-        <v>630</v>
+        <v>685</v>
       </c>
       <c r="C283">
         <v>1</v>
       </c>
       <c r="D283" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E283">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F283" t="s">
-        <v>608</v>
+        <v>451</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>599</v>
+        <v>274</v>
       </c>
       <c r="B284" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C284">
         <v>1</v>
@@ -8195,18 +8273,18 @@
         <v>69</v>
       </c>
       <c r="E284">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F284" t="s">
-        <v>607</v>
+        <v>441</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B285" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C285">
         <v>1</v>
@@ -8215,18 +8293,18 @@
         <v>69</v>
       </c>
       <c r="E285">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F285" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B286" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="C286">
         <v>1</v>
@@ -8235,18 +8313,18 @@
         <v>69</v>
       </c>
       <c r="E286">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F286" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>601</v>
+        <v>276</v>
       </c>
       <c r="B287" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -8255,15 +8333,15 @@
         <v>69</v>
       </c>
       <c r="E287">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F287" t="s">
-        <v>609</v>
+        <v>443</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B288" t="s">
         <v>638</v>
@@ -8275,15 +8353,15 @@
         <v>69</v>
       </c>
       <c r="E288">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F288" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="B289" t="s">
         <v>630</v>
@@ -8295,18 +8373,18 @@
         <v>69</v>
       </c>
       <c r="E289">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F289" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>271</v>
+        <v>599</v>
       </c>
       <c r="B290" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -8315,138 +8393,138 @@
         <v>69</v>
       </c>
       <c r="E290">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F290" t="s">
-        <v>438</v>
+        <v>607</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="B291" t="s">
-        <v>683</v>
+        <v>635</v>
       </c>
       <c r="C291">
         <v>1</v>
       </c>
       <c r="D291" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E291">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F291" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>598</v>
+        <v>277</v>
       </c>
       <c r="B292" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="C292">
         <v>1</v>
       </c>
       <c r="D292" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E292">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F292" t="s">
-        <v>606</v>
+        <v>444</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>263</v>
+        <v>601</v>
       </c>
       <c r="B293" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C293">
         <v>1</v>
       </c>
       <c r="D293" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E293">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F293" t="s">
-        <v>430</v>
+        <v>609</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="B294" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C294">
         <v>1</v>
       </c>
       <c r="D294" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E294">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F294" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>266</v>
+        <v>620</v>
       </c>
       <c r="B295" t="s">
-        <v>647</v>
+        <v>630</v>
       </c>
       <c r="C295">
         <v>1</v>
       </c>
       <c r="D295" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E295">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F295" t="s">
-        <v>433</v>
+        <v>619</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B296" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="C296">
         <v>1</v>
       </c>
       <c r="D296" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E296">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F296" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B297" t="s">
-        <v>638</v>
+        <v>683</v>
       </c>
       <c r="C297">
         <v>1</v>
@@ -8455,18 +8533,18 @@
         <v>73</v>
       </c>
       <c r="E297">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F297" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>269</v>
+        <v>598</v>
       </c>
       <c r="B298" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C298">
         <v>1</v>
@@ -8475,18 +8553,18 @@
         <v>73</v>
       </c>
       <c r="E298">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F298" t="s">
-        <v>436</v>
+        <v>606</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B299" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="C299">
         <v>1</v>
@@ -8495,18 +8573,18 @@
         <v>73</v>
       </c>
       <c r="E299">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F299" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>123</v>
+        <v>267</v>
       </c>
       <c r="B300" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C300">
         <v>1</v>
@@ -8515,135 +8593,135 @@
         <v>73</v>
       </c>
       <c r="E300">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F300" t="s">
-        <v>230</v>
+        <v>434</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="B301" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="C301">
         <v>1</v>
       </c>
       <c r="D301" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E301">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F301" t="s">
-        <v>253</v>
+        <v>433</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="B302" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C302">
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E302">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F302" t="s">
-        <v>252</v>
+        <v>432</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="B303" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="C303">
         <v>1</v>
       </c>
       <c r="D303" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E303">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F303" t="s">
-        <v>244</v>
+        <v>437</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="B304" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C304">
         <v>1</v>
       </c>
       <c r="D304" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E304">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F304" t="s">
-        <v>256</v>
+        <v>436</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="B305" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="C305">
         <v>1</v>
       </c>
       <c r="D305" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E305">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F305" t="s">
-        <v>255</v>
+        <v>435</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>247</v>
+        <v>123</v>
       </c>
       <c r="B306" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C306">
         <v>1</v>
       </c>
       <c r="D306" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E306">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F306" t="s">
-        <v>254</v>
+        <v>230</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B307" t="s">
         <v>635</v>
@@ -8655,18 +8733,18 @@
         <v>80</v>
       </c>
       <c r="E307">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F307" t="s">
-        <v>426</v>
+        <v>253</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>602</v>
+        <v>245</v>
       </c>
       <c r="B308" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="C308">
         <v>1</v>
@@ -8675,18 +8753,18 @@
         <v>80</v>
       </c>
       <c r="E308">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F308" t="s">
-        <v>610</v>
+        <v>252</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B309" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -8695,18 +8773,18 @@
         <v>80</v>
       </c>
       <c r="E309">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F309" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B310" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C310">
         <v>1</v>
@@ -8715,18 +8793,18 @@
         <v>80</v>
       </c>
       <c r="E310">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F310" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="B311" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C311">
         <v>1</v>
@@ -8735,18 +8813,18 @@
         <v>80</v>
       </c>
       <c r="E311">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F311" t="s">
-        <v>429</v>
+        <v>255</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="B312" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C312">
         <v>1</v>
@@ -8755,18 +8833,18 @@
         <v>80</v>
       </c>
       <c r="E312">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F312" t="s">
-        <v>428</v>
+        <v>254</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B313" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -8775,26 +8853,146 @@
         <v>80</v>
       </c>
       <c r="E313">
+        <v>3</v>
+      </c>
+      <c r="F313" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>602</v>
+      </c>
+      <c r="B314" t="s">
+        <v>640</v>
+      </c>
+      <c r="C314">
+        <v>1</v>
+      </c>
+      <c r="D314" t="s">
+        <v>80</v>
+      </c>
+      <c r="E314">
+        <v>3</v>
+      </c>
+      <c r="F314" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>251</v>
+      </c>
+      <c r="B315" t="s">
+        <v>633</v>
+      </c>
+      <c r="C315">
+        <v>1</v>
+      </c>
+      <c r="D315" t="s">
+        <v>80</v>
+      </c>
+      <c r="E315">
+        <v>3</v>
+      </c>
+      <c r="F315" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>250</v>
+      </c>
+      <c r="B316" t="s">
+        <v>635</v>
+      </c>
+      <c r="C316">
+        <v>1</v>
+      </c>
+      <c r="D316" t="s">
+        <v>80</v>
+      </c>
+      <c r="E316">
+        <v>3</v>
+      </c>
+      <c r="F316" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>262</v>
+      </c>
+      <c r="B317" t="s">
+        <v>639</v>
+      </c>
+      <c r="C317">
+        <v>1</v>
+      </c>
+      <c r="D317" t="s">
+        <v>80</v>
+      </c>
+      <c r="E317">
         <v>4</v>
       </c>
-      <c r="F313" t="s">
+      <c r="F317" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>261</v>
+      </c>
+      <c r="B318" t="s">
+        <v>639</v>
+      </c>
+      <c r="C318">
+        <v>1</v>
+      </c>
+      <c r="D318" t="s">
+        <v>80</v>
+      </c>
+      <c r="E318">
+        <v>4</v>
+      </c>
+      <c r="F318" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>260</v>
+      </c>
+      <c r="B319" t="s">
+        <v>629</v>
+      </c>
+      <c r="C319">
+        <v>1</v>
+      </c>
+      <c r="D319" t="s">
+        <v>80</v>
+      </c>
+      <c r="E319">
+        <v>4</v>
+      </c>
+      <c r="F319" t="s">
         <v>427</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F313" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F313">
-      <sortCondition descending="1" ref="C2:C313"/>
-      <sortCondition ref="D2:D313"/>
-      <sortCondition ref="E2:E313"/>
-      <sortCondition descending="1" ref="A2:A313"/>
+  <autoFilter ref="A1:F319" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F319">
+      <sortCondition descending="1" ref="C2:C319"/>
+      <sortCondition ref="D2:D319"/>
+      <sortCondition ref="E2:E319"/>
+      <sortCondition descending="1" ref="A2:A319"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F312">
-    <sortCondition descending="1" ref="C2:C312"/>
-    <sortCondition ref="D2:D312"/>
-    <sortCondition ref="E2:E312"/>
-    <sortCondition descending="1" ref="A2:A312"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F318">
+    <sortCondition descending="1" ref="C2:C318"/>
+    <sortCondition ref="D2:D318"/>
+    <sortCondition ref="E2:E318"/>
+    <sortCondition descending="1" ref="A2:A318"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\BECARIO PROCESOS\EOAT PROJECT\Inventario_repo_v3\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1D1F16-7B66-40EE-AF0F-DE0160BBC991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3552635C-92B1-4ABB-A23B-D3BECA88CD06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$319</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$322</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="750">
   <si>
     <t>I-1937</t>
   </si>
@@ -2253,6 +2253,42 @@
   </si>
   <si>
     <t>I-1947.jpeg</t>
+  </si>
+  <si>
+    <t>I-1953</t>
+  </si>
+  <si>
+    <t>I-1955</t>
+  </si>
+  <si>
+    <t>I-1953.jpeg</t>
+  </si>
+  <si>
+    <t>I-1955.jpeg</t>
+  </si>
+  <si>
+    <t>I-1959</t>
+  </si>
+  <si>
+    <t>I-1959.jpeg</t>
+  </si>
+  <si>
+    <t>I-1962</t>
+  </si>
+  <si>
+    <t>I-1963</t>
+  </si>
+  <si>
+    <t>I-1962.jpeg</t>
+  </si>
+  <si>
+    <t>I-1963.jpeg</t>
+  </si>
+  <si>
+    <t>I-1964</t>
+  </si>
+  <si>
+    <t>I-1964.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2630,7 +2666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-  <dimension ref="A1:F319"/>
+  <dimension ref="A1:F322"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -3854,10 +3890,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>86</v>
+        <v>738</v>
       </c>
       <c r="B62" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="C62">
         <v>3</v>
@@ -3868,13 +3904,16 @@
       <c r="E62">
         <v>1</v>
       </c>
+      <c r="F62" t="s">
+        <v>740</v>
+      </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>86</v>
+        <v>739</v>
       </c>
       <c r="B63" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="C63">
         <v>3</v>
@@ -3883,12 +3922,15 @@
         <v>87</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>748</v>
       </c>
       <c r="B64" t="s">
         <v>242</v>
@@ -3900,15 +3942,15 @@
         <v>87</v>
       </c>
       <c r="E64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F64" t="s">
-        <v>179</v>
+        <v>749</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="B65" t="s">
         <v>242</v>
@@ -3917,18 +3959,18 @@
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B66" t="s">
         <v>242</v>
@@ -3940,15 +3982,15 @@
         <v>89</v>
       </c>
       <c r="E66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F66" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B67" t="s">
         <v>242</v>
@@ -3963,15 +4005,15 @@
         <v>2</v>
       </c>
       <c r="F67" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B68" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="C68">
         <v>3</v>
@@ -3980,35 +4022,35 @@
         <v>89</v>
       </c>
       <c r="E68">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="F68" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B69" t="s">
-        <v>701</v>
+        <v>86</v>
       </c>
       <c r="C69">
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E69">
-        <v>1</v>
-      </c>
-      <c r="F69" t="s">
-        <v>205</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B70" t="s">
-        <v>242</v>
+        <v>701</v>
       </c>
       <c r="C70">
         <v>3</v>
@@ -4020,15 +4062,15 @@
         <v>1</v>
       </c>
       <c r="F70" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B71" t="s">
-        <v>632</v>
+        <v>242</v>
       </c>
       <c r="C71">
         <v>3</v>
@@ -4037,18 +4079,18 @@
         <v>93</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F71" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B72" t="s">
-        <v>702</v>
+        <v>632</v>
       </c>
       <c r="C72">
         <v>3</v>
@@ -4060,15 +4102,15 @@
         <v>2</v>
       </c>
       <c r="F72" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B73" t="s">
-        <v>242</v>
+        <v>702</v>
       </c>
       <c r="C73">
         <v>3</v>
@@ -4077,38 +4119,38 @@
         <v>93</v>
       </c>
       <c r="E73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F73" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B74" t="s">
-        <v>703</v>
+        <v>242</v>
       </c>
       <c r="C74">
         <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F74" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B75" t="s">
-        <v>633</v>
+        <v>703</v>
       </c>
       <c r="C75">
         <v>3</v>
@@ -4120,15 +4162,15 @@
         <v>1</v>
       </c>
       <c r="F75" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B76" t="s">
-        <v>242</v>
+        <v>633</v>
       </c>
       <c r="C76">
         <v>3</v>
@@ -4137,15 +4179,15 @@
         <v>99</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B77" t="s">
         <v>242</v>
@@ -4157,15 +4199,15 @@
         <v>99</v>
       </c>
       <c r="E77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F77" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B78" t="s">
         <v>242</v>
@@ -4180,32 +4222,32 @@
         <v>3</v>
       </c>
       <c r="F78" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="B79" t="s">
         <v>242</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F79" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>724</v>
+        <v>65</v>
       </c>
       <c r="B80" t="s">
         <v>242</v>
@@ -4217,15 +4259,15 @@
         <v>64</v>
       </c>
       <c r="E80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80" t="s">
-        <v>726</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B81" t="s">
         <v>242</v>
@@ -4240,15 +4282,15 @@
         <v>2</v>
       </c>
       <c r="F81" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>66</v>
+        <v>725</v>
       </c>
       <c r="B82" t="s">
-        <v>635</v>
+        <v>242</v>
       </c>
       <c r="C82">
         <v>2</v>
@@ -4257,18 +4299,18 @@
         <v>64</v>
       </c>
       <c r="E82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F82" t="s">
-        <v>185</v>
+        <v>727</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B83" t="s">
-        <v>704</v>
+        <v>635</v>
       </c>
       <c r="C83">
         <v>2</v>
@@ -4280,35 +4322,35 @@
         <v>3</v>
       </c>
       <c r="F83" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>618</v>
+        <v>67</v>
       </c>
       <c r="B84" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="C84">
         <v>2</v>
       </c>
       <c r="D84" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F84" t="s">
-        <v>617</v>
+        <v>186</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>68</v>
+        <v>618</v>
       </c>
       <c r="B85" t="s">
-        <v>626</v>
+        <v>712</v>
       </c>
       <c r="C85">
         <v>2</v>
@@ -4320,15 +4362,15 @@
         <v>1</v>
       </c>
       <c r="F85" t="s">
-        <v>187</v>
+        <v>617</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>730</v>
+        <v>68</v>
       </c>
       <c r="B86" t="s">
-        <v>242</v>
+        <v>626</v>
       </c>
       <c r="C86">
         <v>2</v>
@@ -4337,18 +4379,18 @@
         <v>69</v>
       </c>
       <c r="E86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F86" t="s">
-        <v>731</v>
+        <v>187</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>70</v>
+        <v>730</v>
       </c>
       <c r="B87" t="s">
-        <v>705</v>
+        <v>242</v>
       </c>
       <c r="C87">
         <v>2</v>
@@ -4360,15 +4402,15 @@
         <v>2</v>
       </c>
       <c r="F87" t="s">
-        <v>188</v>
+        <v>731</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B88" t="s">
-        <v>655</v>
+        <v>705</v>
       </c>
       <c r="C88">
         <v>2</v>
@@ -4377,35 +4419,35 @@
         <v>69</v>
       </c>
       <c r="E88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F88" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B89" t="s">
-        <v>627</v>
+        <v>655</v>
       </c>
       <c r="C89">
         <v>2</v>
       </c>
       <c r="D89" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F89" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B90" t="s">
         <v>627</v>
@@ -4420,15 +4462,15 @@
         <v>1</v>
       </c>
       <c r="F90" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B91" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="C91">
         <v>2</v>
@@ -4437,18 +4479,18 @@
         <v>73</v>
       </c>
       <c r="E91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B92" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C92">
         <v>2</v>
@@ -4460,15 +4502,15 @@
         <v>2</v>
       </c>
       <c r="F92" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B93" t="s">
-        <v>706</v>
+        <v>633</v>
       </c>
       <c r="C93">
         <v>2</v>
@@ -4477,18 +4519,18 @@
         <v>73</v>
       </c>
       <c r="E93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F93" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B94" t="s">
-        <v>629</v>
+        <v>706</v>
       </c>
       <c r="C94">
         <v>2</v>
@@ -4500,32 +4542,32 @@
         <v>3</v>
       </c>
       <c r="F94" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B95" t="s">
-        <v>242</v>
+        <v>629</v>
       </c>
       <c r="C95">
         <v>2</v>
       </c>
       <c r="D95" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F95" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B96" t="s">
         <v>242</v>
@@ -4540,15 +4582,15 @@
         <v>1</v>
       </c>
       <c r="F96" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B97" t="s">
-        <v>655</v>
+        <v>242</v>
       </c>
       <c r="C97">
         <v>2</v>
@@ -4557,18 +4599,18 @@
         <v>80</v>
       </c>
       <c r="E97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B98" t="s">
-        <v>627</v>
+        <v>655</v>
       </c>
       <c r="C98">
         <v>2</v>
@@ -4580,15 +4622,15 @@
         <v>2</v>
       </c>
       <c r="F98" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B99" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -4597,18 +4639,18 @@
         <v>80</v>
       </c>
       <c r="E99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F99" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B100" t="s">
-        <v>707</v>
+        <v>633</v>
       </c>
       <c r="C100">
         <v>2</v>
@@ -4620,35 +4662,35 @@
         <v>3</v>
       </c>
       <c r="F100" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>736</v>
+        <v>85</v>
       </c>
       <c r="B101" t="s">
-        <v>242</v>
+        <v>707</v>
       </c>
       <c r="C101">
         <v>2</v>
       </c>
       <c r="D101" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="E101">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F101" t="s">
-        <v>737</v>
+        <v>201</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>105</v>
+        <v>742</v>
       </c>
       <c r="B102" t="s">
-        <v>708</v>
+        <v>242</v>
       </c>
       <c r="C102">
         <v>2</v>
@@ -4657,18 +4699,18 @@
         <v>104</v>
       </c>
       <c r="E102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F102" t="s">
-        <v>215</v>
+        <v>743</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>106</v>
+        <v>736</v>
       </c>
       <c r="B103" t="s">
-        <v>709</v>
+        <v>242</v>
       </c>
       <c r="C103">
         <v>2</v>
@@ -4677,18 +4719,18 @@
         <v>104</v>
       </c>
       <c r="E103">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F103" t="s">
-        <v>216</v>
+        <v>737</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>242</v>
+        <v>708</v>
       </c>
       <c r="C104">
         <v>2</v>
@@ -4697,58 +4739,58 @@
         <v>104</v>
       </c>
       <c r="E104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F104" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="C105">
         <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E105">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F105" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>710</v>
+        <v>242</v>
       </c>
       <c r="C106">
         <v>2</v>
       </c>
       <c r="D106" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F106" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>663</v>
+        <v>705</v>
       </c>
       <c r="C107">
         <v>2</v>
@@ -4757,18 +4799,18 @@
         <v>109</v>
       </c>
       <c r="E107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F107" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B108" t="s">
-        <v>635</v>
+        <v>710</v>
       </c>
       <c r="C108">
         <v>2</v>
@@ -4777,18 +4819,18 @@
         <v>109</v>
       </c>
       <c r="E108">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F108" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B109" t="s">
-        <v>711</v>
+        <v>663</v>
       </c>
       <c r="C109">
         <v>2</v>
@@ -4797,58 +4839,58 @@
         <v>109</v>
       </c>
       <c r="E109">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F109" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B110" t="s">
-        <v>661</v>
+        <v>635</v>
       </c>
       <c r="C110">
         <v>2</v>
       </c>
       <c r="D110" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E110">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F110" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B111" t="s">
-        <v>242</v>
+        <v>711</v>
       </c>
       <c r="C111">
         <v>2</v>
       </c>
       <c r="D111" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E111">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F111" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B112" t="s">
-        <v>638</v>
+        <v>661</v>
       </c>
       <c r="C112">
         <v>2</v>
@@ -4857,18 +4899,18 @@
         <v>115</v>
       </c>
       <c r="E112">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B113" t="s">
-        <v>712</v>
+        <v>242</v>
       </c>
       <c r="C113">
         <v>2</v>
@@ -4877,58 +4919,58 @@
         <v>115</v>
       </c>
       <c r="E113">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F113" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B114" t="s">
-        <v>627</v>
+        <v>638</v>
       </c>
       <c r="C114">
         <v>2</v>
       </c>
       <c r="D114" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E114">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F114" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B115" t="s">
-        <v>242</v>
+        <v>712</v>
       </c>
       <c r="C115">
         <v>2</v>
       </c>
       <c r="D115" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E115">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F115" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B116" t="s">
-        <v>707</v>
+        <v>627</v>
       </c>
       <c r="C116">
         <v>2</v>
@@ -4937,15 +4979,15 @@
         <v>120</v>
       </c>
       <c r="E116">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F116" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B117" t="s">
         <v>242</v>
@@ -4954,38 +4996,38 @@
         <v>2</v>
       </c>
       <c r="D117" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B118" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C118">
         <v>2</v>
       </c>
       <c r="D118" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F118" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B119" t="s">
         <v>242</v>
@@ -4997,18 +5039,18 @@
         <v>125</v>
       </c>
       <c r="E119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F119" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B120" t="s">
-        <v>242</v>
+        <v>713</v>
       </c>
       <c r="C120">
         <v>2</v>
@@ -5017,18 +5059,18 @@
         <v>125</v>
       </c>
       <c r="E120">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F120" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B121" t="s">
-        <v>682</v>
+        <v>242</v>
       </c>
       <c r="C121">
         <v>2</v>
@@ -5037,52 +5079,58 @@
         <v>125</v>
       </c>
       <c r="E121">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F121" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="B122" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="C122">
         <v>2</v>
       </c>
       <c r="D122" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E122">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F122" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="B123" t="s">
-        <v>86</v>
+        <v>682</v>
       </c>
       <c r="C123">
         <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E123">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="F123" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>86</v>
+        <v>744</v>
       </c>
       <c r="B124" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -5091,24 +5139,30 @@
         <v>130</v>
       </c>
       <c r="E124">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F124" t="s">
+        <v>746</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>86</v>
+        <v>745</v>
       </c>
       <c r="B125" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="C125">
         <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E125">
         <v>1</v>
+      </c>
+      <c r="F125" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -5122,7 +5176,7 @@
         <v>2</v>
       </c>
       <c r="D126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E126">
         <v>2</v>
@@ -5130,22 +5184,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>615</v>
+        <v>86</v>
       </c>
       <c r="B127" t="s">
-        <v>242</v>
+        <v>86</v>
       </c>
       <c r="C127">
         <v>2</v>
       </c>
       <c r="D127" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E127">
         <v>3</v>
-      </c>
-      <c r="F127" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -5159,7 +5210,7 @@
         <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E128">
         <v>1</v>
@@ -5176,7 +5227,7 @@
         <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E129">
         <v>2</v>
@@ -5184,87 +5235,81 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>86</v>
+        <v>615</v>
       </c>
       <c r="B130" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
       <c r="C130">
         <v>2</v>
       </c>
       <c r="D130" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E130">
         <v>3</v>
+      </c>
+      <c r="F130" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>621</v>
+        <v>86</v>
       </c>
       <c r="B131" t="s">
-        <v>627</v>
+        <v>86</v>
       </c>
       <c r="C131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D131" t="s">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="E131">
         <v>1</v>
-      </c>
-      <c r="F131" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>416</v>
+        <v>86</v>
       </c>
       <c r="B132" t="s">
-        <v>647</v>
+        <v>86</v>
       </c>
       <c r="C132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D132" t="s">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="E132">
-        <v>1</v>
-      </c>
-      <c r="F132" t="s">
-        <v>582</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>414</v>
+        <v>86</v>
       </c>
       <c r="B133" t="s">
-        <v>636</v>
+        <v>86</v>
       </c>
       <c r="C133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D133" t="s">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="E133">
-        <v>1</v>
-      </c>
-      <c r="F133" t="s">
-        <v>580</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>417</v>
+        <v>621</v>
       </c>
       <c r="B134" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -5273,18 +5318,18 @@
         <v>1</v>
       </c>
       <c r="E134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F134" t="s">
-        <v>583</v>
+        <v>622</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B135" t="s">
-        <v>676</v>
+        <v>647</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -5293,18 +5338,18 @@
         <v>1</v>
       </c>
       <c r="E135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F135" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="B136" t="s">
-        <v>675</v>
+        <v>636</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -5313,18 +5358,18 @@
         <v>1</v>
       </c>
       <c r="E136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F136" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B137" t="s">
-        <v>677</v>
+        <v>634</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -5333,18 +5378,18 @@
         <v>1</v>
       </c>
       <c r="E137">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F137" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B138" t="s">
-        <v>634</v>
+        <v>676</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -5353,18 +5398,18 @@
         <v>1</v>
       </c>
       <c r="E138">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F138" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B139" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -5373,18 +5418,18 @@
         <v>1</v>
       </c>
       <c r="E139">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F139" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B140" t="s">
-        <v>628</v>
+        <v>677</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -5393,18 +5438,18 @@
         <v>1</v>
       </c>
       <c r="E140">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F140" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B141" t="s">
-        <v>678</v>
+        <v>634</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -5413,18 +5458,18 @@
         <v>1</v>
       </c>
       <c r="E141">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F141" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>596</v>
+        <v>420</v>
       </c>
       <c r="B142" t="s">
-        <v>635</v>
+        <v>670</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -5436,52 +5481,52 @@
         <v>4</v>
       </c>
       <c r="F142" t="s">
-        <v>604</v>
+        <v>586</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>623</v>
+        <v>419</v>
       </c>
       <c r="B143" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="C143">
         <v>1</v>
       </c>
       <c r="D143" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E143">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F143" t="s">
-        <v>624</v>
+        <v>585</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="B144" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="C144">
         <v>1</v>
       </c>
       <c r="D144" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E144">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F144" t="s">
-        <v>573</v>
+        <v>588</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>406</v>
+        <v>596</v>
       </c>
       <c r="B145" t="s">
         <v>635</v>
@@ -5490,21 +5535,21 @@
         <v>1</v>
       </c>
       <c r="D145" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E145">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F145" t="s">
-        <v>572</v>
+        <v>604</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>405</v>
+        <v>623</v>
       </c>
       <c r="B146" t="s">
-        <v>242</v>
+        <v>633</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -5516,15 +5561,15 @@
         <v>1</v>
       </c>
       <c r="F146" t="s">
-        <v>571</v>
+        <v>624</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B147" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -5533,18 +5578,18 @@
         <v>8</v>
       </c>
       <c r="E147">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F147" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B148" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -5553,18 +5598,18 @@
         <v>8</v>
       </c>
       <c r="E148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F148" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B149" t="s">
-        <v>671</v>
+        <v>242</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -5573,18 +5618,18 @@
         <v>8</v>
       </c>
       <c r="E149">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F149" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B150" t="s">
-        <v>242</v>
+        <v>659</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -5593,18 +5638,18 @@
         <v>8</v>
       </c>
       <c r="E150">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F150" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="B151" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -5613,18 +5658,18 @@
         <v>8</v>
       </c>
       <c r="E151">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F151" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B152" t="s">
-        <v>242</v>
+        <v>671</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -5633,18 +5678,18 @@
         <v>8</v>
       </c>
       <c r="E152">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F152" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B153" t="s">
-        <v>627</v>
+        <v>242</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -5653,35 +5698,35 @@
         <v>8</v>
       </c>
       <c r="E153">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F153" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="B154" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C154">
         <v>1</v>
       </c>
       <c r="D154" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E154">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F154" t="s">
-        <v>561</v>
+        <v>581</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="B155" t="s">
         <v>242</v>
@@ -5690,38 +5735,38 @@
         <v>1</v>
       </c>
       <c r="D155" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E155">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F155" t="s">
-        <v>563</v>
+        <v>579</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="B156" t="s">
-        <v>660</v>
+        <v>627</v>
       </c>
       <c r="C156">
         <v>1</v>
       </c>
       <c r="D156" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E156">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F156" t="s">
-        <v>562</v>
+        <v>578</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>597</v>
+        <v>395</v>
       </c>
       <c r="B157" t="s">
         <v>629</v>
@@ -5733,18 +5778,18 @@
         <v>15</v>
       </c>
       <c r="E157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F157" t="s">
-        <v>605</v>
+        <v>561</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B158" t="s">
-        <v>645</v>
+        <v>242</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -5753,18 +5798,18 @@
         <v>15</v>
       </c>
       <c r="E158">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F158" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B159" t="s">
-        <v>714</v>
+        <v>660</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -5773,18 +5818,18 @@
         <v>15</v>
       </c>
       <c r="E159">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F159" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>398</v>
+        <v>597</v>
       </c>
       <c r="B160" t="s">
-        <v>666</v>
+        <v>629</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -5793,18 +5838,18 @@
         <v>15</v>
       </c>
       <c r="E160">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F160" t="s">
-        <v>564</v>
+        <v>605</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B161" t="s">
-        <v>627</v>
+        <v>645</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -5813,18 +5858,18 @@
         <v>15</v>
       </c>
       <c r="E161">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F161" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B162" t="s">
-        <v>634</v>
+        <v>714</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -5833,18 +5878,18 @@
         <v>15</v>
       </c>
       <c r="E162">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F162" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B163" t="s">
-        <v>634</v>
+        <v>666</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -5853,18 +5898,18 @@
         <v>15</v>
       </c>
       <c r="E163">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F163" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B164" t="s">
-        <v>242</v>
+        <v>627</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -5876,75 +5921,75 @@
         <v>4</v>
       </c>
       <c r="F164" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="B165" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C165">
         <v>1</v>
       </c>
       <c r="D165" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E165">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F165" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="B166" t="s">
-        <v>242</v>
+        <v>634</v>
       </c>
       <c r="C166">
         <v>1</v>
       </c>
       <c r="D166" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E166">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F166" t="s">
-        <v>550</v>
+        <v>568</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="B167" t="s">
-        <v>635</v>
+        <v>242</v>
       </c>
       <c r="C167">
         <v>1</v>
       </c>
       <c r="D167" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E167">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F167" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B168" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -5956,15 +6001,15 @@
         <v>1</v>
       </c>
       <c r="F168" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B169" t="s">
-        <v>633</v>
+        <v>242</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -5973,18 +6018,18 @@
         <v>23</v>
       </c>
       <c r="E169">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F169" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B170" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -5993,18 +6038,18 @@
         <v>23</v>
       </c>
       <c r="E170">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F170" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="B171" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -6013,18 +6058,18 @@
         <v>23</v>
       </c>
       <c r="E171">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F171" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B172" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -6033,18 +6078,18 @@
         <v>23</v>
       </c>
       <c r="E172">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F172" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B173" t="s">
-        <v>635</v>
+        <v>648</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -6053,18 +6098,18 @@
         <v>23</v>
       </c>
       <c r="E173">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F173" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B174" t="s">
-        <v>647</v>
+        <v>627</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -6073,18 +6118,18 @@
         <v>23</v>
       </c>
       <c r="E174">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F174" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B175" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -6093,18 +6138,18 @@
         <v>23</v>
       </c>
       <c r="E175">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F175" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="B176" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -6113,18 +6158,18 @@
         <v>23</v>
       </c>
       <c r="E176">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F176" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B177" t="s">
-        <v>688</v>
+        <v>647</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -6136,12 +6181,12 @@
         <v>4</v>
       </c>
       <c r="F177" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="B178" t="s">
         <v>638</v>
@@ -6150,61 +6195,61 @@
         <v>1</v>
       </c>
       <c r="D178" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E178">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F178" t="s">
-        <v>537</v>
+        <v>559</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="B179" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="C179">
         <v>1</v>
       </c>
       <c r="D179" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E179">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F179" t="s">
-        <v>536</v>
+        <v>558</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="B180" t="s">
-        <v>629</v>
+        <v>688</v>
       </c>
       <c r="C180">
         <v>1</v>
       </c>
       <c r="D180" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E180">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F180" t="s">
-        <v>540</v>
+        <v>557</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B181" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -6213,18 +6258,18 @@
         <v>29</v>
       </c>
       <c r="E181">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F181" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B182" t="s">
-        <v>627</v>
+        <v>645</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -6233,18 +6278,18 @@
         <v>29</v>
       </c>
       <c r="E182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F182" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B183" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -6253,15 +6298,15 @@
         <v>29</v>
       </c>
       <c r="E183">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F183" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B184" t="s">
         <v>629</v>
@@ -6273,18 +6318,18 @@
         <v>29</v>
       </c>
       <c r="E184">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F184" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B185" t="s">
-        <v>660</v>
+        <v>627</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -6293,18 +6338,18 @@
         <v>29</v>
       </c>
       <c r="E185">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F185" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B186" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -6316,15 +6361,15 @@
         <v>3</v>
       </c>
       <c r="F186" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B187" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C187">
         <v>1</v>
@@ -6333,18 +6378,18 @@
         <v>29</v>
       </c>
       <c r="E187">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F187" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B188" t="s">
-        <v>633</v>
+        <v>660</v>
       </c>
       <c r="C188">
         <v>1</v>
@@ -6353,18 +6398,18 @@
         <v>29</v>
       </c>
       <c r="E188">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F188" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B189" t="s">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="C189">
         <v>1</v>
@@ -6373,78 +6418,78 @@
         <v>29</v>
       </c>
       <c r="E189">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F189" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="B190" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C190">
         <v>1</v>
       </c>
       <c r="D190" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E190">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F190" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="B191" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C191">
         <v>1</v>
       </c>
       <c r="D191" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E191">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F191" t="s">
-        <v>528</v>
+        <v>546</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="B192" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C192">
         <v>1</v>
       </c>
       <c r="D192" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E192">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F192" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B193" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C193">
         <v>1</v>
@@ -6453,18 +6498,18 @@
         <v>32</v>
       </c>
       <c r="E193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F193" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B194" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -6473,18 +6518,18 @@
         <v>32</v>
       </c>
       <c r="E194">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F194" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B195" t="s">
-        <v>629</v>
+        <v>659</v>
       </c>
       <c r="C195">
         <v>1</v>
@@ -6493,18 +6538,18 @@
         <v>32</v>
       </c>
       <c r="E195">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F195" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B196" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C196">
         <v>1</v>
@@ -6513,18 +6558,18 @@
         <v>32</v>
       </c>
       <c r="E196">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F196" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B197" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C197">
         <v>1</v>
@@ -6533,18 +6578,18 @@
         <v>32</v>
       </c>
       <c r="E197">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F197" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B198" t="s">
-        <v>715</v>
+        <v>629</v>
       </c>
       <c r="C198">
         <v>1</v>
@@ -6553,18 +6598,18 @@
         <v>32</v>
       </c>
       <c r="E198">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F198" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B199" t="s">
-        <v>690</v>
+        <v>629</v>
       </c>
       <c r="C199">
         <v>1</v>
@@ -6573,78 +6618,78 @@
         <v>32</v>
       </c>
       <c r="E199">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F199" t="s">
-        <v>689</v>
+        <v>534</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="B200" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="C200">
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E200">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F200" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B201" t="s">
-        <v>641</v>
+        <v>715</v>
       </c>
       <c r="C201">
         <v>1</v>
       </c>
       <c r="D201" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E201">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F201" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B202" t="s">
-        <v>629</v>
+        <v>690</v>
       </c>
       <c r="C202">
         <v>1</v>
       </c>
       <c r="D202" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E202">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F202" t="s">
-        <v>518</v>
+        <v>689</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B203" t="s">
-        <v>687</v>
+        <v>641</v>
       </c>
       <c r="C203">
         <v>1</v>
@@ -6653,18 +6698,18 @@
         <v>38</v>
       </c>
       <c r="E203">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F203" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B204" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="C204">
         <v>1</v>
@@ -6673,18 +6718,18 @@
         <v>38</v>
       </c>
       <c r="E204">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F204" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B205" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C205">
         <v>1</v>
@@ -6693,18 +6738,18 @@
         <v>38</v>
       </c>
       <c r="E205">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F205" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B206" t="s">
-        <v>658</v>
+        <v>687</v>
       </c>
       <c r="C206">
         <v>1</v>
@@ -6712,19 +6757,19 @@
       <c r="D206" t="s">
         <v>38</v>
       </c>
-      <c r="E206" t="s">
-        <v>612</v>
+      <c r="E206">
+        <v>2</v>
       </c>
       <c r="F206" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B207" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="C207">
         <v>1</v>
@@ -6732,19 +6777,19 @@
       <c r="D207" t="s">
         <v>38</v>
       </c>
-      <c r="E207" t="s">
-        <v>612</v>
+      <c r="E207">
+        <v>2</v>
       </c>
       <c r="F207" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B208" t="s">
-        <v>656</v>
+        <v>635</v>
       </c>
       <c r="C208">
         <v>1</v>
@@ -6752,79 +6797,79 @@
       <c r="D208" t="s">
         <v>38</v>
       </c>
-      <c r="E208" t="s">
-        <v>612</v>
+      <c r="E208">
+        <v>2</v>
       </c>
       <c r="F208" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="B209" t="s">
-        <v>635</v>
+        <v>658</v>
       </c>
       <c r="C209">
         <v>1</v>
       </c>
       <c r="D209" t="s">
-        <v>44</v>
-      </c>
-      <c r="E209">
-        <v>1</v>
+        <v>38</v>
+      </c>
+      <c r="E209" t="s">
+        <v>612</v>
       </c>
       <c r="F209" t="s">
-        <v>508</v>
+        <v>526</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="B210" t="s">
-        <v>629</v>
+        <v>657</v>
       </c>
       <c r="C210">
         <v>1</v>
       </c>
       <c r="D210" t="s">
-        <v>44</v>
-      </c>
-      <c r="E210">
-        <v>1</v>
+        <v>38</v>
+      </c>
+      <c r="E210" t="s">
+        <v>612</v>
       </c>
       <c r="F210" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="B211" t="s">
-        <v>630</v>
+        <v>656</v>
       </c>
       <c r="C211">
         <v>1</v>
       </c>
       <c r="D211" t="s">
-        <v>44</v>
-      </c>
-      <c r="E211">
-        <v>1</v>
+        <v>38</v>
+      </c>
+      <c r="E211" t="s">
+        <v>612</v>
       </c>
       <c r="F211" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B212" t="s">
-        <v>654</v>
+        <v>635</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -6833,18 +6878,18 @@
         <v>44</v>
       </c>
       <c r="E212">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F212" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B213" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C213">
         <v>1</v>
@@ -6853,18 +6898,18 @@
         <v>44</v>
       </c>
       <c r="E213">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F213" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B214" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="C214">
         <v>1</v>
@@ -6873,18 +6918,18 @@
         <v>44</v>
       </c>
       <c r="E214">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F214" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B215" t="s">
-        <v>629</v>
+        <v>654</v>
       </c>
       <c r="C215">
         <v>1</v>
@@ -6893,15 +6938,15 @@
         <v>44</v>
       </c>
       <c r="E215">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F215" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B216" t="s">
         <v>635</v>
@@ -6913,15 +6958,15 @@
         <v>44</v>
       </c>
       <c r="E216">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F216" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B217" t="s">
         <v>635</v>
@@ -6933,18 +6978,18 @@
         <v>44</v>
       </c>
       <c r="E217">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F217" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B218" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -6953,18 +6998,18 @@
         <v>44</v>
       </c>
       <c r="E218">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F218" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B219" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C219">
         <v>1</v>
@@ -6973,18 +7018,18 @@
         <v>44</v>
       </c>
       <c r="E219">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F219" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B220" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C220">
         <v>1</v>
@@ -6993,75 +7038,75 @@
         <v>44</v>
       </c>
       <c r="E220">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F220" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="B221" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="C221">
         <v>1</v>
       </c>
       <c r="D221" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E221">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F221" t="s">
-        <v>497</v>
+        <v>517</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="B222" t="s">
-        <v>647</v>
+        <v>627</v>
       </c>
       <c r="C222">
         <v>1</v>
       </c>
       <c r="D222" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E222">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F222" t="s">
-        <v>496</v>
+        <v>516</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>328</v>
+        <v>348</v>
       </c>
       <c r="B223" t="s">
-        <v>647</v>
+        <v>629</v>
       </c>
       <c r="C223">
         <v>1</v>
       </c>
       <c r="D223" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E223">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F223" t="s">
-        <v>495</v>
+        <v>515</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B224" t="s">
         <v>635</v>
@@ -7076,15 +7121,15 @@
         <v>1</v>
       </c>
       <c r="F224" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B225" t="s">
-        <v>629</v>
+        <v>647</v>
       </c>
       <c r="C225">
         <v>1</v>
@@ -7093,18 +7138,18 @@
         <v>50</v>
       </c>
       <c r="E225">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F225" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B226" t="s">
-        <v>629</v>
+        <v>647</v>
       </c>
       <c r="C226">
         <v>1</v>
@@ -7113,18 +7158,18 @@
         <v>50</v>
       </c>
       <c r="E226">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F226" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B227" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -7133,18 +7178,18 @@
         <v>50</v>
       </c>
       <c r="E227">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F227" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B228" t="s">
-        <v>659</v>
+        <v>629</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -7153,18 +7198,18 @@
         <v>50</v>
       </c>
       <c r="E228">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F228" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B229" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C229">
         <v>1</v>
@@ -7173,18 +7218,18 @@
         <v>50</v>
       </c>
       <c r="E229">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F229" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B230" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -7193,18 +7238,18 @@
         <v>50</v>
       </c>
       <c r="E230">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F230" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B231" t="s">
-        <v>635</v>
+        <v>659</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -7213,18 +7258,18 @@
         <v>50</v>
       </c>
       <c r="E231">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F231" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B232" t="s">
-        <v>686</v>
+        <v>635</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -7233,15 +7278,15 @@
         <v>50</v>
       </c>
       <c r="E232">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F232" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="B233" t="s">
         <v>635</v>
@@ -7250,18 +7295,18 @@
         <v>1</v>
       </c>
       <c r="D233" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E233">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F233" t="s">
-        <v>481</v>
+        <v>505</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="B234" t="s">
         <v>635</v>
@@ -7270,38 +7315,38 @@
         <v>1</v>
       </c>
       <c r="D234" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E234">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F234" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>312</v>
+        <v>336</v>
       </c>
       <c r="B235" t="s">
-        <v>635</v>
+        <v>686</v>
       </c>
       <c r="C235">
         <v>1</v>
       </c>
       <c r="D235" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E235">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F235" t="s">
-        <v>479</v>
+        <v>503</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B236" t="s">
         <v>635</v>
@@ -7316,15 +7361,15 @@
         <v>1</v>
       </c>
       <c r="F236" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B237" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -7333,18 +7378,18 @@
         <v>54</v>
       </c>
       <c r="E237">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F237" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B238" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -7353,15 +7398,15 @@
         <v>54</v>
       </c>
       <c r="E238">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F238" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B239" t="s">
         <v>635</v>
@@ -7373,18 +7418,18 @@
         <v>54</v>
       </c>
       <c r="E239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F239" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B240" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -7396,15 +7441,15 @@
         <v>2</v>
       </c>
       <c r="F240" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B241" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -7413,18 +7458,18 @@
         <v>54</v>
       </c>
       <c r="E241">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F241" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B242" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -7433,18 +7478,18 @@
         <v>54</v>
       </c>
       <c r="E242">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F242" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B243" t="s">
-        <v>649</v>
+        <v>629</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -7453,18 +7498,18 @@
         <v>54</v>
       </c>
       <c r="E243">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F243" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B244" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -7476,15 +7521,15 @@
         <v>3</v>
       </c>
       <c r="F244" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B245" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -7496,15 +7541,15 @@
         <v>3</v>
       </c>
       <c r="F245" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B246" t="s">
-        <v>635</v>
+        <v>649</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -7516,12 +7561,12 @@
         <v>3</v>
       </c>
       <c r="F246" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B247" t="s">
         <v>629</v>
@@ -7533,18 +7578,18 @@
         <v>54</v>
       </c>
       <c r="E247">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F247" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B248" t="s">
-        <v>650</v>
+        <v>635</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -7553,15 +7598,15 @@
         <v>54</v>
       </c>
       <c r="E248">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F248" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="B249" t="s">
         <v>635</v>
@@ -7570,61 +7615,61 @@
         <v>1</v>
       </c>
       <c r="D249" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E249">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F249" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>297</v>
+        <v>326</v>
       </c>
       <c r="B250" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="C250">
         <v>1</v>
       </c>
       <c r="D250" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E250">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F250" t="s">
-        <v>464</v>
+        <v>493</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>296</v>
+        <v>325</v>
       </c>
       <c r="B251" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="C251">
         <v>1</v>
       </c>
       <c r="D251" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E251">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F251" t="s">
-        <v>463</v>
+        <v>492</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B252" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -7633,18 +7678,18 @@
         <v>59</v>
       </c>
       <c r="E252">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F252" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B253" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -7653,18 +7698,18 @@
         <v>59</v>
       </c>
       <c r="E253">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F253" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B254" t="s">
-        <v>629</v>
+        <v>644</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -7673,18 +7718,18 @@
         <v>59</v>
       </c>
       <c r="E254">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F254" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B255" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -7696,15 +7741,15 @@
         <v>2</v>
       </c>
       <c r="F255" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B256" t="s">
-        <v>629</v>
+        <v>647</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -7713,15 +7758,15 @@
         <v>59</v>
       </c>
       <c r="E256">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F256" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B257" t="s">
         <v>629</v>
@@ -7733,18 +7778,18 @@
         <v>59</v>
       </c>
       <c r="E257">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F257" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B258" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -7753,15 +7798,15 @@
         <v>59</v>
       </c>
       <c r="E258">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F258" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B259" t="s">
         <v>629</v>
@@ -7776,15 +7821,15 @@
         <v>3</v>
       </c>
       <c r="F259" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B260" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -7793,18 +7838,18 @@
         <v>59</v>
       </c>
       <c r="E260">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F260" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B261" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -7813,15 +7858,15 @@
         <v>59</v>
       </c>
       <c r="E261">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F261" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B262" t="s">
         <v>629</v>
@@ -7833,18 +7878,18 @@
         <v>59</v>
       </c>
       <c r="E262">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F262" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B263" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -7856,75 +7901,75 @@
         <v>4</v>
       </c>
       <c r="F263" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="B264" t="s">
-        <v>663</v>
+        <v>635</v>
       </c>
       <c r="C264">
         <v>1</v>
       </c>
       <c r="D264" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E264">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F264" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="B265" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C265">
         <v>1</v>
       </c>
       <c r="D265" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E265">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F265" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="B266" t="s">
-        <v>635</v>
+        <v>645</v>
       </c>
       <c r="C266">
         <v>1</v>
       </c>
       <c r="D266" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E266">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F266" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B267" t="s">
-        <v>635</v>
+        <v>663</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -7933,18 +7978,18 @@
         <v>63</v>
       </c>
       <c r="E267">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F267" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B268" t="s">
-        <v>684</v>
+        <v>631</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -7953,18 +7998,18 @@
         <v>63</v>
       </c>
       <c r="E268">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F268" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B269" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -7973,18 +8018,18 @@
         <v>63</v>
       </c>
       <c r="E269">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F269" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>603</v>
+        <v>291</v>
       </c>
       <c r="B270" t="s">
-        <v>242</v>
+        <v>635</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -7993,18 +8038,18 @@
         <v>63</v>
       </c>
       <c r="E270">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F270" t="s">
-        <v>611</v>
+        <v>458</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B271" t="s">
-        <v>242</v>
+        <v>684</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -8013,18 +8058,18 @@
         <v>63</v>
       </c>
       <c r="E271">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F271" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B272" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -8033,18 +8078,18 @@
         <v>63</v>
       </c>
       <c r="E272">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F272" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>295</v>
+        <v>603</v>
       </c>
       <c r="B273" t="s">
-        <v>644</v>
+        <v>242</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -8053,18 +8098,18 @@
         <v>63</v>
       </c>
       <c r="E273">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F273" t="s">
-        <v>462</v>
+        <v>611</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B274" t="s">
-        <v>647</v>
+        <v>242</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -8073,15 +8118,15 @@
         <v>63</v>
       </c>
       <c r="E274">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F274" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B275" t="s">
         <v>635</v>
@@ -8090,61 +8135,61 @@
         <v>1</v>
       </c>
       <c r="D275" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E275">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F275" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>680</v>
+        <v>295</v>
       </c>
       <c r="B276" t="s">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="C276">
         <v>1</v>
       </c>
       <c r="D276" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E276">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F276" t="s">
-        <v>681</v>
+        <v>462</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B277" t="s">
-        <v>684</v>
+        <v>647</v>
       </c>
       <c r="C277">
         <v>1</v>
       </c>
       <c r="D277" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E277">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F277" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B278" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -8153,15 +8198,15 @@
         <v>64</v>
       </c>
       <c r="E278">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F278" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>281</v>
+        <v>680</v>
       </c>
       <c r="B279" t="s">
         <v>635</v>
@@ -8173,18 +8218,18 @@
         <v>64</v>
       </c>
       <c r="E279">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F279" t="s">
-        <v>448</v>
+        <v>681</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>425</v>
+        <v>283</v>
       </c>
       <c r="B280" t="s">
-        <v>643</v>
+        <v>684</v>
       </c>
       <c r="C280">
         <v>1</v>
@@ -8193,18 +8238,18 @@
         <v>64</v>
       </c>
       <c r="E280">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F280" t="s">
-        <v>591</v>
+        <v>450</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>592</v>
+        <v>282</v>
       </c>
       <c r="B281" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="C281">
         <v>1</v>
@@ -8213,18 +8258,18 @@
         <v>64</v>
       </c>
       <c r="E281">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F281" t="s">
-        <v>593</v>
+        <v>449</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C282">
         <v>1</v>
@@ -8233,18 +8278,18 @@
         <v>64</v>
       </c>
       <c r="E282">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F282" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>284</v>
+        <v>425</v>
       </c>
       <c r="B283" t="s">
-        <v>685</v>
+        <v>643</v>
       </c>
       <c r="C283">
         <v>1</v>
@@ -8256,75 +8301,75 @@
         <v>4</v>
       </c>
       <c r="F283" t="s">
-        <v>451</v>
+        <v>591</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>274</v>
+        <v>592</v>
       </c>
       <c r="B284" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C284">
         <v>1</v>
       </c>
       <c r="D284" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E284">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F284" t="s">
-        <v>441</v>
+        <v>593</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B285" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C285">
         <v>1</v>
       </c>
       <c r="D285" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E285">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F285" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>633</v>
+        <v>685</v>
       </c>
       <c r="C286">
         <v>1</v>
       </c>
       <c r="D286" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E286">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F286" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B287" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -8333,18 +8378,18 @@
         <v>69</v>
       </c>
       <c r="E287">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F287" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B288" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C288">
         <v>1</v>
@@ -8353,18 +8398,18 @@
         <v>69</v>
       </c>
       <c r="E288">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F288" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>600</v>
+        <v>272</v>
       </c>
       <c r="B289" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C289">
         <v>1</v>
@@ -8373,18 +8418,18 @@
         <v>69</v>
       </c>
       <c r="E289">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F289" t="s">
-        <v>608</v>
+        <v>439</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>599</v>
+        <v>276</v>
       </c>
       <c r="B290" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -8396,15 +8441,15 @@
         <v>2</v>
       </c>
       <c r="F290" t="s">
-        <v>607</v>
+        <v>443</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B291" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C291">
         <v>1</v>
@@ -8413,18 +8458,18 @@
         <v>69</v>
       </c>
       <c r="E291">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F291" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>277</v>
+        <v>600</v>
       </c>
       <c r="B292" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C292">
         <v>1</v>
@@ -8433,15 +8478,15 @@
         <v>69</v>
       </c>
       <c r="E292">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F292" t="s">
-        <v>444</v>
+        <v>608</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B293" t="s">
         <v>638</v>
@@ -8453,18 +8498,18 @@
         <v>69</v>
       </c>
       <c r="E293">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F293" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B294" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C294">
         <v>1</v>
@@ -8473,18 +8518,18 @@
         <v>69</v>
       </c>
       <c r="E294">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F294" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>620</v>
+        <v>277</v>
       </c>
       <c r="B295" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C295">
         <v>1</v>
@@ -8493,18 +8538,18 @@
         <v>69</v>
       </c>
       <c r="E295">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F295" t="s">
-        <v>619</v>
+        <v>444</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>271</v>
+        <v>601</v>
       </c>
       <c r="B296" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="C296">
         <v>1</v>
@@ -8513,78 +8558,78 @@
         <v>69</v>
       </c>
       <c r="E296">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F296" t="s">
-        <v>438</v>
+        <v>609</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="B297" t="s">
-        <v>683</v>
+        <v>638</v>
       </c>
       <c r="C297">
         <v>1</v>
       </c>
       <c r="D297" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E297">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F297" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>598</v>
+        <v>620</v>
       </c>
       <c r="B298" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="C298">
         <v>1</v>
       </c>
       <c r="D298" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E298">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F298" t="s">
-        <v>606</v>
+        <v>619</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B299" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="C299">
         <v>1</v>
       </c>
       <c r="D299" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E299">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F299" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B300" t="s">
-        <v>635</v>
+        <v>683</v>
       </c>
       <c r="C300">
         <v>1</v>
@@ -8593,18 +8638,18 @@
         <v>73</v>
       </c>
       <c r="E300">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F300" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>266</v>
+        <v>598</v>
       </c>
       <c r="B301" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="C301">
         <v>1</v>
@@ -8613,18 +8658,18 @@
         <v>73</v>
       </c>
       <c r="E301">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F301" t="s">
-        <v>433</v>
+        <v>606</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B302" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C302">
         <v>1</v>
@@ -8633,18 +8678,18 @@
         <v>73</v>
       </c>
       <c r="E302">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F302" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B303" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C303">
         <v>1</v>
@@ -8653,18 +8698,18 @@
         <v>73</v>
       </c>
       <c r="E303">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F303" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B304" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="C304">
         <v>1</v>
@@ -8673,18 +8718,18 @@
         <v>73</v>
       </c>
       <c r="E304">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F304" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B305" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="C305">
         <v>1</v>
@@ -8693,18 +8738,18 @@
         <v>73</v>
       </c>
       <c r="E305">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F305" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>123</v>
+        <v>270</v>
       </c>
       <c r="B306" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -8713,15 +8758,15 @@
         <v>73</v>
       </c>
       <c r="E306">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F306" t="s">
-        <v>230</v>
+        <v>437</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="B307" t="s">
         <v>635</v>
@@ -8730,61 +8775,61 @@
         <v>1</v>
       </c>
       <c r="D307" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E307">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F307" t="s">
-        <v>253</v>
+        <v>436</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="B308" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="C308">
         <v>1</v>
       </c>
       <c r="D308" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E308">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F308" t="s">
-        <v>252</v>
+        <v>435</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>243</v>
+        <v>123</v>
       </c>
       <c r="B309" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="C309">
         <v>1</v>
       </c>
       <c r="D309" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E309">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F309" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B310" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C310">
         <v>1</v>
@@ -8793,15 +8838,15 @@
         <v>80</v>
       </c>
       <c r="E310">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F310" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B311" t="s">
         <v>635</v>
@@ -8813,18 +8858,18 @@
         <v>80</v>
       </c>
       <c r="E311">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F311" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B312" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C312">
         <v>1</v>
@@ -8833,18 +8878,18 @@
         <v>80</v>
       </c>
       <c r="E312">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F312" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="B313" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -8853,18 +8898,18 @@
         <v>80</v>
       </c>
       <c r="E313">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F313" t="s">
-        <v>426</v>
+        <v>256</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>602</v>
+        <v>248</v>
       </c>
       <c r="B314" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="C314">
         <v>1</v>
@@ -8873,15 +8918,15 @@
         <v>80</v>
       </c>
       <c r="E314">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F314" t="s">
-        <v>610</v>
+        <v>255</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B315" t="s">
         <v>633</v>
@@ -8893,15 +8938,15 @@
         <v>80</v>
       </c>
       <c r="E315">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F315" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="B316" t="s">
         <v>635</v>
@@ -8916,15 +8961,15 @@
         <v>3</v>
       </c>
       <c r="F316" t="s">
-        <v>257</v>
+        <v>426</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>262</v>
+        <v>602</v>
       </c>
       <c r="B317" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -8933,18 +8978,18 @@
         <v>80</v>
       </c>
       <c r="E317">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F317" t="s">
-        <v>429</v>
+        <v>610</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="B318" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -8953,18 +8998,18 @@
         <v>80</v>
       </c>
       <c r="E318">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F318" t="s">
-        <v>428</v>
+        <v>258</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="B319" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -8973,26 +9018,86 @@
         <v>80</v>
       </c>
       <c r="E319">
+        <v>3</v>
+      </c>
+      <c r="F319" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>262</v>
+      </c>
+      <c r="B320" t="s">
+        <v>639</v>
+      </c>
+      <c r="C320">
+        <v>1</v>
+      </c>
+      <c r="D320" t="s">
+        <v>80</v>
+      </c>
+      <c r="E320">
         <v>4</v>
       </c>
-      <c r="F319" t="s">
+      <c r="F320" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>261</v>
+      </c>
+      <c r="B321" t="s">
+        <v>639</v>
+      </c>
+      <c r="C321">
+        <v>1</v>
+      </c>
+      <c r="D321" t="s">
+        <v>80</v>
+      </c>
+      <c r="E321">
+        <v>4</v>
+      </c>
+      <c r="F321" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>260</v>
+      </c>
+      <c r="B322" t="s">
+        <v>629</v>
+      </c>
+      <c r="C322">
+        <v>1</v>
+      </c>
+      <c r="D322" t="s">
+        <v>80</v>
+      </c>
+      <c r="E322">
+        <v>4</v>
+      </c>
+      <c r="F322" t="s">
         <v>427</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F319" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F319">
-      <sortCondition descending="1" ref="C2:C319"/>
-      <sortCondition ref="D2:D319"/>
-      <sortCondition ref="E2:E319"/>
-      <sortCondition descending="1" ref="A2:A319"/>
+  <autoFilter ref="A1:F322" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F322">
+      <sortCondition descending="1" ref="C2:C322"/>
+      <sortCondition ref="D2:D322"/>
+      <sortCondition ref="E2:E322"/>
+      <sortCondition descending="1" ref="A2:A322"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F318">
-    <sortCondition descending="1" ref="C2:C318"/>
-    <sortCondition ref="D2:D318"/>
-    <sortCondition ref="E2:E318"/>
-    <sortCondition descending="1" ref="A2:A318"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F321">
+    <sortCondition descending="1" ref="C2:C321"/>
+    <sortCondition ref="D2:D321"/>
+    <sortCondition ref="E2:E321"/>
+    <sortCondition descending="1" ref="A2:A321"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
